--- a/thaco/API/1 - VPTQ THACO-11FEBv2.xlsx
+++ b/thaco/API/1 - VPTQ THACO-11FEBv2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/API/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC81F2D8-AEDD-8648-9867-1327F7D9F23C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F3329C-22EE-8142-9521-EF5CA36403B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38400" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="761" xr2:uid="{D2D6ECD8-DC99-4D28-8DAC-0623419D46D2}"/>
   </bookViews>
@@ -4365,18 +4365,91 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Đối tượng Lương ngày tại các TĐTV
-Reply:
-    LT: Lương Tháng
-LN: Lương ngày
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Comment:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">    Đối tượng Lương ngày tại các TĐTV
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Reply:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">    LT: Lương Tháng
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">LN: Lương ngày
 </t>
         </r>
       </text>
@@ -4432,7 +4505,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="158">
   <si>
     <t>CÔNG TY …..............</t>
   </si>
@@ -5745,7 +5818,7 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="45" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="503">
+  <cellXfs count="504">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6630,6 +6703,114 @@
     <xf numFmtId="165" fontId="29" fillId="7" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="54" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="54" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="6" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="6" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="54" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6639,27 +6820,6 @@
     <xf numFmtId="164" fontId="54" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="55" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6669,6 +6829,60 @@
     <xf numFmtId="165" fontId="55" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="43" fontId="13" fillId="3" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="3" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="3" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="3" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="72" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="72" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="72" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="71" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6678,13 +6892,34 @@
     <xf numFmtId="165" fontId="71" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6696,166 +6931,145 @@
     <xf numFmtId="165" fontId="8" fillId="6" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="44" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="44" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="44" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="22" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="6" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="22" fillId="2" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="44" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="22" fillId="2" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="44" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="44" fillId="6" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="3" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="3" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="3" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="3" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="72" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="72" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="72" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="54" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="54" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="22" fillId="2" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -6883,15 +7097,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6900,15 +7105,6 @@
     <xf numFmtId="165" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="22" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6924,127 +7120,64 @@
     <xf numFmtId="165" fontId="22" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="22" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="22" fillId="2" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="22" fillId="2" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="22" fillId="2" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7053,14 +7186,41 @@
     <xf numFmtId="0" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="28" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="28" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="28" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -7074,92 +7234,8 @@
     <xf numFmtId="165" fontId="18" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -7952,91 +8028,91 @@
       <c r="CD2" s="279"/>
     </row>
     <row r="3" spans="1:87" s="16" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="351" t="str">
+      <c r="A3" s="397" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
         <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
       </c>
-      <c r="B3" s="351"/>
-      <c r="C3" s="351"/>
-      <c r="D3" s="351"/>
-      <c r="E3" s="351"/>
-      <c r="F3" s="351"/>
-      <c r="G3" s="351"/>
-      <c r="H3" s="351"/>
-      <c r="I3" s="351"/>
-      <c r="J3" s="351"/>
-      <c r="K3" s="351"/>
-      <c r="L3" s="351"/>
-      <c r="M3" s="351"/>
-      <c r="N3" s="351"/>
-      <c r="O3" s="351"/>
-      <c r="P3" s="351"/>
-      <c r="Q3" s="351"/>
-      <c r="R3" s="351"/>
-      <c r="S3" s="351"/>
-      <c r="T3" s="351"/>
-      <c r="U3" s="351"/>
-      <c r="V3" s="351"/>
-      <c r="W3" s="351"/>
-      <c r="X3" s="351"/>
-      <c r="Y3" s="351"/>
-      <c r="Z3" s="351"/>
-      <c r="AA3" s="351"/>
-      <c r="AB3" s="351"/>
-      <c r="AC3" s="351"/>
-      <c r="AD3" s="351"/>
-      <c r="AE3" s="351"/>
-      <c r="AF3" s="351"/>
-      <c r="AG3" s="351"/>
-      <c r="AH3" s="351"/>
-      <c r="AI3" s="351"/>
-      <c r="AJ3" s="351"/>
-      <c r="AK3" s="351"/>
-      <c r="AL3" s="351"/>
-      <c r="AM3" s="351"/>
-      <c r="AN3" s="351"/>
-      <c r="AO3" s="351"/>
-      <c r="AP3" s="351"/>
-      <c r="AQ3" s="351"/>
-      <c r="AR3" s="351"/>
-      <c r="AS3" s="351"/>
-      <c r="AT3" s="351"/>
-      <c r="AU3" s="351"/>
-      <c r="AV3" s="351"/>
-      <c r="AW3" s="351"/>
-      <c r="AX3" s="351"/>
-      <c r="AY3" s="351"/>
-      <c r="AZ3" s="351"/>
-      <c r="BA3" s="351"/>
-      <c r="BB3" s="351"/>
-      <c r="BC3" s="351"/>
-      <c r="BD3" s="351"/>
-      <c r="BE3" s="351"/>
-      <c r="BF3" s="351"/>
-      <c r="BG3" s="351"/>
-      <c r="BH3" s="351"/>
-      <c r="BI3" s="351"/>
-      <c r="BJ3" s="351"/>
-      <c r="BK3" s="351"/>
-      <c r="BL3" s="351"/>
-      <c r="BM3" s="351"/>
-      <c r="BN3" s="351"/>
-      <c r="BO3" s="351"/>
-      <c r="BP3" s="351"/>
-      <c r="BQ3" s="351"/>
-      <c r="BR3" s="351"/>
-      <c r="BS3" s="351"/>
-      <c r="BT3" s="351"/>
-      <c r="BU3" s="351"/>
+      <c r="B3" s="397"/>
+      <c r="C3" s="397"/>
+      <c r="D3" s="397"/>
+      <c r="E3" s="397"/>
+      <c r="F3" s="397"/>
+      <c r="G3" s="397"/>
+      <c r="H3" s="397"/>
+      <c r="I3" s="397"/>
+      <c r="J3" s="397"/>
+      <c r="K3" s="397"/>
+      <c r="L3" s="397"/>
+      <c r="M3" s="397"/>
+      <c r="N3" s="397"/>
+      <c r="O3" s="397"/>
+      <c r="P3" s="397"/>
+      <c r="Q3" s="397"/>
+      <c r="R3" s="397"/>
+      <c r="S3" s="397"/>
+      <c r="T3" s="397"/>
+      <c r="U3" s="397"/>
+      <c r="V3" s="397"/>
+      <c r="W3" s="397"/>
+      <c r="X3" s="397"/>
+      <c r="Y3" s="397"/>
+      <c r="Z3" s="397"/>
+      <c r="AA3" s="397"/>
+      <c r="AB3" s="397"/>
+      <c r="AC3" s="397"/>
+      <c r="AD3" s="397"/>
+      <c r="AE3" s="397"/>
+      <c r="AF3" s="397"/>
+      <c r="AG3" s="397"/>
+      <c r="AH3" s="397"/>
+      <c r="AI3" s="397"/>
+      <c r="AJ3" s="397"/>
+      <c r="AK3" s="397"/>
+      <c r="AL3" s="397"/>
+      <c r="AM3" s="397"/>
+      <c r="AN3" s="397"/>
+      <c r="AO3" s="397"/>
+      <c r="AP3" s="397"/>
+      <c r="AQ3" s="397"/>
+      <c r="AR3" s="397"/>
+      <c r="AS3" s="397"/>
+      <c r="AT3" s="397"/>
+      <c r="AU3" s="397"/>
+      <c r="AV3" s="397"/>
+      <c r="AW3" s="397"/>
+      <c r="AX3" s="397"/>
+      <c r="AY3" s="397"/>
+      <c r="AZ3" s="397"/>
+      <c r="BA3" s="397"/>
+      <c r="BB3" s="397"/>
+      <c r="BC3" s="397"/>
+      <c r="BD3" s="397"/>
+      <c r="BE3" s="397"/>
+      <c r="BF3" s="397"/>
+      <c r="BG3" s="397"/>
+      <c r="BH3" s="397"/>
+      <c r="BI3" s="397"/>
+      <c r="BJ3" s="397"/>
+      <c r="BK3" s="397"/>
+      <c r="BL3" s="397"/>
+      <c r="BM3" s="397"/>
+      <c r="BN3" s="397"/>
+      <c r="BO3" s="397"/>
+      <c r="BP3" s="397"/>
+      <c r="BQ3" s="397"/>
+      <c r="BR3" s="397"/>
+      <c r="BS3" s="397"/>
+      <c r="BT3" s="397"/>
+      <c r="BU3" s="397"/>
       <c r="BV3" s="281"/>
-      <c r="BW3" s="355" t="s">
+      <c r="BW3" s="375" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="355"/>
-      <c r="BY3" s="355"/>
-      <c r="BZ3" s="355"/>
-      <c r="CA3" s="355"/>
-      <c r="CB3" s="356"/>
+      <c r="BX3" s="375"/>
+      <c r="BY3" s="375"/>
+      <c r="BZ3" s="375"/>
+      <c r="CA3" s="375"/>
+      <c r="CB3" s="376"/>
       <c r="CC3" s="282"/>
       <c r="CD3" s="282"/>
     </row>
@@ -8114,12 +8190,12 @@
       <c r="BT4" s="283"/>
       <c r="BU4" s="283"/>
       <c r="BV4" s="283"/>
-      <c r="BW4" s="356"/>
-      <c r="BX4" s="356"/>
-      <c r="BY4" s="356"/>
-      <c r="BZ4" s="356"/>
-      <c r="CA4" s="356"/>
-      <c r="CB4" s="356"/>
+      <c r="BW4" s="376"/>
+      <c r="BX4" s="376"/>
+      <c r="BY4" s="376"/>
+      <c r="BZ4" s="376"/>
+      <c r="CA4" s="376"/>
+      <c r="CB4" s="376"/>
       <c r="CC4" s="282"/>
       <c r="CD4" s="282"/>
     </row>
@@ -8197,12 +8273,12 @@
       <c r="BT5" s="283"/>
       <c r="BU5" s="283"/>
       <c r="BV5" s="283"/>
-      <c r="BW5" s="356"/>
-      <c r="BX5" s="356"/>
-      <c r="BY5" s="356"/>
-      <c r="BZ5" s="356"/>
-      <c r="CA5" s="356"/>
-      <c r="CB5" s="356"/>
+      <c r="BW5" s="376"/>
+      <c r="BX5" s="376"/>
+      <c r="BY5" s="376"/>
+      <c r="BZ5" s="376"/>
+      <c r="CA5" s="376"/>
+      <c r="CB5" s="376"/>
       <c r="CC5" s="282"/>
       <c r="CD5" s="282"/>
     </row>
@@ -8280,12 +8356,12 @@
       <c r="BT6" s="285"/>
       <c r="BU6" s="285"/>
       <c r="BV6" s="285"/>
-      <c r="BW6" s="355"/>
-      <c r="BX6" s="355"/>
-      <c r="BY6" s="355"/>
-      <c r="BZ6" s="355"/>
-      <c r="CA6" s="355"/>
-      <c r="CB6" s="356"/>
+      <c r="BW6" s="375"/>
+      <c r="BX6" s="375"/>
+      <c r="BY6" s="375"/>
+      <c r="BZ6" s="375"/>
+      <c r="CA6" s="375"/>
+      <c r="CB6" s="376"/>
       <c r="CC6" s="282"/>
       <c r="CD6" s="282"/>
     </row>
@@ -8438,356 +8514,356 @@
       </c>
     </row>
     <row r="8" spans="1:87" s="237" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="357" t="s">
+      <c r="A8" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="360" t="s">
+      <c r="B8" s="380" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="342" t="s">
+      <c r="C8" s="329" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="352" t="s">
+      <c r="D8" s="383" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="352" t="s">
+      <c r="E8" s="383" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="342" t="s">
+      <c r="F8" s="329" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="339" t="s">
+      <c r="G8" s="386" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="369" t="s">
+      <c r="H8" s="354" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="369" t="s">
+      <c r="I8" s="354" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="339" t="s">
+      <c r="J8" s="386" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="372" t="s">
+      <c r="K8" s="357" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="373"/>
-      <c r="M8" s="373"/>
-      <c r="N8" s="373"/>
-      <c r="O8" s="373"/>
-      <c r="P8" s="373"/>
-      <c r="Q8" s="373"/>
-      <c r="R8" s="373"/>
-      <c r="S8" s="373"/>
-      <c r="T8" s="373"/>
-      <c r="U8" s="373"/>
-      <c r="V8" s="373"/>
-      <c r="W8" s="373"/>
-      <c r="X8" s="373"/>
-      <c r="Y8" s="374" t="s">
+      <c r="L8" s="358"/>
+      <c r="M8" s="358"/>
+      <c r="N8" s="358"/>
+      <c r="O8" s="358"/>
+      <c r="P8" s="358"/>
+      <c r="Q8" s="358"/>
+      <c r="R8" s="358"/>
+      <c r="S8" s="358"/>
+      <c r="T8" s="358"/>
+      <c r="U8" s="358"/>
+      <c r="V8" s="358"/>
+      <c r="W8" s="358"/>
+      <c r="X8" s="358"/>
+      <c r="Y8" s="359" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="375"/>
-      <c r="AA8" s="375"/>
-      <c r="AB8" s="375"/>
-      <c r="AC8" s="375"/>
-      <c r="AD8" s="375"/>
-      <c r="AE8" s="375"/>
-      <c r="AF8" s="375"/>
-      <c r="AG8" s="375"/>
-      <c r="AH8" s="375"/>
-      <c r="AI8" s="375"/>
-      <c r="AJ8" s="375"/>
-      <c r="AK8" s="375"/>
-      <c r="AL8" s="375"/>
-      <c r="AM8" s="375"/>
-      <c r="AN8" s="375"/>
-      <c r="AO8" s="376"/>
-      <c r="AP8" s="339" t="s">
+      <c r="Z8" s="360"/>
+      <c r="AA8" s="360"/>
+      <c r="AB8" s="360"/>
+      <c r="AC8" s="360"/>
+      <c r="AD8" s="360"/>
+      <c r="AE8" s="360"/>
+      <c r="AF8" s="360"/>
+      <c r="AG8" s="360"/>
+      <c r="AH8" s="360"/>
+      <c r="AI8" s="360"/>
+      <c r="AJ8" s="360"/>
+      <c r="AK8" s="360"/>
+      <c r="AL8" s="360"/>
+      <c r="AM8" s="360"/>
+      <c r="AN8" s="360"/>
+      <c r="AO8" s="361"/>
+      <c r="AP8" s="386" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="339" t="s">
+      <c r="AQ8" s="386" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="339" t="s">
+      <c r="AR8" s="386" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="339" t="s">
+      <c r="AS8" s="386" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="339" t="s">
+      <c r="AT8" s="386" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="339" t="s">
+      <c r="AU8" s="386" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="342" t="s">
+      <c r="AV8" s="329" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="348" t="s">
+      <c r="AW8" s="395" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="342" t="s">
+      <c r="AX8" s="329" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="345" t="s">
+      <c r="AY8" s="399" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="346"/>
-      <c r="BA8" s="346"/>
-      <c r="BB8" s="346"/>
-      <c r="BC8" s="346"/>
-      <c r="BD8" s="346"/>
-      <c r="BE8" s="346"/>
-      <c r="BF8" s="346"/>
-      <c r="BG8" s="346"/>
-      <c r="BH8" s="346"/>
-      <c r="BI8" s="346"/>
-      <c r="BJ8" s="346"/>
-      <c r="BK8" s="346"/>
-      <c r="BL8" s="346"/>
-      <c r="BM8" s="346"/>
-      <c r="BN8" s="346"/>
-      <c r="BO8" s="346"/>
-      <c r="BP8" s="346"/>
-      <c r="BQ8" s="347"/>
-      <c r="BR8" s="333" t="s">
+      <c r="AZ8" s="400"/>
+      <c r="BA8" s="400"/>
+      <c r="BB8" s="400"/>
+      <c r="BC8" s="400"/>
+      <c r="BD8" s="400"/>
+      <c r="BE8" s="400"/>
+      <c r="BF8" s="400"/>
+      <c r="BG8" s="400"/>
+      <c r="BH8" s="400"/>
+      <c r="BI8" s="400"/>
+      <c r="BJ8" s="400"/>
+      <c r="BK8" s="400"/>
+      <c r="BL8" s="400"/>
+      <c r="BM8" s="400"/>
+      <c r="BN8" s="400"/>
+      <c r="BO8" s="400"/>
+      <c r="BP8" s="400"/>
+      <c r="BQ8" s="401"/>
+      <c r="BR8" s="346" t="s">
         <v>26</v>
       </c>
-      <c r="BS8" s="401"/>
-      <c r="BT8" s="342" t="s">
+      <c r="BS8" s="353"/>
+      <c r="BT8" s="329" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="333" t="s">
+      <c r="BU8" s="346" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="306"/>
-      <c r="BW8" s="387" t="s">
+      <c r="BW8" s="334" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="390" t="s">
+      <c r="BX8" s="337" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="391"/>
-      <c r="BZ8" s="391"/>
-      <c r="CA8" s="392"/>
-      <c r="CB8" s="384" t="s">
+      <c r="BY8" s="338"/>
+      <c r="BZ8" s="338"/>
+      <c r="CA8" s="339"/>
+      <c r="CB8" s="326" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="384" t="s">
+      <c r="CC8" s="326" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="384" t="s">
+      <c r="CD8" s="326" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="28"/>
       <c r="CI8" s="28"/>
     </row>
     <row r="9" spans="1:87" s="237" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="358"/>
-      <c r="B9" s="361"/>
-      <c r="C9" s="343"/>
-      <c r="D9" s="353"/>
-      <c r="E9" s="353"/>
-      <c r="F9" s="343"/>
-      <c r="G9" s="340"/>
-      <c r="H9" s="370"/>
-      <c r="I9" s="370"/>
-      <c r="J9" s="340"/>
-      <c r="K9" s="326" t="s">
+      <c r="A9" s="378"/>
+      <c r="B9" s="381"/>
+      <c r="C9" s="330"/>
+      <c r="D9" s="384"/>
+      <c r="E9" s="384"/>
+      <c r="F9" s="330"/>
+      <c r="G9" s="387"/>
+      <c r="H9" s="355"/>
+      <c r="I9" s="355"/>
+      <c r="J9" s="387"/>
+      <c r="K9" s="362" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="326" t="s">
+      <c r="L9" s="362" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="326" t="s">
+      <c r="M9" s="362" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="326" t="s">
+      <c r="N9" s="362" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="326" t="s">
+      <c r="O9" s="362" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="326" t="s">
+      <c r="P9" s="362" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="326" t="s">
+      <c r="Q9" s="362" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="326" t="s">
+      <c r="R9" s="362" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="326" t="s">
+      <c r="S9" s="362" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="326" t="s">
+      <c r="T9" s="362" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="326" t="s">
+      <c r="U9" s="362" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="377" t="s">
+      <c r="V9" s="368" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="378"/>
-      <c r="X9" s="326" t="s">
+      <c r="W9" s="369"/>
+      <c r="X9" s="362" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="336" t="s">
+      <c r="Y9" s="365" t="s">
         <v>47</v>
       </c>
-      <c r="Z9" s="336" t="s">
+      <c r="Z9" s="365" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="336" t="s">
+      <c r="AA9" s="365" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="336" t="s">
+      <c r="AB9" s="365" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="336" t="s">
+      <c r="AC9" s="365" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="336" t="s">
+      <c r="AD9" s="365" t="s">
         <v>52</v>
       </c>
-      <c r="AE9" s="336" t="s">
+      <c r="AE9" s="365" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="336" t="s">
+      <c r="AF9" s="365" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="336" t="s">
+      <c r="AG9" s="365" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="336" t="s">
+      <c r="AH9" s="365" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="336" t="s">
+      <c r="AI9" s="365" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="381" t="s">
+      <c r="AJ9" s="372" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="333" t="s">
+      <c r="AK9" s="346" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="348" t="s">
+      <c r="AL9" s="395" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="336" t="s">
+      <c r="AM9" s="365" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="342" t="s">
+      <c r="AN9" s="329" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="342" t="s">
+      <c r="AO9" s="329" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="340"/>
-      <c r="AQ9" s="340"/>
-      <c r="AR9" s="340"/>
-      <c r="AS9" s="340"/>
-      <c r="AT9" s="340"/>
-      <c r="AU9" s="340"/>
-      <c r="AV9" s="343"/>
-      <c r="AW9" s="349"/>
-      <c r="AX9" s="343"/>
-      <c r="AY9" s="363" t="s">
+      <c r="AP9" s="387"/>
+      <c r="AQ9" s="387"/>
+      <c r="AR9" s="387"/>
+      <c r="AS9" s="387"/>
+      <c r="AT9" s="387"/>
+      <c r="AU9" s="387"/>
+      <c r="AV9" s="330"/>
+      <c r="AW9" s="398"/>
+      <c r="AX9" s="330"/>
+      <c r="AY9" s="389" t="s">
         <v>64</v>
       </c>
-      <c r="AZ9" s="364"/>
-      <c r="BA9" s="364"/>
-      <c r="BB9" s="364"/>
-      <c r="BC9" s="364"/>
-      <c r="BD9" s="364"/>
-      <c r="BE9" s="364"/>
-      <c r="BF9" s="364"/>
-      <c r="BG9" s="364"/>
-      <c r="BH9" s="364"/>
-      <c r="BI9" s="364"/>
-      <c r="BJ9" s="364"/>
-      <c r="BK9" s="364"/>
-      <c r="BL9" s="365"/>
-      <c r="BM9" s="366" t="s">
+      <c r="AZ9" s="390"/>
+      <c r="BA9" s="390"/>
+      <c r="BB9" s="390"/>
+      <c r="BC9" s="390"/>
+      <c r="BD9" s="390"/>
+      <c r="BE9" s="390"/>
+      <c r="BF9" s="390"/>
+      <c r="BG9" s="390"/>
+      <c r="BH9" s="390"/>
+      <c r="BI9" s="390"/>
+      <c r="BJ9" s="390"/>
+      <c r="BK9" s="390"/>
+      <c r="BL9" s="391"/>
+      <c r="BM9" s="392" t="s">
         <v>65</v>
       </c>
-      <c r="BN9" s="367"/>
-      <c r="BO9" s="367"/>
-      <c r="BP9" s="367"/>
-      <c r="BQ9" s="368"/>
-      <c r="BR9" s="343" t="s">
+      <c r="BN9" s="393"/>
+      <c r="BO9" s="393"/>
+      <c r="BP9" s="393"/>
+      <c r="BQ9" s="394"/>
+      <c r="BR9" s="330" t="s">
         <v>66</v>
       </c>
-      <c r="BS9" s="343" t="s">
+      <c r="BS9" s="330" t="s">
         <v>67</v>
       </c>
-      <c r="BT9" s="343"/>
-      <c r="BU9" s="334"/>
+      <c r="BT9" s="330"/>
+      <c r="BU9" s="347"/>
       <c r="BV9" s="306"/>
-      <c r="BW9" s="388"/>
-      <c r="BX9" s="393"/>
-      <c r="BY9" s="394"/>
-      <c r="BZ9" s="394"/>
-      <c r="CA9" s="395"/>
-      <c r="CB9" s="385"/>
-      <c r="CC9" s="385"/>
-      <c r="CD9" s="385"/>
+      <c r="BW9" s="335"/>
+      <c r="BX9" s="340"/>
+      <c r="BY9" s="341"/>
+      <c r="BZ9" s="341"/>
+      <c r="CA9" s="342"/>
+      <c r="CB9" s="327"/>
+      <c r="CC9" s="327"/>
+      <c r="CD9" s="327"/>
       <c r="CH9" s="28"/>
       <c r="CI9" s="28"/>
     </row>
     <row r="10" spans="1:87" s="78" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="358"/>
-      <c r="B10" s="361"/>
-      <c r="C10" s="343"/>
-      <c r="D10" s="353"/>
-      <c r="E10" s="353"/>
-      <c r="F10" s="343"/>
-      <c r="G10" s="340"/>
-      <c r="H10" s="370"/>
-      <c r="I10" s="370"/>
-      <c r="J10" s="340"/>
-      <c r="K10" s="327"/>
-      <c r="L10" s="327"/>
-      <c r="M10" s="327"/>
-      <c r="N10" s="327"/>
-      <c r="O10" s="327"/>
-      <c r="P10" s="327"/>
-      <c r="Q10" s="327"/>
-      <c r="R10" s="327"/>
-      <c r="S10" s="327"/>
-      <c r="T10" s="327"/>
-      <c r="U10" s="327"/>
-      <c r="V10" s="379"/>
-      <c r="W10" s="380"/>
-      <c r="X10" s="327"/>
-      <c r="Y10" s="337"/>
-      <c r="Z10" s="337"/>
-      <c r="AA10" s="337"/>
-      <c r="AB10" s="337"/>
-      <c r="AC10" s="337"/>
-      <c r="AD10" s="337"/>
-      <c r="AE10" s="337"/>
-      <c r="AF10" s="337"/>
-      <c r="AG10" s="337"/>
-      <c r="AH10" s="337"/>
-      <c r="AI10" s="337"/>
-      <c r="AJ10" s="382"/>
-      <c r="AK10" s="334"/>
-      <c r="AL10" s="349"/>
-      <c r="AM10" s="337"/>
-      <c r="AN10" s="343"/>
-      <c r="AO10" s="343"/>
-      <c r="AP10" s="340"/>
-      <c r="AQ10" s="340"/>
-      <c r="AR10" s="340"/>
-      <c r="AS10" s="340"/>
-      <c r="AT10" s="340"/>
-      <c r="AU10" s="340"/>
-      <c r="AV10" s="343"/>
-      <c r="AW10" s="349"/>
-      <c r="AX10" s="343"/>
+      <c r="A10" s="378"/>
+      <c r="B10" s="381"/>
+      <c r="C10" s="330"/>
+      <c r="D10" s="384"/>
+      <c r="E10" s="384"/>
+      <c r="F10" s="330"/>
+      <c r="G10" s="387"/>
+      <c r="H10" s="355"/>
+      <c r="I10" s="355"/>
+      <c r="J10" s="387"/>
+      <c r="K10" s="363"/>
+      <c r="L10" s="363"/>
+      <c r="M10" s="363"/>
+      <c r="N10" s="363"/>
+      <c r="O10" s="363"/>
+      <c r="P10" s="363"/>
+      <c r="Q10" s="363"/>
+      <c r="R10" s="363"/>
+      <c r="S10" s="363"/>
+      <c r="T10" s="363"/>
+      <c r="U10" s="363"/>
+      <c r="V10" s="370"/>
+      <c r="W10" s="371"/>
+      <c r="X10" s="363"/>
+      <c r="Y10" s="366"/>
+      <c r="Z10" s="366"/>
+      <c r="AA10" s="366"/>
+      <c r="AB10" s="366"/>
+      <c r="AC10" s="366"/>
+      <c r="AD10" s="366"/>
+      <c r="AE10" s="366"/>
+      <c r="AF10" s="366"/>
+      <c r="AG10" s="366"/>
+      <c r="AH10" s="366"/>
+      <c r="AI10" s="366"/>
+      <c r="AJ10" s="373"/>
+      <c r="AK10" s="347"/>
+      <c r="AL10" s="398"/>
+      <c r="AM10" s="366"/>
+      <c r="AN10" s="330"/>
+      <c r="AO10" s="330"/>
+      <c r="AP10" s="387"/>
+      <c r="AQ10" s="387"/>
+      <c r="AR10" s="387"/>
+      <c r="AS10" s="387"/>
+      <c r="AT10" s="387"/>
+      <c r="AU10" s="387"/>
+      <c r="AV10" s="330"/>
+      <c r="AW10" s="398"/>
+      <c r="AX10" s="330"/>
       <c r="AY10" s="307" t="s">
         <v>68</v>
       </c>
@@ -8797,67 +8873,67 @@
       <c r="BA10" s="307" t="s">
         <v>70</v>
       </c>
-      <c r="BB10" s="399" t="s">
+      <c r="BB10" s="349" t="s">
         <v>71</v>
       </c>
-      <c r="BC10" s="329" t="s">
+      <c r="BC10" s="351" t="s">
         <v>72</v>
       </c>
-      <c r="BD10" s="329" t="s">
+      <c r="BD10" s="351" t="s">
         <v>73</v>
       </c>
-      <c r="BE10" s="331" t="s">
+      <c r="BE10" s="332" t="s">
         <v>74</v>
       </c>
-      <c r="BF10" s="331" t="s">
+      <c r="BF10" s="332" t="s">
         <v>75</v>
       </c>
-      <c r="BG10" s="331" t="s">
+      <c r="BG10" s="332" t="s">
         <v>76</v>
       </c>
-      <c r="BH10" s="329" t="s">
+      <c r="BH10" s="351" t="s">
         <v>77</v>
       </c>
-      <c r="BI10" s="329" t="s">
+      <c r="BI10" s="351" t="s">
         <v>78</v>
       </c>
-      <c r="BJ10" s="331" t="s">
+      <c r="BJ10" s="332" t="s">
         <v>79</v>
       </c>
-      <c r="BK10" s="331" t="s">
+      <c r="BK10" s="332" t="s">
         <v>80</v>
       </c>
-      <c r="BL10" s="342" t="s">
+      <c r="BL10" s="329" t="s">
         <v>81</v>
       </c>
-      <c r="BM10" s="329" t="s">
+      <c r="BM10" s="351" t="s">
         <v>82</v>
       </c>
-      <c r="BN10" s="348" t="s">
+      <c r="BN10" s="395" t="s">
         <v>83</v>
       </c>
-      <c r="BO10" s="329" t="s">
+      <c r="BO10" s="351" t="s">
         <v>84</v>
       </c>
-      <c r="BP10" s="348" t="s">
+      <c r="BP10" s="395" t="s">
         <v>85</v>
       </c>
-      <c r="BQ10" s="348" t="s">
+      <c r="BQ10" s="395" t="s">
         <v>86</v>
       </c>
-      <c r="BR10" s="343"/>
-      <c r="BS10" s="343"/>
-      <c r="BT10" s="343"/>
-      <c r="BU10" s="334"/>
+      <c r="BR10" s="330"/>
+      <c r="BS10" s="330"/>
+      <c r="BT10" s="330"/>
+      <c r="BU10" s="347"/>
       <c r="BV10" s="306"/>
-      <c r="BW10" s="389"/>
-      <c r="BX10" s="396"/>
-      <c r="BY10" s="397"/>
-      <c r="BZ10" s="397"/>
-      <c r="CA10" s="398"/>
-      <c r="CB10" s="386"/>
-      <c r="CC10" s="386"/>
-      <c r="CD10" s="386"/>
+      <c r="BW10" s="336"/>
+      <c r="BX10" s="343"/>
+      <c r="BY10" s="344"/>
+      <c r="BZ10" s="344"/>
+      <c r="CA10" s="345"/>
+      <c r="CB10" s="328"/>
+      <c r="CC10" s="328"/>
+      <c r="CD10" s="328"/>
       <c r="CE10" s="305" t="s">
         <v>3</v>
       </c>
@@ -8865,60 +8941,60 @@
       <c r="CI10" s="28"/>
     </row>
     <row r="11" spans="1:87" s="78" customFormat="1" ht="42">
-      <c r="A11" s="359"/>
-      <c r="B11" s="362"/>
-      <c r="C11" s="344"/>
-      <c r="D11" s="354"/>
-      <c r="E11" s="354"/>
-      <c r="F11" s="344"/>
-      <c r="G11" s="341"/>
-      <c r="H11" s="371"/>
-      <c r="I11" s="371"/>
-      <c r="J11" s="341"/>
-      <c r="K11" s="328"/>
-      <c r="L11" s="328"/>
-      <c r="M11" s="328"/>
-      <c r="N11" s="328"/>
-      <c r="O11" s="328"/>
-      <c r="P11" s="328"/>
-      <c r="Q11" s="328"/>
-      <c r="R11" s="328"/>
-      <c r="S11" s="328"/>
-      <c r="T11" s="328"/>
-      <c r="U11" s="328"/>
+      <c r="A11" s="379"/>
+      <c r="B11" s="382"/>
+      <c r="C11" s="331"/>
+      <c r="D11" s="385"/>
+      <c r="E11" s="385"/>
+      <c r="F11" s="331"/>
+      <c r="G11" s="388"/>
+      <c r="H11" s="356"/>
+      <c r="I11" s="356"/>
+      <c r="J11" s="388"/>
+      <c r="K11" s="364"/>
+      <c r="L11" s="364"/>
+      <c r="M11" s="364"/>
+      <c r="N11" s="364"/>
+      <c r="O11" s="364"/>
+      <c r="P11" s="364"/>
+      <c r="Q11" s="364"/>
+      <c r="R11" s="364"/>
+      <c r="S11" s="364"/>
+      <c r="T11" s="364"/>
+      <c r="U11" s="364"/>
       <c r="V11" s="308" t="s">
         <v>87</v>
       </c>
       <c r="W11" s="308" t="s">
         <v>88</v>
       </c>
-      <c r="X11" s="328"/>
-      <c r="Y11" s="338"/>
-      <c r="Z11" s="338"/>
-      <c r="AA11" s="338"/>
-      <c r="AB11" s="338"/>
-      <c r="AC11" s="338"/>
-      <c r="AD11" s="338"/>
-      <c r="AE11" s="338"/>
-      <c r="AF11" s="338"/>
-      <c r="AG11" s="338"/>
-      <c r="AH11" s="338"/>
-      <c r="AI11" s="338"/>
-      <c r="AJ11" s="383"/>
-      <c r="AK11" s="335"/>
-      <c r="AL11" s="350"/>
-      <c r="AM11" s="338"/>
-      <c r="AN11" s="344"/>
-      <c r="AO11" s="344"/>
-      <c r="AP11" s="341"/>
-      <c r="AQ11" s="341"/>
-      <c r="AR11" s="341"/>
-      <c r="AS11" s="341"/>
-      <c r="AT11" s="341"/>
-      <c r="AU11" s="341"/>
-      <c r="AV11" s="344"/>
-      <c r="AW11" s="350"/>
-      <c r="AX11" s="344"/>
+      <c r="X11" s="364"/>
+      <c r="Y11" s="367"/>
+      <c r="Z11" s="367"/>
+      <c r="AA11" s="367"/>
+      <c r="AB11" s="367"/>
+      <c r="AC11" s="367"/>
+      <c r="AD11" s="367"/>
+      <c r="AE11" s="367"/>
+      <c r="AF11" s="367"/>
+      <c r="AG11" s="367"/>
+      <c r="AH11" s="367"/>
+      <c r="AI11" s="367"/>
+      <c r="AJ11" s="374"/>
+      <c r="AK11" s="348"/>
+      <c r="AL11" s="396"/>
+      <c r="AM11" s="367"/>
+      <c r="AN11" s="331"/>
+      <c r="AO11" s="331"/>
+      <c r="AP11" s="388"/>
+      <c r="AQ11" s="388"/>
+      <c r="AR11" s="388"/>
+      <c r="AS11" s="388"/>
+      <c r="AT11" s="388"/>
+      <c r="AU11" s="388"/>
+      <c r="AV11" s="331"/>
+      <c r="AW11" s="396"/>
+      <c r="AX11" s="331"/>
       <c r="AY11" s="312" t="s">
         <v>89</v>
       </c>
@@ -8928,28 +9004,28 @@
       <c r="BA11" s="312" t="s">
         <v>91</v>
       </c>
-      <c r="BB11" s="400"/>
-      <c r="BC11" s="330"/>
-      <c r="BD11" s="330"/>
-      <c r="BE11" s="332"/>
-      <c r="BF11" s="332"/>
-      <c r="BG11" s="332"/>
-      <c r="BH11" s="330"/>
-      <c r="BI11" s="330"/>
-      <c r="BJ11" s="332"/>
-      <c r="BK11" s="332"/>
-      <c r="BL11" s="344"/>
-      <c r="BM11" s="330"/>
-      <c r="BN11" s="350"/>
-      <c r="BO11" s="330"/>
-      <c r="BP11" s="350"/>
-      <c r="BQ11" s="350"/>
-      <c r="BR11" s="344"/>
-      <c r="BS11" s="344"/>
-      <c r="BT11" s="344"/>
-      <c r="BU11" s="335"/>
+      <c r="BB11" s="350"/>
+      <c r="BC11" s="352"/>
+      <c r="BD11" s="352"/>
+      <c r="BE11" s="333"/>
+      <c r="BF11" s="333"/>
+      <c r="BG11" s="333"/>
+      <c r="BH11" s="352"/>
+      <c r="BI11" s="352"/>
+      <c r="BJ11" s="333"/>
+      <c r="BK11" s="333"/>
+      <c r="BL11" s="331"/>
+      <c r="BM11" s="352"/>
+      <c r="BN11" s="396"/>
+      <c r="BO11" s="352"/>
+      <c r="BP11" s="396"/>
+      <c r="BQ11" s="396"/>
+      <c r="BR11" s="331"/>
+      <c r="BS11" s="331"/>
+      <c r="BT11" s="331"/>
+      <c r="BU11" s="348"/>
       <c r="BV11" s="306"/>
-      <c r="BW11" s="389"/>
+      <c r="BW11" s="336"/>
       <c r="BX11" s="310" t="s">
         <v>92</v>
       </c>
@@ -8962,9 +9038,9 @@
       <c r="CA11" s="309" t="s">
         <v>95</v>
       </c>
-      <c r="CB11" s="386"/>
-      <c r="CC11" s="386"/>
-      <c r="CD11" s="386"/>
+      <c r="CB11" s="328"/>
+      <c r="CC11" s="328"/>
+      <c r="CD11" s="328"/>
       <c r="CE11" s="311">
         <v>26</v>
       </c>
@@ -8989,7 +9065,7 @@
       </c>
       <c r="I12" s="91">
         <f t="shared" si="0"/>
-        <v>179340000</v>
+        <v>182340000</v>
       </c>
       <c r="J12" s="91"/>
       <c r="K12" s="288">
@@ -9094,12 +9170,12 @@
         <v>0</v>
       </c>
       <c r="AN12" s="91">
-        <f t="shared" ref="AN12:BT12" si="2">SUM(AN13:AN19)</f>
+        <f t="shared" ref="AN12:BQ12" si="2">SUM(AN13:AN19)</f>
         <v>3650769.230769231</v>
       </c>
       <c r="AO12" s="91">
         <f t="shared" si="2"/>
-        <v>178705384.61538464</v>
+        <v>181705384.61538464</v>
       </c>
       <c r="AP12" s="91"/>
       <c r="AQ12" s="91"/>
@@ -9109,7 +9185,7 @@
       <c r="AU12" s="91"/>
       <c r="AV12" s="91">
         <f t="shared" si="2"/>
-        <v>239266923.07692307</v>
+        <v>242266923.07692307</v>
       </c>
       <c r="AW12" s="91"/>
       <c r="AX12" s="91"/>
@@ -9146,7 +9222,7 @@
       <c r="BK12" s="91"/>
       <c r="BL12" s="91">
         <f t="shared" si="2"/>
-        <v>20400380</v>
+        <v>14719781</v>
       </c>
       <c r="BM12" s="91">
         <f t="shared" si="2"/>
@@ -9173,7 +9249,7 @@
       <c r="BT12" s="91"/>
       <c r="BU12" s="289">
         <f t="shared" ref="BU12" si="3">SUM(BU13:BU19)</f>
-        <v>213402943.07692307</v>
+        <v>222083542.07692307</v>
       </c>
       <c r="BV12" s="235"/>
       <c r="BW12" s="108"/>
@@ -9187,7 +9263,6 @@
     </row>
     <row r="13" spans="1:87" s="99" customFormat="1" ht="30.5" customHeight="1">
       <c r="A13" s="313">
-        <f>IF(B13=0,"",COUNTA($B$13:(B13)))</f>
         <v>1</v>
       </c>
       <c r="B13" s="314">
@@ -9214,7 +9289,7 @@
       </c>
       <c r="I13" s="318">
         <f>CB13-BZ13-G13-H13</f>
-        <v>49700000</v>
+        <v>52700000</v>
       </c>
       <c r="J13" s="319">
         <v>1</v>
@@ -9319,7 +9394,7 @@
       </c>
       <c r="AO13" s="318">
         <f t="shared" ref="AO13:AO19" si="9">IF(F13="LN",I13*(K13+L13)/26+(H13+I13)*50%*M13/26+MAX($G13*P13/26*150%,P13*$BW13/26)-AC13+MAX($G13*Q13/26*200%,Q13*$BW13/26)-AD13+MAX($G13*R13/26*300%,R13*$BW13/26)-AE13+BW13*S13/26-AF13+AH13-AG13,I13-I13*($CE$11-K13-L13)/26+(H13+I13)*50%*M13/26+BW13*O13/26-AB13+MAX($G13*P13/26*150%,P13*$BW13/26)-AC13+MAX($G13*Q13/26*200%,Q13*$BW13/26)-AD13+MAX($G13*R13/26*300%,R13*$BW13/26)-AE13+BW13*S13/26-AF13+AH13-AG13+(G13-G13*($CE$11-K13-L13)/26-Y13)+(H13-H13*($CE$11-K13-L13)/26-AN13))</f>
-        <v>49700000</v>
+        <v>52700000</v>
       </c>
       <c r="AP13" s="318"/>
       <c r="AQ13" s="318"/>
@@ -9331,11 +9406,12 @@
       <c r="AU13" s="318"/>
       <c r="AV13" s="318">
         <f>Y13+Z13+AA13+AB13+AC13+AD13+AE13+AF13+AG13+AI13+AJ13+AK13+AL13+AM13+AN13+AO13+AP13-AQ13+AR13+AS13+AT13+AU13</f>
-        <v>61000000</v>
+        <v>64000000</v>
       </c>
       <c r="AW13" s="318"/>
-      <c r="AX13" s="318" t="s">
-        <v>102</v>
+      <c r="AX13" s="318" t="str">
+        <f t="shared" ref="AX13:AX19" si="10">IF(E13="CT","x",0)</f>
+        <v>x</v>
       </c>
       <c r="AY13" s="321">
         <f>ROUND(IF($AX13="x",($G13+$H13)*AY$11,0),0)</f>
@@ -9346,7 +9422,7 @@
         <v>154500</v>
       </c>
       <c r="BA13" s="321">
-        <f t="shared" ref="BA13" si="10">ROUND(IF($AX13="x",($G13+$H13)*BA$11,0),0)</f>
+        <f t="shared" ref="BA13" si="11">ROUND(IF($AX13="x",($G13+$H13)*BA$11,0),0)</f>
         <v>103000</v>
       </c>
       <c r="BB13" s="321">
@@ -9360,12 +9436,12 @@
         <v>95200</v>
       </c>
       <c r="BF13" s="321">
-        <f>AM13+IF(E13="CT",IF(AR13&gt;=730000,730000,AR13),0)+IF(((AV13-AM13-IF(AR13&gt;=730000,730000,AR13)-AS13)*15%-AS13)&gt;"0",((AV13-AM13-IF(AR13&gt;=730000,730000,AR13)-AS13)*15%-AS13),0)</f>
-        <v>730000</v>
+        <f>AM13+IF(E13="CT",IF(AR13&gt;=730000,730000,AR13),0)+IF(((AV13-AM13-IF(AR13&gt;=730000,730000,AR13)-AS13)*15%-AS13)&gt;0,((AV13-AM13-IF(AR13&gt;=730000,730000,AR13)-AS13)*15%-AS13),0)</f>
+        <v>10220500</v>
       </c>
       <c r="BG13" s="321">
         <f>AV13-BF13+AW13</f>
-        <v>60270000</v>
+        <v>53779500</v>
       </c>
       <c r="BH13" s="321">
         <v>3</v>
@@ -9374,16 +9450,16 @@
         <v>4400000</v>
       </c>
       <c r="BJ13" s="321">
-        <f t="shared" ref="BJ13:BJ19" si="11">IF(E13="CT",11000000,0)</f>
+        <f t="shared" ref="BJ13:BJ19" si="12">IF(E13="CT",11000000,0)</f>
         <v>11000000</v>
       </c>
       <c r="BK13" s="321">
         <f>BG13-BB13-BC13+BD13-BH13*BI13-BJ13</f>
-        <v>34988500</v>
+        <v>28498000</v>
       </c>
       <c r="BL13" s="322">
         <f>IF(E13="TV",BK13*10%,IF(BK13&gt;0,ROUND(IF(BK13&gt;=80000000,BK13*35%-9850000,IF(BK13&gt;=52000000,BK13*30%-5850000,IF(BK13&gt;=32000000,BK13*25%-3250000,IF(BK13&gt;=18000000,BK13*20%-1650000,IF(BK13&gt;=10000000,BK13*15%-750000,IF(BK13&gt;5000000,BK13*10%-250000,BK13*5%)))))),0),0))</f>
-        <v>5497125</v>
+        <v>4049600</v>
       </c>
       <c r="BM13" s="321"/>
       <c r="BN13" s="321"/>
@@ -9397,7 +9473,7 @@
       <c r="BT13" s="321"/>
       <c r="BU13" s="323">
         <f>AV13-BB13-BC13+BD13-BE13-BL13-BM13-BN13-BO13-BP13-BQ13-BR13+BS13-BT13</f>
-        <v>54326175</v>
+        <v>58773700</v>
       </c>
       <c r="BV13" s="324"/>
       <c r="BW13" s="325">
@@ -9411,11 +9487,12 @@
         <v>200000</v>
       </c>
       <c r="CA13" s="322">
-        <v>0</v>
+        <f t="shared" ref="CA13:CA19" si="13">+BW13*5%</f>
+        <v>3000000</v>
       </c>
       <c r="CB13" s="322">
         <f>SUM(BW13:CA13)</f>
-        <v>60200000</v>
+        <v>63200000</v>
       </c>
       <c r="CC13" s="322" t="s">
         <v>123</v>
@@ -9429,7 +9506,6 @@
     </row>
     <row r="14" spans="1:87" s="99" customFormat="1" ht="30.5" customHeight="1">
       <c r="A14" s="87">
-        <f>IF(B14=0,"",COUNTA($B$13:(B14)))</f>
         <v>2</v>
       </c>
       <c r="B14" s="88">
@@ -9455,7 +9531,7 @@
         <v>780000</v>
       </c>
       <c r="I14" s="91">
-        <f t="shared" ref="I14:I19" si="12">CB14-BZ14-G14-H14</f>
+        <f t="shared" ref="I14:I19" si="14">CB14-BZ14-G14-H14</f>
         <v>42740000</v>
       </c>
       <c r="J14" s="239">
@@ -9506,27 +9582,27 @@
         <v>7827692.307692308</v>
       </c>
       <c r="Z14" s="91">
-        <f t="shared" ref="Z14:Z15" si="13">M14*G14/26</f>
+        <f t="shared" ref="Z14:Z15" si="15">M14*G14/26</f>
         <v>0</v>
       </c>
       <c r="AA14" s="91">
-        <f t="shared" ref="AA14:AA15" si="14">G14*N14/26</f>
+        <f t="shared" ref="AA14:AA15" si="16">G14*N14/26</f>
         <v>0</v>
       </c>
       <c r="AB14" s="91">
-        <f t="shared" ref="AB14:AB15" si="15">G14*O14/26</f>
+        <f t="shared" ref="AB14:AB15" si="17">G14*O14/26</f>
         <v>0</v>
       </c>
       <c r="AC14" s="91">
-        <f t="shared" ref="AC14:AC15" si="16">G14*P14*150%/26</f>
+        <f t="shared" ref="AC14:AC15" si="18">G14*P14*150%/26</f>
         <v>0</v>
       </c>
       <c r="AD14" s="91">
-        <f t="shared" ref="AD14:AD15" si="17">G14*Q14/26*200%</f>
+        <f t="shared" ref="AD14:AD15" si="19">G14*Q14/26*200%</f>
         <v>0</v>
       </c>
       <c r="AE14" s="91">
-        <f t="shared" ref="AE14:AE15" si="18">G14*R14/26*300%</f>
+        <f t="shared" ref="AE14:AE15" si="20">G14*R14/26*300%</f>
         <v>0</v>
       </c>
       <c r="AF14" s="91">
@@ -9534,7 +9610,7 @@
         <v>0</v>
       </c>
       <c r="AG14" s="91">
-        <f t="shared" ref="AG14:AG15" si="19">T14*G14/26/8</f>
+        <f t="shared" ref="AG14:AG15" si="21">T14*G14/26/8</f>
         <v>0</v>
       </c>
       <c r="AH14" s="91">
@@ -9542,7 +9618,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="91">
-        <f t="shared" ref="AI14:AI15" si="20">G14*V14/26</f>
+        <f t="shared" ref="AI14:AI15" si="22">G14*V14/26</f>
         <v>0</v>
       </c>
       <c r="AJ14" s="91"/>
@@ -9556,7 +9632,7 @@
         <v>0</v>
       </c>
       <c r="AN14" s="91">
-        <f t="shared" ref="AN14:AN15" si="21">H14/26*K14</f>
+        <f t="shared" ref="AN14:AN15" si="23">H14/26*K14</f>
         <v>570000</v>
       </c>
       <c r="AO14" s="91">
@@ -9572,16 +9648,16 @@
       <c r="AT14" s="91"/>
       <c r="AU14" s="91"/>
       <c r="AV14" s="91">
-        <f t="shared" ref="AV14:AV15" si="22">Y14+Z14+AA14+AB14+AC14+AD14+AE14+AF14+AG14+AI14+AJ14+AK14+AL14+AM14+AN14+AO14+AP14-AQ14+AR14+AS14+AT14+AU14</f>
+        <f t="shared" ref="AV14:AV15" si="24">Y14+Z14+AA14+AB14+AC14+AD14+AE14+AF14+AG14+AI14+AJ14+AK14+AL14+AM14+AN14+AO14+AP14-AQ14+AR14+AS14+AT14+AU14</f>
         <v>48758461.538461544</v>
       </c>
       <c r="AW14" s="91"/>
       <c r="AX14" s="91" t="str">
-        <f t="shared" ref="AX14:AX19" si="23">IF(E14="CT","x",0)</f>
+        <f t="shared" si="10"/>
         <v>x</v>
       </c>
       <c r="AY14" s="85">
-        <f t="shared" ref="AY14:AZ19" si="24">ROUND(IF($AX14="x",($G14+$H14)*AY$11,0),0)</f>
+        <f t="shared" ref="AY14:AZ19" si="25">ROUND(IF($AX14="x",($G14+$H14)*AY$11,0),0)</f>
         <v>740800</v>
       </c>
       <c r="AZ14" s="85">
@@ -9599,32 +9675,32 @@
       <c r="BC14" s="85"/>
       <c r="BD14" s="85"/>
       <c r="BE14" s="85">
-        <f t="shared" ref="BE14:BE15" si="25">IF(G14*1%&gt;=234000,234000,G14*1%)</f>
+        <f t="shared" ref="BE14:BE15" si="26">IF(G14*1%&gt;=234000,234000,G14*1%)</f>
         <v>84800</v>
       </c>
       <c r="BF14" s="85">
-        <f t="shared" ref="BF14:BF15" si="26">AM14+IF(E14="CT",IF(AR14&gt;=730000,730000,AR14),0)+IF(((AV14-AM14-IF(AR14&gt;=730000,730000,AR14)-AS14)*15%-AS14)&gt;"0",((AV14-AM14-IF(AR14&gt;=730000,730000,AR14)-AS14)*15%-AS14),0)</f>
-        <v>720000</v>
+        <f t="shared" ref="BF14:BF19" si="27">AM14+IF(E14="CT",IF(AR14&gt;=730000,730000,AR14),0)+IF(((AV14-AM14-IF(AR14&gt;=730000,730000,AR14)-AS14)*15%-AS14)&gt;0,((AV14-AM14-IF(AR14&gt;=730000,730000,AR14)-AS14)*15%-AS14),0)</f>
+        <v>7925769.230769231</v>
       </c>
       <c r="BG14" s="85">
-        <f t="shared" ref="BG14:BG15" si="27">AV14-BF14+AW14</f>
-        <v>48038461.538461544</v>
+        <f t="shared" ref="BG14:BG15" si="28">AV14-BF14+AW14</f>
+        <v>40832692.307692312</v>
       </c>
       <c r="BH14" s="85"/>
       <c r="BI14" s="85">
         <v>4400000</v>
       </c>
       <c r="BJ14" s="85">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11000000</v>
       </c>
       <c r="BK14" s="85">
-        <f t="shared" ref="BK14:BK15" si="28">BG14-BB14-BC14+BD14-BH14*BI14-BJ14</f>
-        <v>36066161.538461544</v>
+        <f t="shared" ref="BK14:BK15" si="29">BG14-BB14-BC14+BD14-BH14*BI14-BJ14</f>
+        <v>28860392.307692312</v>
       </c>
       <c r="BL14" s="84">
-        <f t="shared" ref="BL14:BL15" si="29">IF(E14="TV",BK14*10%,IF(BK14&gt;0,ROUND(IF(BK14&gt;=80000000,BK14*35%-9850000,IF(BK14&gt;=52000000,BK14*30%-5850000,IF(BK14&gt;=32000000,BK14*25%-3250000,IF(BK14&gt;=18000000,BK14*20%-1650000,IF(BK14&gt;=10000000,BK14*15%-750000,IF(BK14&gt;5000000,BK14*10%-250000,BK14*5%)))))),0),0))</f>
-        <v>5766540</v>
+        <f t="shared" ref="BL14:BL15" si="30">IF(E14="TV",BK14*10%,IF(BK14&gt;0,ROUND(IF(BK14&gt;=80000000,BK14*35%-9850000,IF(BK14&gt;=52000000,BK14*30%-5850000,IF(BK14&gt;=32000000,BK14*25%-3250000,IF(BK14&gt;=18000000,BK14*20%-1650000,IF(BK14&gt;=10000000,BK14*15%-750000,IF(BK14&gt;5000000,BK14*10%-250000,BK14*5%)))))),0),0))</f>
+        <v>4122078</v>
       </c>
       <c r="BM14" s="85"/>
       <c r="BN14" s="85"/>
@@ -9637,8 +9713,8 @@
       <c r="BS14" s="85"/>
       <c r="BT14" s="85"/>
       <c r="BU14" s="105">
-        <f t="shared" ref="BU14:BU15" si="30">AV14-BB14-BC14+BD14-BE14-BL14-BM14-BN14-BO14-BP14-BQ14-BR14+BS14-BT14</f>
-        <v>41934821.538461544</v>
+        <f t="shared" ref="BU14:BU15" si="31">AV14-BB14-BC14+BD14-BE14-BL14-BM14-BN14-BO14-BP14-BQ14-BR14+BS14-BT14</f>
+        <v>43579283.538461544</v>
       </c>
       <c r="BV14" s="235"/>
       <c r="BW14" s="108">
@@ -9654,7 +9730,7 @@
         <v>200000</v>
       </c>
       <c r="CA14" s="84">
-        <f t="shared" ref="CA14:CA19" si="31">+BW14*5%</f>
+        <f t="shared" si="13"/>
         <v>2000000</v>
       </c>
       <c r="CB14" s="84">
@@ -9673,7 +9749,6 @@
     </row>
     <row r="15" spans="1:87" s="99" customFormat="1" ht="30.5" customHeight="1">
       <c r="A15" s="87">
-        <f>IF(B15=0,"",COUNTA($B$13:(B15)))</f>
         <v>3</v>
       </c>
       <c r="B15" s="100" t="s">
@@ -9699,7 +9774,7 @@
         <v>300000</v>
       </c>
       <c r="I15" s="91">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>33880000</v>
       </c>
       <c r="J15" s="239">
@@ -9750,27 +9825,27 @@
         <v>7218461.538461538</v>
       </c>
       <c r="Z15" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AA15" s="91">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AB15" s="91">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC15" s="91">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AD15" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AE15" s="91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF15" s="91">
@@ -9778,7 +9853,7 @@
         <v>0</v>
       </c>
       <c r="AG15" s="91">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AH15" s="91">
@@ -9786,7 +9861,7 @@
         <v>3246153.846153846</v>
       </c>
       <c r="AI15" s="91">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AJ15" s="91"/>
@@ -9800,7 +9875,7 @@
         <v>0</v>
       </c>
       <c r="AN15" s="91">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>276923.07692307694</v>
       </c>
       <c r="AO15" s="91">
@@ -9816,20 +9891,20 @@
       <c r="AT15" s="91"/>
       <c r="AU15" s="91"/>
       <c r="AV15" s="91">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>42575384.615384616</v>
       </c>
       <c r="AW15" s="91"/>
       <c r="AX15" s="91" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="10"/>
         <v>x</v>
       </c>
       <c r="AY15" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>649600</v>
       </c>
       <c r="AZ15" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>121800</v>
       </c>
       <c r="BA15" s="85">
@@ -9843,32 +9918,32 @@
       <c r="BC15" s="85"/>
       <c r="BD15" s="85"/>
       <c r="BE15" s="85">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>78200</v>
       </c>
       <c r="BF15" s="85">
-        <f t="shared" si="26"/>
-        <v>560000</v>
+        <f t="shared" si="27"/>
+        <v>6862307.692307692</v>
       </c>
       <c r="BG15" s="85">
-        <f t="shared" si="27"/>
-        <v>42015384.615384616</v>
+        <f t="shared" si="28"/>
+        <v>35713076.923076928</v>
       </c>
       <c r="BH15" s="85"/>
       <c r="BI15" s="85">
         <v>4400000</v>
       </c>
       <c r="BJ15" s="85">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11000000</v>
       </c>
       <c r="BK15" s="85">
-        <f t="shared" si="28"/>
-        <v>30162784.615384616</v>
+        <f t="shared" si="29"/>
+        <v>23860476.923076928</v>
       </c>
       <c r="BL15" s="84">
-        <f t="shared" si="29"/>
-        <v>4382557</v>
+        <f t="shared" si="30"/>
+        <v>3122095</v>
       </c>
       <c r="BM15" s="85"/>
       <c r="BN15" s="85"/>
@@ -9881,8 +9956,8 @@
       <c r="BS15" s="85"/>
       <c r="BT15" s="85"/>
       <c r="BU15" s="105">
-        <f t="shared" si="30"/>
-        <v>37262027.615384616</v>
+        <f t="shared" si="31"/>
+        <v>38522489.615384616</v>
       </c>
       <c r="BV15" s="235"/>
       <c r="BW15" s="108">
@@ -9898,7 +9973,7 @@
         <v>200000</v>
       </c>
       <c r="CA15" s="84">
-        <f t="shared" si="31"/>
+        <f t="shared" si="13"/>
         <v>2000000</v>
       </c>
       <c r="CB15" s="84">
@@ -9917,7 +9992,6 @@
     </row>
     <row r="16" spans="1:87" s="99" customFormat="1" ht="30.5" customHeight="1">
       <c r="A16" s="87">
-        <f>IF(B16=0,"",COUNTA($B$13:(B16)))</f>
         <v>4</v>
       </c>
       <c r="B16" s="88">
@@ -9943,7 +10017,7 @@
         <v>780000</v>
       </c>
       <c r="I16" s="91">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>18380000</v>
       </c>
       <c r="J16" s="239">
@@ -10065,11 +10139,11 @@
       </c>
       <c r="AW16" s="91"/>
       <c r="AX16" s="91" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="10"/>
         <v>x</v>
       </c>
       <c r="AY16" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>621600</v>
       </c>
       <c r="AZ16" s="85">
@@ -10091,28 +10165,28 @@
         <v>69900</v>
       </c>
       <c r="BF16" s="85">
-        <f t="shared" ref="BF16:BF17" si="45">AM16+IF(E16="CT",IF(AR16&gt;=730000,730000,AR16),0)+IF(((AV16-AM16-IF(AR16&gt;=730000,730000,AR16)-AS16)*15%-AS16)&gt;"0",((AV16-AM16-IF(AR16&gt;=730000,730000,AR16)-AS16)*15%-AS16),0)</f>
-        <v>720000</v>
+        <f t="shared" si="27"/>
+        <v>4645961.538461538</v>
       </c>
       <c r="BG16" s="85">
-        <f t="shared" ref="BG16:BG17" si="46">AV16-BF16+AW16</f>
-        <v>26173076.923076924</v>
+        <f t="shared" ref="BG16:BG17" si="45">AV16-BF16+AW16</f>
+        <v>22247115.384615384</v>
       </c>
       <c r="BH16" s="85"/>
       <c r="BI16" s="85">
         <v>4400000</v>
       </c>
       <c r="BJ16" s="85">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11000000</v>
       </c>
       <c r="BK16" s="85">
-        <f t="shared" ref="BK16:BK17" si="47">BG16-BB16-BC16+BD16-BH16*BI16-BJ16</f>
-        <v>14357226.923076924</v>
+        <f t="shared" ref="BK16:BK17" si="46">BG16-BB16-BC16+BD16-BH16*BI16-BJ16</f>
+        <v>10431265.384615384</v>
       </c>
       <c r="BL16" s="84">
-        <f t="shared" ref="BL16:BL17" si="48">IF(E16="TV",BK16*10%,IF(BK16&gt;0,ROUND(IF(BK16&gt;=80000000,BK16*35%-9850000,IF(BK16&gt;=52000000,BK16*30%-5850000,IF(BK16&gt;=32000000,BK16*25%-3250000,IF(BK16&gt;=18000000,BK16*20%-1650000,IF(BK16&gt;=10000000,BK16*15%-750000,IF(BK16&gt;5000000,BK16*10%-250000,BK16*5%)))))),0),0))</f>
-        <v>1403584</v>
+        <f t="shared" ref="BL16:BL17" si="47">IF(E16="TV",BK16*10%,IF(BK16&gt;0,ROUND(IF(BK16&gt;=80000000,BK16*35%-9850000,IF(BK16&gt;=52000000,BK16*30%-5850000,IF(BK16&gt;=32000000,BK16*25%-3250000,IF(BK16&gt;=18000000,BK16*20%-1650000,IF(BK16&gt;=10000000,BK16*15%-750000,IF(BK16&gt;5000000,BK16*10%-250000,BK16*5%)))))),0),0))</f>
+        <v>814690</v>
       </c>
       <c r="BM16" s="85"/>
       <c r="BN16" s="85"/>
@@ -10125,8 +10199,8 @@
       <c r="BS16" s="85"/>
       <c r="BT16" s="85"/>
       <c r="BU16" s="105">
-        <f t="shared" ref="BU16:BU17" si="49">AV16-BB16-BC16+BD16-BE16-BL16-BM16-BN16-BO16-BP16-BQ16-BR16+BS16-BT16</f>
-        <v>24603742.923076924</v>
+        <f t="shared" ref="BU16:BU17" si="48">AV16-BB16-BC16+BD16-BE16-BL16-BM16-BN16-BO16-BP16-BQ16-BR16+BS16-BT16</f>
+        <v>25192636.923076924</v>
       </c>
       <c r="BV16" s="235"/>
       <c r="BW16" s="108">
@@ -10142,11 +10216,11 @@
         <v>200000</v>
       </c>
       <c r="CA16" s="84">
-        <f t="shared" si="31"/>
+        <f t="shared" si="13"/>
         <v>1150000</v>
       </c>
       <c r="CB16" s="84">
-        <f t="shared" ref="CB16:CB17" si="50">SUM(BW16:CA16)</f>
+        <f t="shared" ref="CB16:CB17" si="49">SUM(BW16:CA16)</f>
         <v>26350000</v>
       </c>
       <c r="CC16" s="84" t="s">
@@ -10161,7 +10235,6 @@
     </row>
     <row r="17" spans="1:87" s="99" customFormat="1" ht="30.5" customHeight="1">
       <c r="A17" s="87">
-        <f>IF(B17=0,"",COUNTA($B$13:(B17)))</f>
         <v>5</v>
       </c>
       <c r="B17" s="100" t="s">
@@ -10187,7 +10260,7 @@
         <v>300000</v>
       </c>
       <c r="I17" s="91">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>6400000</v>
       </c>
       <c r="J17" s="239">
@@ -10309,15 +10382,15 @@
       </c>
       <c r="AW17" s="91"/>
       <c r="AX17" s="91" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="10"/>
         <v>x</v>
       </c>
       <c r="AY17" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>412000</v>
       </c>
       <c r="AZ17" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>77250</v>
       </c>
       <c r="BA17" s="85">
@@ -10325,7 +10398,7 @@
         <v>51500</v>
       </c>
       <c r="BB17" s="85">
-        <f t="shared" ref="BB17" si="51">SUM(AY17:BA17)</f>
+        <f t="shared" ref="BB17" si="50">SUM(AY17:BA17)</f>
         <v>540750</v>
       </c>
       <c r="BC17" s="85"/>
@@ -10335,28 +10408,28 @@
         <v>48500</v>
       </c>
       <c r="BF17" s="85">
+        <f t="shared" si="27"/>
+        <v>2303461.5384615385</v>
+      </c>
+      <c r="BG17" s="85">
         <f t="shared" si="45"/>
-        <v>560000</v>
-      </c>
-      <c r="BG17" s="85">
-        <f t="shared" si="46"/>
-        <v>11623076.923076924</v>
+        <v>9879615.3846153859</v>
       </c>
       <c r="BH17" s="85"/>
       <c r="BI17" s="85">
         <v>4400000</v>
       </c>
       <c r="BJ17" s="85">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11000000</v>
       </c>
       <c r="BK17" s="85">
+        <f t="shared" si="46"/>
+        <v>-1661134.6153846141</v>
+      </c>
+      <c r="BL17" s="84">
         <f t="shared" si="47"/>
-        <v>82326.923076923937</v>
-      </c>
-      <c r="BL17" s="84">
-        <f t="shared" si="48"/>
-        <v>4116</v>
+        <v>0</v>
       </c>
       <c r="BM17" s="85"/>
       <c r="BN17" s="85"/>
@@ -10369,8 +10442,8 @@
       <c r="BS17" s="85"/>
       <c r="BT17" s="85"/>
       <c r="BU17" s="105">
-        <f t="shared" si="49"/>
-        <v>11589710.923076924</v>
+        <f t="shared" si="48"/>
+        <v>11593826.923076924</v>
       </c>
       <c r="BV17" s="235"/>
       <c r="BW17" s="108">
@@ -10386,11 +10459,11 @@
         <v>200000</v>
       </c>
       <c r="CA17" s="84">
-        <f t="shared" si="31"/>
+        <f t="shared" si="13"/>
         <v>550000</v>
       </c>
       <c r="CB17" s="84">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>11750000</v>
       </c>
       <c r="CC17" s="84" t="s">
@@ -10405,7 +10478,6 @@
     </row>
     <row r="18" spans="1:87" s="99" customFormat="1" ht="30.5" customHeight="1">
       <c r="A18" s="87">
-        <f>IF(B18=0,"",COUNTA($B$13:(B18)))</f>
         <v>6</v>
       </c>
       <c r="B18" s="88">
@@ -10431,7 +10503,7 @@
         <v>780000</v>
       </c>
       <c r="I18" s="91">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>17030000</v>
       </c>
       <c r="J18" s="239">
@@ -10482,27 +10554,27 @@
         <v>6340000</v>
       </c>
       <c r="Z18" s="91">
-        <f t="shared" ref="Z18:Z19" si="52">M18*G18/26</f>
+        <f t="shared" ref="Z18:Z19" si="51">M18*G18/26</f>
         <v>0</v>
       </c>
       <c r="AA18" s="91">
-        <f t="shared" ref="AA18:AA19" si="53">G18*N18/26</f>
+        <f t="shared" ref="AA18:AA19" si="52">G18*N18/26</f>
         <v>0</v>
       </c>
       <c r="AB18" s="91">
-        <f t="shared" ref="AB18:AB19" si="54">G18*O18/26</f>
+        <f t="shared" ref="AB18:AB19" si="53">G18*O18/26</f>
         <v>0</v>
       </c>
       <c r="AC18" s="91">
-        <f t="shared" ref="AC18:AC19" si="55">G18*P18*150%/26</f>
+        <f t="shared" ref="AC18:AC19" si="54">G18*P18*150%/26</f>
         <v>0</v>
       </c>
       <c r="AD18" s="91">
-        <f t="shared" ref="AD18:AD19" si="56">G18*Q18/26*200%</f>
+        <f t="shared" ref="AD18:AD19" si="55">G18*Q18/26*200%</f>
         <v>0</v>
       </c>
       <c r="AE18" s="91">
-        <f t="shared" ref="AE18:AE19" si="57">G18*R18/26*300%</f>
+        <f t="shared" ref="AE18:AE19" si="56">G18*R18/26*300%</f>
         <v>0</v>
       </c>
       <c r="AF18" s="91">
@@ -10510,7 +10582,7 @@
         <v>0</v>
       </c>
       <c r="AG18" s="91">
-        <f t="shared" ref="AG18:AG19" si="58">T18*G18/26/8</f>
+        <f t="shared" ref="AG18:AG19" si="57">T18*G18/26/8</f>
         <v>0</v>
       </c>
       <c r="AH18" s="91">
@@ -10518,7 +10590,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="91">
-        <f t="shared" ref="AI18:AI19" si="59">G18*V18/26</f>
+        <f t="shared" ref="AI18:AI19" si="58">G18*V18/26</f>
         <v>0</v>
       </c>
       <c r="AJ18" s="91"/>
@@ -10532,7 +10604,7 @@
         <v>0</v>
       </c>
       <c r="AN18" s="91">
-        <f t="shared" ref="AN18:AN19" si="60">H18/26*K18</f>
+        <f t="shared" ref="AN18:AN19" si="59">H18/26*K18</f>
         <v>780000</v>
       </c>
       <c r="AO18" s="91">
@@ -10548,16 +10620,16 @@
       <c r="AT18" s="91"/>
       <c r="AU18" s="91"/>
       <c r="AV18" s="91">
-        <f t="shared" ref="AV18:AV19" si="61">Y18+Z18+AA18+AB18+AC18+AD18+AE18+AF18+AG18+AI18+AJ18+AK18+AL18+AM18+AN18+AO18+AP18-AQ18+AR18+AS18+AT18+AU18</f>
+        <f t="shared" ref="AV18:AV19" si="60">Y18+Z18+AA18+AB18+AC18+AD18+AE18+AF18+AG18+AI18+AJ18+AK18+AL18+AM18+AN18+AO18+AP18-AQ18+AR18+AS18+AT18+AU18</f>
         <v>24870000</v>
       </c>
       <c r="AW18" s="91"/>
       <c r="AX18" s="91">
-        <f t="shared" si="23"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY18" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AZ18" s="85">
@@ -10575,32 +10647,32 @@
       <c r="BC18" s="85"/>
       <c r="BD18" s="85"/>
       <c r="BE18" s="85">
-        <f t="shared" ref="BE18:BE19" si="62">IF(G18*1%&gt;=234000,234000,G18*1%)</f>
+        <f t="shared" ref="BE18:BE19" si="61">IF(G18*1%&gt;=234000,234000,G18*1%)</f>
         <v>63400</v>
       </c>
       <c r="BF18" s="85">
-        <f t="shared" ref="BF18:BF19" si="63">AM18+IF(E18="CT",IF(AR18&gt;=730000,730000,AR18),0)+IF(((AV18-AM18-IF(AR18&gt;=730000,730000,AR18)-AS18)*15%-AS18)&gt;"0",((AV18-AM18-IF(AR18&gt;=730000,730000,AR18)-AS18)*15%-AS18),0)</f>
-        <v>0</v>
+        <f t="shared" si="27"/>
+        <v>3622500</v>
       </c>
       <c r="BG18" s="85">
-        <f t="shared" ref="BG18:BG19" si="64">AV18-BF18+AW18</f>
-        <v>24870000</v>
+        <f t="shared" ref="BG18:BG19" si="62">AV18-BF18+AW18</f>
+        <v>21247500</v>
       </c>
       <c r="BH18" s="85"/>
       <c r="BI18" s="85">
         <v>4400000</v>
       </c>
       <c r="BJ18" s="85">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BK18" s="85">
-        <f t="shared" ref="BK18:BK19" si="65">BG18-BB18-BC18+BD18-BH18*BI18-BJ18</f>
-        <v>24870000</v>
+        <f t="shared" ref="BK18:BK19" si="63">BG18-BB18-BC18+BD18-BH18*BI18-BJ18</f>
+        <v>21247500</v>
       </c>
       <c r="BL18" s="84">
-        <f t="shared" ref="BL18:BL19" si="66">IF(E18="TV",BK18*10%,IF(BK18&gt;0,ROUND(IF(BK18&gt;=80000000,BK18*35%-9850000,IF(BK18&gt;=52000000,BK18*30%-5850000,IF(BK18&gt;=32000000,BK18*25%-3250000,IF(BK18&gt;=18000000,BK18*20%-1650000,IF(BK18&gt;=10000000,BK18*15%-750000,IF(BK18&gt;5000000,BK18*10%-250000,BK18*5%)))))),0),0))</f>
-        <v>2487000</v>
+        <f t="shared" ref="BL18:BL19" si="64">IF(E18="TV",BK18*10%,IF(BK18&gt;0,ROUND(IF(BK18&gt;=80000000,BK18*35%-9850000,IF(BK18&gt;=52000000,BK18*30%-5850000,IF(BK18&gt;=32000000,BK18*25%-3250000,IF(BK18&gt;=18000000,BK18*20%-1650000,IF(BK18&gt;=10000000,BK18*15%-750000,IF(BK18&gt;5000000,BK18*10%-250000,BK18*5%)))))),0),0))</f>
+        <v>2124750</v>
       </c>
       <c r="BM18" s="85"/>
       <c r="BN18" s="85"/>
@@ -10613,8 +10685,8 @@
       <c r="BS18" s="85"/>
       <c r="BT18" s="85"/>
       <c r="BU18" s="105">
-        <f t="shared" ref="BU18:BU19" si="67">AV18-BB18-BC18+BD18-BE18-BL18-BM18-BN18-BO18-BP18-BQ18-BR18+BS18-BT18</f>
-        <v>22319600</v>
+        <f t="shared" ref="BU18:BU19" si="65">AV18-BB18-BC18+BD18-BE18-BL18-BM18-BN18-BO18-BP18-BQ18-BR18+BS18-BT18</f>
+        <v>22681850</v>
       </c>
       <c r="BV18" s="235"/>
       <c r="BW18" s="108">
@@ -10630,11 +10702,11 @@
         <v>200000</v>
       </c>
       <c r="CA18" s="84">
-        <f t="shared" si="31"/>
+        <f t="shared" si="13"/>
         <v>1150000</v>
       </c>
       <c r="CB18" s="84">
-        <f t="shared" ref="CB18:CB19" si="68">SUM(BW18:CA18)</f>
+        <f t="shared" ref="CB18:CB19" si="66">SUM(BW18:CA18)</f>
         <v>24350000</v>
       </c>
       <c r="CC18" s="84" t="s">
@@ -10649,7 +10721,6 @@
     </row>
     <row r="19" spans="1:87" s="99" customFormat="1" ht="30.5" customHeight="1">
       <c r="A19" s="87">
-        <f>IF(B19=0,"",COUNTA($B$13:(B19)))</f>
         <v>7</v>
       </c>
       <c r="B19" s="100" t="s">
@@ -10675,7 +10746,7 @@
         <v>300000</v>
       </c>
       <c r="I19" s="91">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>11210000</v>
       </c>
       <c r="J19" s="239">
@@ -10726,27 +10797,27 @@
         <v>6340000</v>
       </c>
       <c r="Z19" s="91">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="91">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="AA19" s="91">
+      <c r="AB19" s="91">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="AB19" s="91">
+      <c r="AC19" s="91">
         <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="AC19" s="91">
+        <v>1828846.1538461538</v>
+      </c>
+      <c r="AD19" s="91">
         <f t="shared" si="55"/>
-        <v>1828846.1538461538</v>
-      </c>
-      <c r="AD19" s="91">
+        <v>975384.61538461538</v>
+      </c>
+      <c r="AE19" s="91">
         <f t="shared" si="56"/>
-        <v>975384.61538461538</v>
-      </c>
-      <c r="AE19" s="91">
-        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AF19" s="91">
@@ -10754,7 +10825,7 @@
         <v>0</v>
       </c>
       <c r="AG19" s="91">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AH19" s="91">
@@ -10762,7 +10833,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="91">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AJ19" s="91"/>
@@ -10776,7 +10847,7 @@
         <v>0</v>
       </c>
       <c r="AN19" s="91">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>300000</v>
       </c>
       <c r="AO19" s="91">
@@ -10792,20 +10863,20 @@
       <c r="AT19" s="91"/>
       <c r="AU19" s="91"/>
       <c r="AV19" s="91">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>22986923.076923076</v>
       </c>
       <c r="AW19" s="91"/>
       <c r="AX19" s="91" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="10"/>
         <v>x</v>
       </c>
       <c r="AY19" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>531200</v>
       </c>
       <c r="AZ19" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>99600</v>
       </c>
       <c r="BA19" s="85">
@@ -10813,38 +10884,38 @@
         <v>66400</v>
       </c>
       <c r="BB19" s="85">
-        <f t="shared" ref="BB19" si="69">SUM(AY19:BA19)</f>
+        <f t="shared" ref="BB19" si="67">SUM(AY19:BA19)</f>
         <v>697200</v>
       </c>
       <c r="BC19" s="85"/>
       <c r="BD19" s="85"/>
       <c r="BE19" s="85">
+        <f t="shared" si="61"/>
+        <v>63400</v>
+      </c>
+      <c r="BF19" s="85">
+        <f t="shared" si="27"/>
+        <v>3924038.4615384615</v>
+      </c>
+      <c r="BG19" s="85">
         <f t="shared" si="62"/>
-        <v>63400</v>
-      </c>
-      <c r="BF19" s="85">
-        <f t="shared" si="63"/>
-        <v>560000</v>
-      </c>
-      <c r="BG19" s="85">
-        <f t="shared" si="64"/>
-        <v>22426923.076923076</v>
+        <v>19062884.615384616</v>
       </c>
       <c r="BH19" s="85"/>
       <c r="BI19" s="85">
         <v>4400000</v>
       </c>
       <c r="BJ19" s="85">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11000000</v>
       </c>
       <c r="BK19" s="85">
-        <f t="shared" si="65"/>
-        <v>10729723.076923076</v>
+        <f t="shared" si="63"/>
+        <v>7365684.615384616</v>
       </c>
       <c r="BL19" s="84">
-        <f t="shared" si="66"/>
-        <v>859458</v>
+        <f t="shared" si="64"/>
+        <v>486568</v>
       </c>
       <c r="BM19" s="85"/>
       <c r="BN19" s="85"/>
@@ -10857,8 +10928,8 @@
       <c r="BS19" s="85"/>
       <c r="BT19" s="85"/>
       <c r="BU19" s="105">
-        <f t="shared" si="67"/>
-        <v>21366865.076923076</v>
+        <f t="shared" si="65"/>
+        <v>21739755.076923076</v>
       </c>
       <c r="BV19" s="235"/>
       <c r="BW19" s="108">
@@ -10874,11 +10945,11 @@
         <v>200000</v>
       </c>
       <c r="CA19" s="84">
-        <f t="shared" si="31"/>
+        <f t="shared" si="13"/>
         <v>850000</v>
       </c>
       <c r="CB19" s="84">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>18050000</v>
       </c>
       <c r="CC19" s="84" t="s">
@@ -11024,6 +11095,72 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="82">
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AI9:AI11"/>
+    <mergeCell ref="AS8:AS11"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="AP8:AP11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="AY8:BQ8"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="BS9:BS11"/>
+    <mergeCell ref="BO10:BO11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="BL10:BL11"/>
+    <mergeCell ref="AY9:BL9"/>
+    <mergeCell ref="BM9:BQ9"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BQ10:BQ11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="AC9:AC11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="M9:M11"/>
     <mergeCell ref="CD8:CD11"/>
     <mergeCell ref="AX8:AX11"/>
     <mergeCell ref="BF10:BF11"/>
@@ -11040,72 +11177,6 @@
     <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BR8:BS8"/>
     <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="AY9:BL9"/>
-    <mergeCell ref="BM9:BQ9"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BQ10:BQ11"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="BJ10:BJ11"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="BS9:BS11"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="AP8:AP11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="AV8:AV11"/>
-    <mergeCell ref="AY8:BQ8"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="BH10:BH11"/>
   </mergeCells>
   <conditionalFormatting sqref="B13:B1048576 B1:B11">
     <cfRule type="duplicateValues" dxfId="22" priority="36"/>
@@ -11313,91 +11384,91 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" outlineLevel="1">
-      <c r="A3" s="402" t="str">
+      <c r="A3" s="449" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
         <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
       </c>
-      <c r="B3" s="402"/>
-      <c r="C3" s="402"/>
-      <c r="D3" s="402"/>
-      <c r="E3" s="402"/>
-      <c r="F3" s="402"/>
-      <c r="G3" s="402"/>
-      <c r="H3" s="402"/>
-      <c r="I3" s="402"/>
-      <c r="J3" s="402"/>
-      <c r="K3" s="402"/>
-      <c r="L3" s="402"/>
-      <c r="M3" s="402"/>
-      <c r="N3" s="402"/>
-      <c r="O3" s="402"/>
-      <c r="P3" s="402"/>
-      <c r="Q3" s="402"/>
-      <c r="R3" s="402"/>
-      <c r="S3" s="402"/>
-      <c r="T3" s="402"/>
-      <c r="U3" s="402"/>
-      <c r="V3" s="402"/>
-      <c r="W3" s="402"/>
-      <c r="X3" s="402"/>
-      <c r="Y3" s="402"/>
-      <c r="Z3" s="402"/>
-      <c r="AA3" s="402"/>
-      <c r="AB3" s="402"/>
-      <c r="AC3" s="402"/>
-      <c r="AD3" s="402"/>
-      <c r="AE3" s="402"/>
-      <c r="AF3" s="402"/>
-      <c r="AG3" s="402"/>
-      <c r="AH3" s="402"/>
-      <c r="AI3" s="402"/>
-      <c r="AJ3" s="402"/>
-      <c r="AK3" s="402"/>
-      <c r="AL3" s="402"/>
-      <c r="AM3" s="402"/>
-      <c r="AN3" s="402"/>
-      <c r="AO3" s="402"/>
-      <c r="AP3" s="402"/>
-      <c r="AQ3" s="402"/>
-      <c r="AR3" s="402"/>
-      <c r="AS3" s="402"/>
-      <c r="AT3" s="402"/>
-      <c r="AU3" s="402"/>
-      <c r="AV3" s="402"/>
-      <c r="AW3" s="402"/>
-      <c r="AX3" s="402"/>
-      <c r="AY3" s="402"/>
-      <c r="AZ3" s="402"/>
-      <c r="BA3" s="402"/>
-      <c r="BB3" s="402"/>
-      <c r="BC3" s="402"/>
-      <c r="BD3" s="402"/>
-      <c r="BE3" s="402"/>
-      <c r="BF3" s="402"/>
-      <c r="BG3" s="402"/>
-      <c r="BH3" s="402"/>
-      <c r="BI3" s="402"/>
-      <c r="BJ3" s="402"/>
-      <c r="BK3" s="402"/>
-      <c r="BL3" s="402"/>
-      <c r="BM3" s="402"/>
-      <c r="BN3" s="402"/>
-      <c r="BO3" s="402"/>
-      <c r="BP3" s="402"/>
-      <c r="BQ3" s="402"/>
-      <c r="BR3" s="402"/>
-      <c r="BS3" s="402"/>
-      <c r="BT3" s="402"/>
-      <c r="BU3" s="402"/>
+      <c r="B3" s="449"/>
+      <c r="C3" s="449"/>
+      <c r="D3" s="449"/>
+      <c r="E3" s="449"/>
+      <c r="F3" s="449"/>
+      <c r="G3" s="449"/>
+      <c r="H3" s="449"/>
+      <c r="I3" s="449"/>
+      <c r="J3" s="449"/>
+      <c r="K3" s="449"/>
+      <c r="L3" s="449"/>
+      <c r="M3" s="449"/>
+      <c r="N3" s="449"/>
+      <c r="O3" s="449"/>
+      <c r="P3" s="449"/>
+      <c r="Q3" s="449"/>
+      <c r="R3" s="449"/>
+      <c r="S3" s="449"/>
+      <c r="T3" s="449"/>
+      <c r="U3" s="449"/>
+      <c r="V3" s="449"/>
+      <c r="W3" s="449"/>
+      <c r="X3" s="449"/>
+      <c r="Y3" s="449"/>
+      <c r="Z3" s="449"/>
+      <c r="AA3" s="449"/>
+      <c r="AB3" s="449"/>
+      <c r="AC3" s="449"/>
+      <c r="AD3" s="449"/>
+      <c r="AE3" s="449"/>
+      <c r="AF3" s="449"/>
+      <c r="AG3" s="449"/>
+      <c r="AH3" s="449"/>
+      <c r="AI3" s="449"/>
+      <c r="AJ3" s="449"/>
+      <c r="AK3" s="449"/>
+      <c r="AL3" s="449"/>
+      <c r="AM3" s="449"/>
+      <c r="AN3" s="449"/>
+      <c r="AO3" s="449"/>
+      <c r="AP3" s="449"/>
+      <c r="AQ3" s="449"/>
+      <c r="AR3" s="449"/>
+      <c r="AS3" s="449"/>
+      <c r="AT3" s="449"/>
+      <c r="AU3" s="449"/>
+      <c r="AV3" s="449"/>
+      <c r="AW3" s="449"/>
+      <c r="AX3" s="449"/>
+      <c r="AY3" s="449"/>
+      <c r="AZ3" s="449"/>
+      <c r="BA3" s="449"/>
+      <c r="BB3" s="449"/>
+      <c r="BC3" s="449"/>
+      <c r="BD3" s="449"/>
+      <c r="BE3" s="449"/>
+      <c r="BF3" s="449"/>
+      <c r="BG3" s="449"/>
+      <c r="BH3" s="449"/>
+      <c r="BI3" s="449"/>
+      <c r="BJ3" s="449"/>
+      <c r="BK3" s="449"/>
+      <c r="BL3" s="449"/>
+      <c r="BM3" s="449"/>
+      <c r="BN3" s="449"/>
+      <c r="BO3" s="449"/>
+      <c r="BP3" s="449"/>
+      <c r="BQ3" s="449"/>
+      <c r="BR3" s="449"/>
+      <c r="BS3" s="449"/>
+      <c r="BT3" s="449"/>
+      <c r="BU3" s="449"/>
       <c r="BV3"/>
-      <c r="BW3" s="403" t="s">
+      <c r="BW3" s="450" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="403"/>
-      <c r="BY3" s="403"/>
-      <c r="BZ3" s="403"/>
-      <c r="CA3" s="403"/>
-      <c r="CB3" s="402"/>
+      <c r="BX3" s="450"/>
+      <c r="BY3" s="450"/>
+      <c r="BZ3" s="450"/>
+      <c r="CA3" s="450"/>
+      <c r="CB3" s="449"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -11481,366 +11552,366 @@
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
       <c r="BV4"/>
-      <c r="BW4" s="402"/>
-      <c r="BX4" s="402"/>
-      <c r="BY4" s="402"/>
-      <c r="BZ4" s="402"/>
-      <c r="CA4" s="402"/>
-      <c r="CB4" s="402"/>
+      <c r="BW4" s="449"/>
+      <c r="BX4" s="449"/>
+      <c r="BY4" s="449"/>
+      <c r="BZ4" s="449"/>
+      <c r="CA4" s="449"/>
+      <c r="CB4" s="449"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="404" t="s">
+      <c r="A5" s="451" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="407" t="s">
+      <c r="B5" s="454" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="410" t="s">
+      <c r="C5" s="402" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="413" t="s">
+      <c r="D5" s="457" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="413" t="s">
+      <c r="E5" s="457" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="410" t="s">
+      <c r="F5" s="402" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="410" t="s">
+      <c r="G5" s="402" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="416" t="s">
+      <c r="H5" s="415" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="416" t="s">
+      <c r="I5" s="415" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="410" t="s">
+      <c r="J5" s="402" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="419" t="s">
+      <c r="K5" s="460" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="420"/>
-      <c r="M5" s="420"/>
-      <c r="N5" s="420"/>
-      <c r="O5" s="420"/>
-      <c r="P5" s="420"/>
-      <c r="Q5" s="420"/>
-      <c r="R5" s="420"/>
-      <c r="S5" s="420"/>
-      <c r="T5" s="420"/>
-      <c r="U5" s="420"/>
-      <c r="V5" s="420"/>
-      <c r="W5" s="420"/>
-      <c r="X5" s="420"/>
-      <c r="Y5" s="421" t="s">
+      <c r="L5" s="461"/>
+      <c r="M5" s="461"/>
+      <c r="N5" s="461"/>
+      <c r="O5" s="461"/>
+      <c r="P5" s="461"/>
+      <c r="Q5" s="461"/>
+      <c r="R5" s="461"/>
+      <c r="S5" s="461"/>
+      <c r="T5" s="461"/>
+      <c r="U5" s="461"/>
+      <c r="V5" s="461"/>
+      <c r="W5" s="461"/>
+      <c r="X5" s="461"/>
+      <c r="Y5" s="462" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="422"/>
-      <c r="AA5" s="422"/>
-      <c r="AB5" s="422"/>
-      <c r="AC5" s="422"/>
-      <c r="AD5" s="422"/>
-      <c r="AE5" s="422"/>
-      <c r="AF5" s="422"/>
-      <c r="AG5" s="422"/>
-      <c r="AH5" s="422"/>
-      <c r="AI5" s="422"/>
-      <c r="AJ5" s="422"/>
-      <c r="AK5" s="422"/>
-      <c r="AL5" s="422"/>
-      <c r="AM5" s="422"/>
-      <c r="AN5" s="422"/>
-      <c r="AO5" s="423"/>
-      <c r="AP5" s="410" t="s">
+      <c r="Z5" s="463"/>
+      <c r="AA5" s="463"/>
+      <c r="AB5" s="463"/>
+      <c r="AC5" s="463"/>
+      <c r="AD5" s="463"/>
+      <c r="AE5" s="463"/>
+      <c r="AF5" s="463"/>
+      <c r="AG5" s="463"/>
+      <c r="AH5" s="463"/>
+      <c r="AI5" s="463"/>
+      <c r="AJ5" s="463"/>
+      <c r="AK5" s="463"/>
+      <c r="AL5" s="463"/>
+      <c r="AM5" s="463"/>
+      <c r="AN5" s="463"/>
+      <c r="AO5" s="464"/>
+      <c r="AP5" s="402" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="410" t="s">
+      <c r="AQ5" s="402" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="410" t="s">
+      <c r="AR5" s="402" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="410" t="s">
+      <c r="AS5" s="402" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="410" t="s">
+      <c r="AT5" s="402" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="410" t="s">
+      <c r="AU5" s="402" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="410" t="s">
+      <c r="AV5" s="402" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="410" t="s">
+      <c r="AW5" s="402" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="410" t="s">
+      <c r="AX5" s="402" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="431" t="s">
+      <c r="AY5" s="405" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="432"/>
-      <c r="BA5" s="432"/>
-      <c r="BB5" s="432"/>
-      <c r="BC5" s="432"/>
-      <c r="BD5" s="432"/>
-      <c r="BE5" s="432"/>
-      <c r="BF5" s="432"/>
-      <c r="BG5" s="432"/>
-      <c r="BH5" s="432"/>
-      <c r="BI5" s="432"/>
-      <c r="BJ5" s="432"/>
-      <c r="BK5" s="432"/>
-      <c r="BL5" s="432"/>
-      <c r="BM5" s="432"/>
-      <c r="BN5" s="432"/>
-      <c r="BO5" s="432"/>
-      <c r="BP5" s="432"/>
-      <c r="BQ5" s="433"/>
-      <c r="BR5" s="434" t="s">
+      <c r="AZ5" s="406"/>
+      <c r="BA5" s="406"/>
+      <c r="BB5" s="406"/>
+      <c r="BC5" s="406"/>
+      <c r="BD5" s="406"/>
+      <c r="BE5" s="406"/>
+      <c r="BF5" s="406"/>
+      <c r="BG5" s="406"/>
+      <c r="BH5" s="406"/>
+      <c r="BI5" s="406"/>
+      <c r="BJ5" s="406"/>
+      <c r="BK5" s="406"/>
+      <c r="BL5" s="406"/>
+      <c r="BM5" s="406"/>
+      <c r="BN5" s="406"/>
+      <c r="BO5" s="406"/>
+      <c r="BP5" s="406"/>
+      <c r="BQ5" s="407"/>
+      <c r="BR5" s="433" t="s">
         <v>26</v>
       </c>
-      <c r="BS5" s="435"/>
-      <c r="BT5" s="436" t="s">
+      <c r="BS5" s="442"/>
+      <c r="BT5" s="410" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="434" t="s">
+      <c r="BU5" s="433" t="s">
         <v>28</v>
       </c>
       <c r="BV5"/>
-      <c r="BW5" s="457" t="s">
+      <c r="BW5" s="436" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="443" t="s">
+      <c r="BX5" s="421" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="444"/>
-      <c r="BZ5" s="444"/>
-      <c r="CA5" s="445"/>
-      <c r="CB5" s="452" t="s">
+      <c r="BY5" s="422"/>
+      <c r="BZ5" s="422"/>
+      <c r="CA5" s="423"/>
+      <c r="CB5" s="430" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="384" t="s">
+      <c r="CC5" s="326" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="384" t="s">
+      <c r="CD5" s="326" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
     <row r="6" spans="1:87" s="136" customFormat="1">
-      <c r="A6" s="405"/>
-      <c r="B6" s="408"/>
-      <c r="C6" s="411"/>
-      <c r="D6" s="414"/>
-      <c r="E6" s="414"/>
-      <c r="F6" s="411"/>
-      <c r="G6" s="411"/>
-      <c r="H6" s="417"/>
-      <c r="I6" s="417"/>
-      <c r="J6" s="411"/>
-      <c r="K6" s="424" t="s">
+      <c r="A6" s="452"/>
+      <c r="B6" s="455"/>
+      <c r="C6" s="403"/>
+      <c r="D6" s="458"/>
+      <c r="E6" s="458"/>
+      <c r="F6" s="403"/>
+      <c r="G6" s="403"/>
+      <c r="H6" s="416"/>
+      <c r="I6" s="416"/>
+      <c r="J6" s="403"/>
+      <c r="K6" s="439" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="424" t="s">
+      <c r="L6" s="439" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="424" t="s">
+      <c r="M6" s="439" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="424" t="s">
+      <c r="N6" s="439" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="424" t="s">
+      <c r="O6" s="439" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="424" t="s">
+      <c r="P6" s="439" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="424" t="s">
+      <c r="Q6" s="439" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="424" t="s">
+      <c r="R6" s="439" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="424" t="s">
+      <c r="S6" s="439" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="424" t="s">
+      <c r="T6" s="439" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="424" t="s">
+      <c r="U6" s="439" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="427" t="s">
+      <c r="V6" s="445" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="428"/>
-      <c r="X6" s="424" t="s">
+      <c r="W6" s="446"/>
+      <c r="X6" s="439" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="410" t="s">
+      <c r="Y6" s="402" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="410" t="s">
+      <c r="Z6" s="402" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="410" t="s">
+      <c r="AA6" s="402" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="410" t="s">
+      <c r="AB6" s="402" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="416" t="s">
+      <c r="AC6" s="415" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="416" t="s">
+      <c r="AD6" s="415" t="s">
         <v>52</v>
       </c>
-      <c r="AE6" s="416" t="s">
+      <c r="AE6" s="415" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="416" t="s">
+      <c r="AF6" s="415" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="410" t="s">
+      <c r="AG6" s="402" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="416" t="s">
+      <c r="AH6" s="415" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="416" t="s">
+      <c r="AI6" s="415" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="410" t="s">
+      <c r="AJ6" s="402" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="460" t="s">
+      <c r="AK6" s="418" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="410" t="s">
+      <c r="AL6" s="402" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="410" t="s">
+      <c r="AM6" s="402" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="342" t="s">
+      <c r="AN6" s="329" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="410" t="s">
+      <c r="AO6" s="402" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="411"/>
-      <c r="AQ6" s="411"/>
-      <c r="AR6" s="411"/>
-      <c r="AS6" s="411"/>
-      <c r="AT6" s="411"/>
-      <c r="AU6" s="411"/>
-      <c r="AV6" s="411"/>
-      <c r="AW6" s="411"/>
-      <c r="AX6" s="411"/>
-      <c r="AY6" s="431" t="s">
+      <c r="AP6" s="403"/>
+      <c r="AQ6" s="403"/>
+      <c r="AR6" s="403"/>
+      <c r="AS6" s="403"/>
+      <c r="AT6" s="403"/>
+      <c r="AU6" s="403"/>
+      <c r="AV6" s="403"/>
+      <c r="AW6" s="403"/>
+      <c r="AX6" s="403"/>
+      <c r="AY6" s="405" t="s">
         <v>64</v>
       </c>
-      <c r="AZ6" s="432"/>
-      <c r="BA6" s="432"/>
-      <c r="BB6" s="432"/>
-      <c r="BC6" s="432"/>
-      <c r="BD6" s="432"/>
-      <c r="BE6" s="432"/>
-      <c r="BF6" s="432"/>
-      <c r="BG6" s="432"/>
-      <c r="BH6" s="432"/>
-      <c r="BI6" s="432"/>
-      <c r="BJ6" s="432"/>
-      <c r="BK6" s="432"/>
-      <c r="BL6" s="433"/>
-      <c r="BM6" s="431" t="s">
+      <c r="AZ6" s="406"/>
+      <c r="BA6" s="406"/>
+      <c r="BB6" s="406"/>
+      <c r="BC6" s="406"/>
+      <c r="BD6" s="406"/>
+      <c r="BE6" s="406"/>
+      <c r="BF6" s="406"/>
+      <c r="BG6" s="406"/>
+      <c r="BH6" s="406"/>
+      <c r="BI6" s="406"/>
+      <c r="BJ6" s="406"/>
+      <c r="BK6" s="406"/>
+      <c r="BL6" s="407"/>
+      <c r="BM6" s="405" t="s">
         <v>65</v>
       </c>
-      <c r="BN6" s="432"/>
-      <c r="BO6" s="432"/>
-      <c r="BP6" s="432"/>
-      <c r="BQ6" s="433"/>
-      <c r="BR6" s="437" t="s">
+      <c r="BN6" s="406"/>
+      <c r="BO6" s="406"/>
+      <c r="BP6" s="406"/>
+      <c r="BQ6" s="407"/>
+      <c r="BR6" s="408" t="s">
         <v>66</v>
       </c>
-      <c r="BS6" s="437" t="s">
+      <c r="BS6" s="408" t="s">
         <v>67</v>
       </c>
-      <c r="BT6" s="437"/>
-      <c r="BU6" s="455"/>
+      <c r="BT6" s="408"/>
+      <c r="BU6" s="434"/>
       <c r="BV6"/>
-      <c r="BW6" s="458"/>
-      <c r="BX6" s="446"/>
-      <c r="BY6" s="447"/>
-      <c r="BZ6" s="447"/>
-      <c r="CA6" s="448"/>
-      <c r="CB6" s="453"/>
-      <c r="CC6" s="385"/>
-      <c r="CD6" s="385"/>
+      <c r="BW6" s="437"/>
+      <c r="BX6" s="424"/>
+      <c r="BY6" s="425"/>
+      <c r="BZ6" s="425"/>
+      <c r="CA6" s="426"/>
+      <c r="CB6" s="431"/>
+      <c r="CC6" s="327"/>
+      <c r="CD6" s="327"/>
       <c r="CH6" s="137"/>
       <c r="CI6" s="138"/>
     </row>
     <row r="7" spans="1:87" s="139" customFormat="1">
-      <c r="A7" s="405"/>
-      <c r="B7" s="408"/>
-      <c r="C7" s="411"/>
-      <c r="D7" s="414"/>
-      <c r="E7" s="414"/>
-      <c r="F7" s="411"/>
-      <c r="G7" s="411"/>
-      <c r="H7" s="417"/>
-      <c r="I7" s="417"/>
-      <c r="J7" s="411"/>
-      <c r="K7" s="425"/>
-      <c r="L7" s="425"/>
-      <c r="M7" s="425"/>
-      <c r="N7" s="425"/>
-      <c r="O7" s="425"/>
-      <c r="P7" s="425"/>
-      <c r="Q7" s="425"/>
-      <c r="R7" s="425"/>
-      <c r="S7" s="425"/>
-      <c r="T7" s="425"/>
-      <c r="U7" s="425"/>
-      <c r="V7" s="429"/>
-      <c r="W7" s="430"/>
-      <c r="X7" s="425"/>
-      <c r="Y7" s="411"/>
-      <c r="Z7" s="411"/>
-      <c r="AA7" s="411"/>
-      <c r="AB7" s="411"/>
-      <c r="AC7" s="417"/>
-      <c r="AD7" s="417"/>
-      <c r="AE7" s="417"/>
-      <c r="AF7" s="417"/>
-      <c r="AG7" s="411"/>
-      <c r="AH7" s="417"/>
-      <c r="AI7" s="417"/>
-      <c r="AJ7" s="411"/>
-      <c r="AK7" s="461"/>
-      <c r="AL7" s="411"/>
-      <c r="AM7" s="411"/>
-      <c r="AN7" s="343"/>
-      <c r="AO7" s="411"/>
-      <c r="AP7" s="411"/>
-      <c r="AQ7" s="411"/>
-      <c r="AR7" s="411"/>
-      <c r="AS7" s="411"/>
-      <c r="AT7" s="411"/>
-      <c r="AU7" s="411"/>
-      <c r="AV7" s="411"/>
-      <c r="AW7" s="411"/>
-      <c r="AX7" s="411"/>
+      <c r="A7" s="452"/>
+      <c r="B7" s="455"/>
+      <c r="C7" s="403"/>
+      <c r="D7" s="458"/>
+      <c r="E7" s="458"/>
+      <c r="F7" s="403"/>
+      <c r="G7" s="403"/>
+      <c r="H7" s="416"/>
+      <c r="I7" s="416"/>
+      <c r="J7" s="403"/>
+      <c r="K7" s="440"/>
+      <c r="L7" s="440"/>
+      <c r="M7" s="440"/>
+      <c r="N7" s="440"/>
+      <c r="O7" s="440"/>
+      <c r="P7" s="440"/>
+      <c r="Q7" s="440"/>
+      <c r="R7" s="440"/>
+      <c r="S7" s="440"/>
+      <c r="T7" s="440"/>
+      <c r="U7" s="440"/>
+      <c r="V7" s="447"/>
+      <c r="W7" s="448"/>
+      <c r="X7" s="440"/>
+      <c r="Y7" s="403"/>
+      <c r="Z7" s="403"/>
+      <c r="AA7" s="403"/>
+      <c r="AB7" s="403"/>
+      <c r="AC7" s="416"/>
+      <c r="AD7" s="416"/>
+      <c r="AE7" s="416"/>
+      <c r="AF7" s="416"/>
+      <c r="AG7" s="403"/>
+      <c r="AH7" s="416"/>
+      <c r="AI7" s="416"/>
+      <c r="AJ7" s="403"/>
+      <c r="AK7" s="419"/>
+      <c r="AL7" s="403"/>
+      <c r="AM7" s="403"/>
+      <c r="AN7" s="330"/>
+      <c r="AO7" s="403"/>
+      <c r="AP7" s="403"/>
+      <c r="AQ7" s="403"/>
+      <c r="AR7" s="403"/>
+      <c r="AS7" s="403"/>
+      <c r="AT7" s="403"/>
+      <c r="AU7" s="403"/>
+      <c r="AV7" s="403"/>
+      <c r="AW7" s="403"/>
+      <c r="AX7" s="403"/>
       <c r="AY7" s="101" t="s">
         <v>68</v>
       </c>
@@ -11850,125 +11921,125 @@
       <c r="BA7" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="BB7" s="436" t="s">
+      <c r="BB7" s="410" t="s">
         <v>71</v>
       </c>
-      <c r="BC7" s="439" t="s">
+      <c r="BC7" s="411" t="s">
         <v>72</v>
       </c>
-      <c r="BD7" s="439" t="s">
+      <c r="BD7" s="411" t="s">
         <v>73</v>
       </c>
-      <c r="BE7" s="441" t="s">
+      <c r="BE7" s="443" t="s">
         <v>74</v>
       </c>
-      <c r="BF7" s="439" t="s">
+      <c r="BF7" s="411" t="s">
         <v>75</v>
       </c>
-      <c r="BG7" s="439" t="s">
+      <c r="BG7" s="411" t="s">
         <v>76</v>
       </c>
-      <c r="BH7" s="439" t="s">
+      <c r="BH7" s="411" t="s">
         <v>77</v>
       </c>
-      <c r="BI7" s="439" t="s">
+      <c r="BI7" s="411" t="s">
         <v>78</v>
       </c>
-      <c r="BJ7" s="439" t="s">
+      <c r="BJ7" s="411" t="s">
         <v>79</v>
       </c>
-      <c r="BK7" s="439" t="s">
+      <c r="BK7" s="411" t="s">
         <v>80</v>
       </c>
-      <c r="BL7" s="463" t="s">
+      <c r="BL7" s="413" t="s">
         <v>81</v>
       </c>
-      <c r="BM7" s="439" t="s">
+      <c r="BM7" s="411" t="s">
         <v>82</v>
       </c>
-      <c r="BN7" s="436" t="s">
+      <c r="BN7" s="410" t="s">
         <v>83</v>
       </c>
-      <c r="BO7" s="439" t="s">
+      <c r="BO7" s="411" t="s">
         <v>84</v>
       </c>
-      <c r="BP7" s="436" t="s">
+      <c r="BP7" s="410" t="s">
         <v>85</v>
       </c>
-      <c r="BQ7" s="436" t="s">
+      <c r="BQ7" s="410" t="s">
         <v>86</v>
       </c>
-      <c r="BR7" s="437"/>
-      <c r="BS7" s="437"/>
-      <c r="BT7" s="437"/>
-      <c r="BU7" s="455"/>
+      <c r="BR7" s="408"/>
+      <c r="BS7" s="408"/>
+      <c r="BT7" s="408"/>
+      <c r="BU7" s="434"/>
       <c r="BV7"/>
-      <c r="BW7" s="459"/>
-      <c r="BX7" s="449"/>
-      <c r="BY7" s="450"/>
-      <c r="BZ7" s="450"/>
-      <c r="CA7" s="451"/>
-      <c r="CB7" s="454"/>
-      <c r="CC7" s="386"/>
-      <c r="CD7" s="386"/>
+      <c r="BW7" s="438"/>
+      <c r="BX7" s="427"/>
+      <c r="BY7" s="428"/>
+      <c r="BZ7" s="428"/>
+      <c r="CA7" s="429"/>
+      <c r="CB7" s="432"/>
+      <c r="CC7" s="328"/>
+      <c r="CD7" s="328"/>
       <c r="CH7" s="137"/>
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="139" customFormat="1">
-      <c r="A8" s="406"/>
-      <c r="B8" s="409"/>
-      <c r="C8" s="412"/>
-      <c r="D8" s="415"/>
-      <c r="E8" s="415"/>
-      <c r="F8" s="412"/>
-      <c r="G8" s="412"/>
-      <c r="H8" s="418"/>
-      <c r="I8" s="418"/>
-      <c r="J8" s="412"/>
-      <c r="K8" s="426"/>
-      <c r="L8" s="426"/>
-      <c r="M8" s="426"/>
-      <c r="N8" s="426"/>
-      <c r="O8" s="426"/>
-      <c r="P8" s="426"/>
-      <c r="Q8" s="426"/>
-      <c r="R8" s="426"/>
-      <c r="S8" s="426"/>
-      <c r="T8" s="426"/>
-      <c r="U8" s="426"/>
+      <c r="A8" s="453"/>
+      <c r="B8" s="456"/>
+      <c r="C8" s="404"/>
+      <c r="D8" s="459"/>
+      <c r="E8" s="459"/>
+      <c r="F8" s="404"/>
+      <c r="G8" s="404"/>
+      <c r="H8" s="417"/>
+      <c r="I8" s="417"/>
+      <c r="J8" s="404"/>
+      <c r="K8" s="441"/>
+      <c r="L8" s="441"/>
+      <c r="M8" s="441"/>
+      <c r="N8" s="441"/>
+      <c r="O8" s="441"/>
+      <c r="P8" s="441"/>
+      <c r="Q8" s="441"/>
+      <c r="R8" s="441"/>
+      <c r="S8" s="441"/>
+      <c r="T8" s="441"/>
+      <c r="U8" s="441"/>
       <c r="V8" s="140" t="s">
         <v>87</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>88</v>
       </c>
-      <c r="X8" s="426"/>
-      <c r="Y8" s="412"/>
-      <c r="Z8" s="412"/>
-      <c r="AA8" s="412"/>
-      <c r="AB8" s="412"/>
-      <c r="AC8" s="418"/>
-      <c r="AD8" s="418"/>
-      <c r="AE8" s="418"/>
-      <c r="AF8" s="418"/>
-      <c r="AG8" s="412"/>
-      <c r="AH8" s="418"/>
-      <c r="AI8" s="418"/>
-      <c r="AJ8" s="412"/>
-      <c r="AK8" s="462"/>
-      <c r="AL8" s="412"/>
-      <c r="AM8" s="412"/>
-      <c r="AN8" s="344"/>
-      <c r="AO8" s="412"/>
-      <c r="AP8" s="412"/>
-      <c r="AQ8" s="412"/>
-      <c r="AR8" s="412"/>
-      <c r="AS8" s="412"/>
-      <c r="AT8" s="412"/>
-      <c r="AU8" s="412"/>
-      <c r="AV8" s="412"/>
-      <c r="AW8" s="412"/>
-      <c r="AX8" s="412"/>
+      <c r="X8" s="441"/>
+      <c r="Y8" s="404"/>
+      <c r="Z8" s="404"/>
+      <c r="AA8" s="404"/>
+      <c r="AB8" s="404"/>
+      <c r="AC8" s="417"/>
+      <c r="AD8" s="417"/>
+      <c r="AE8" s="417"/>
+      <c r="AF8" s="417"/>
+      <c r="AG8" s="404"/>
+      <c r="AH8" s="417"/>
+      <c r="AI8" s="417"/>
+      <c r="AJ8" s="404"/>
+      <c r="AK8" s="420"/>
+      <c r="AL8" s="404"/>
+      <c r="AM8" s="404"/>
+      <c r="AN8" s="331"/>
+      <c r="AO8" s="404"/>
+      <c r="AP8" s="404"/>
+      <c r="AQ8" s="404"/>
+      <c r="AR8" s="404"/>
+      <c r="AS8" s="404"/>
+      <c r="AT8" s="404"/>
+      <c r="AU8" s="404"/>
+      <c r="AV8" s="404"/>
+      <c r="AW8" s="404"/>
+      <c r="AX8" s="404"/>
       <c r="AY8" s="102" t="s">
         <v>89</v>
       </c>
@@ -11978,28 +12049,28 @@
       <c r="BA8" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="BB8" s="438"/>
-      <c r="BC8" s="440"/>
-      <c r="BD8" s="440"/>
-      <c r="BE8" s="442"/>
-      <c r="BF8" s="440"/>
-      <c r="BG8" s="440"/>
-      <c r="BH8" s="440"/>
-      <c r="BI8" s="440"/>
-      <c r="BJ8" s="440"/>
-      <c r="BK8" s="440"/>
-      <c r="BL8" s="464"/>
-      <c r="BM8" s="440"/>
-      <c r="BN8" s="438"/>
-      <c r="BO8" s="440"/>
-      <c r="BP8" s="438"/>
-      <c r="BQ8" s="438"/>
-      <c r="BR8" s="438"/>
-      <c r="BS8" s="438"/>
-      <c r="BT8" s="438"/>
-      <c r="BU8" s="456"/>
+      <c r="BB8" s="409"/>
+      <c r="BC8" s="412"/>
+      <c r="BD8" s="412"/>
+      <c r="BE8" s="444"/>
+      <c r="BF8" s="412"/>
+      <c r="BG8" s="412"/>
+      <c r="BH8" s="412"/>
+      <c r="BI8" s="412"/>
+      <c r="BJ8" s="412"/>
+      <c r="BK8" s="412"/>
+      <c r="BL8" s="414"/>
+      <c r="BM8" s="412"/>
+      <c r="BN8" s="409"/>
+      <c r="BO8" s="412"/>
+      <c r="BP8" s="409"/>
+      <c r="BQ8" s="409"/>
+      <c r="BR8" s="409"/>
+      <c r="BS8" s="409"/>
+      <c r="BT8" s="409"/>
+      <c r="BU8" s="435"/>
       <c r="BV8"/>
-      <c r="BW8" s="459"/>
+      <c r="BW8" s="438"/>
       <c r="BX8" s="72" t="s">
         <v>92</v>
       </c>
@@ -12012,9 +12083,9 @@
       <c r="CA8" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="CB8" s="454"/>
-      <c r="CC8" s="386"/>
-      <c r="CD8" s="386"/>
+      <c r="CB8" s="432"/>
+      <c r="CC8" s="328"/>
+      <c r="CD8" s="328"/>
       <c r="CE8" s="136"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
@@ -14638,56 +14709,22 @@
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <mergeCells count="82">
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="AY6:BL6"/>
-    <mergeCell ref="BM6:BQ6"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="BQ7:BQ8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BK7:BK8"/>
-    <mergeCell ref="BL7:BL8"/>
-    <mergeCell ref="BM7:BM8"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="CB5:CB8"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="AY5:BQ5"/>
-    <mergeCell ref="BR5:BS5"/>
-    <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="BS6:BS8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AP5:AP8"/>
+    <mergeCell ref="Q6:Q8"/>
     <mergeCell ref="R6:R8"/>
     <mergeCell ref="S6:S8"/>
     <mergeCell ref="T6:T8"/>
@@ -14704,22 +14741,56 @@
     <mergeCell ref="U6:U8"/>
     <mergeCell ref="V6:W7"/>
     <mergeCell ref="X6:X8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AP5:AP8"/>
-    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="AY5:BQ5"/>
+    <mergeCell ref="BR5:BS5"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="BH7:BH8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="BS6:BS8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="CB5:CB8"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="AY6:BL6"/>
+    <mergeCell ref="BM6:BQ6"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="BQ7:BQ8"/>
+    <mergeCell ref="BJ7:BJ8"/>
+    <mergeCell ref="BK7:BK8"/>
+    <mergeCell ref="BL7:BL8"/>
+    <mergeCell ref="BM7:BM8"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BO7:BO8"/>
   </mergeCells>
   <conditionalFormatting sqref="B12:B16 B1:B9 C9:BU9 B20:B1048576">
     <cfRule type="duplicateValues" dxfId="19" priority="49"/>
@@ -14949,91 +15020,91 @@
       <c r="CD2" s="12"/>
     </row>
     <row r="3" spans="1:87" s="16" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="489" t="str">
+      <c r="A3" s="471" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
         <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
       </c>
-      <c r="B3" s="489"/>
-      <c r="C3" s="489"/>
-      <c r="D3" s="489"/>
-      <c r="E3" s="489"/>
-      <c r="F3" s="489"/>
-      <c r="G3" s="489"/>
-      <c r="H3" s="489"/>
-      <c r="I3" s="489"/>
-      <c r="J3" s="489"/>
-      <c r="K3" s="489"/>
-      <c r="L3" s="489"/>
-      <c r="M3" s="489"/>
-      <c r="N3" s="489"/>
-      <c r="O3" s="489"/>
-      <c r="P3" s="489"/>
-      <c r="Q3" s="489"/>
-      <c r="R3" s="489"/>
-      <c r="S3" s="489"/>
-      <c r="T3" s="489"/>
-      <c r="U3" s="489"/>
-      <c r="V3" s="489"/>
-      <c r="W3" s="489"/>
-      <c r="X3" s="489"/>
-      <c r="Y3" s="489"/>
-      <c r="Z3" s="489"/>
-      <c r="AA3" s="489"/>
-      <c r="AB3" s="489"/>
-      <c r="AC3" s="489"/>
-      <c r="AD3" s="489"/>
-      <c r="AE3" s="489"/>
-      <c r="AF3" s="489"/>
-      <c r="AG3" s="489"/>
-      <c r="AH3" s="489"/>
-      <c r="AI3" s="489"/>
-      <c r="AJ3" s="489"/>
-      <c r="AK3" s="489"/>
-      <c r="AL3" s="489"/>
-      <c r="AM3" s="489"/>
-      <c r="AN3" s="489"/>
-      <c r="AO3" s="489"/>
-      <c r="AP3" s="489"/>
-      <c r="AQ3" s="489"/>
-      <c r="AR3" s="489"/>
-      <c r="AS3" s="489"/>
-      <c r="AT3" s="489"/>
-      <c r="AU3" s="489"/>
-      <c r="AV3" s="489"/>
-      <c r="AW3" s="489"/>
-      <c r="AX3" s="489"/>
-      <c r="AY3" s="489"/>
-      <c r="AZ3" s="489"/>
-      <c r="BA3" s="489"/>
-      <c r="BB3" s="489"/>
-      <c r="BC3" s="489"/>
-      <c r="BD3" s="489"/>
-      <c r="BE3" s="489"/>
-      <c r="BF3" s="489"/>
-      <c r="BG3" s="489"/>
-      <c r="BH3" s="489"/>
-      <c r="BI3" s="489"/>
-      <c r="BJ3" s="489"/>
-      <c r="BK3" s="489"/>
-      <c r="BL3" s="489"/>
-      <c r="BM3" s="489"/>
-      <c r="BN3" s="489"/>
-      <c r="BO3" s="489"/>
-      <c r="BP3" s="489"/>
-      <c r="BQ3" s="489"/>
-      <c r="BR3" s="489"/>
-      <c r="BS3" s="489"/>
-      <c r="BT3" s="489"/>
-      <c r="BU3" s="489"/>
+      <c r="B3" s="471"/>
+      <c r="C3" s="471"/>
+      <c r="D3" s="471"/>
+      <c r="E3" s="471"/>
+      <c r="F3" s="471"/>
+      <c r="G3" s="471"/>
+      <c r="H3" s="471"/>
+      <c r="I3" s="471"/>
+      <c r="J3" s="471"/>
+      <c r="K3" s="471"/>
+      <c r="L3" s="471"/>
+      <c r="M3" s="471"/>
+      <c r="N3" s="471"/>
+      <c r="O3" s="471"/>
+      <c r="P3" s="471"/>
+      <c r="Q3" s="471"/>
+      <c r="R3" s="471"/>
+      <c r="S3" s="471"/>
+      <c r="T3" s="471"/>
+      <c r="U3" s="471"/>
+      <c r="V3" s="471"/>
+      <c r="W3" s="471"/>
+      <c r="X3" s="471"/>
+      <c r="Y3" s="471"/>
+      <c r="Z3" s="471"/>
+      <c r="AA3" s="471"/>
+      <c r="AB3" s="471"/>
+      <c r="AC3" s="471"/>
+      <c r="AD3" s="471"/>
+      <c r="AE3" s="471"/>
+      <c r="AF3" s="471"/>
+      <c r="AG3" s="471"/>
+      <c r="AH3" s="471"/>
+      <c r="AI3" s="471"/>
+      <c r="AJ3" s="471"/>
+      <c r="AK3" s="471"/>
+      <c r="AL3" s="471"/>
+      <c r="AM3" s="471"/>
+      <c r="AN3" s="471"/>
+      <c r="AO3" s="471"/>
+      <c r="AP3" s="471"/>
+      <c r="AQ3" s="471"/>
+      <c r="AR3" s="471"/>
+      <c r="AS3" s="471"/>
+      <c r="AT3" s="471"/>
+      <c r="AU3" s="471"/>
+      <c r="AV3" s="471"/>
+      <c r="AW3" s="471"/>
+      <c r="AX3" s="471"/>
+      <c r="AY3" s="471"/>
+      <c r="AZ3" s="471"/>
+      <c r="BA3" s="471"/>
+      <c r="BB3" s="471"/>
+      <c r="BC3" s="471"/>
+      <c r="BD3" s="471"/>
+      <c r="BE3" s="471"/>
+      <c r="BF3" s="471"/>
+      <c r="BG3" s="471"/>
+      <c r="BH3" s="471"/>
+      <c r="BI3" s="471"/>
+      <c r="BJ3" s="471"/>
+      <c r="BK3" s="471"/>
+      <c r="BL3" s="471"/>
+      <c r="BM3" s="471"/>
+      <c r="BN3" s="471"/>
+      <c r="BO3" s="471"/>
+      <c r="BP3" s="471"/>
+      <c r="BQ3" s="471"/>
+      <c r="BR3" s="471"/>
+      <c r="BS3" s="471"/>
+      <c r="BT3" s="471"/>
+      <c r="BU3" s="471"/>
       <c r="BV3" s="110"/>
-      <c r="BW3" s="490" t="s">
+      <c r="BW3" s="472" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="490"/>
-      <c r="BY3" s="490"/>
-      <c r="BZ3" s="490"/>
-      <c r="CA3" s="490"/>
-      <c r="CB3" s="491"/>
+      <c r="BX3" s="472"/>
+      <c r="BY3" s="472"/>
+      <c r="BZ3" s="472"/>
+      <c r="CA3" s="472"/>
+      <c r="CB3" s="473"/>
       <c r="CC3" s="71"/>
       <c r="CD3" s="71"/>
       <c r="CE3" s="16" t="s">
@@ -15117,12 +15188,12 @@
       <c r="BT4" s="15"/>
       <c r="BU4" s="15"/>
       <c r="BV4" s="111"/>
-      <c r="BW4" s="491"/>
-      <c r="BX4" s="491"/>
-      <c r="BY4" s="491"/>
-      <c r="BZ4" s="491"/>
-      <c r="CA4" s="491"/>
-      <c r="CB4" s="491"/>
+      <c r="BW4" s="473"/>
+      <c r="BX4" s="473"/>
+      <c r="BY4" s="473"/>
+      <c r="BZ4" s="473"/>
+      <c r="CA4" s="473"/>
+      <c r="CB4" s="473"/>
       <c r="CC4" s="71"/>
       <c r="CD4" s="71"/>
     </row>
@@ -15200,12 +15271,12 @@
       <c r="BT5" s="15"/>
       <c r="BU5" s="15"/>
       <c r="BV5" s="111"/>
-      <c r="BW5" s="491"/>
-      <c r="BX5" s="491"/>
-      <c r="BY5" s="491"/>
-      <c r="BZ5" s="491"/>
-      <c r="CA5" s="491"/>
-      <c r="CB5" s="491"/>
+      <c r="BW5" s="473"/>
+      <c r="BX5" s="473"/>
+      <c r="BY5" s="473"/>
+      <c r="BZ5" s="473"/>
+      <c r="CA5" s="473"/>
+      <c r="CB5" s="473"/>
       <c r="CC5" s="71"/>
       <c r="CD5" s="71"/>
     </row>
@@ -15283,12 +15354,12 @@
       <c r="BT6" s="18"/>
       <c r="BU6" s="18"/>
       <c r="BV6" s="112"/>
-      <c r="BW6" s="490"/>
-      <c r="BX6" s="490"/>
-      <c r="BY6" s="490"/>
-      <c r="BZ6" s="490"/>
-      <c r="CA6" s="490"/>
-      <c r="CB6" s="491"/>
+      <c r="BW6" s="472"/>
+      <c r="BX6" s="472"/>
+      <c r="BY6" s="472"/>
+      <c r="BZ6" s="472"/>
+      <c r="CA6" s="472"/>
+      <c r="CB6" s="473"/>
       <c r="CC6" s="71"/>
       <c r="CD6" s="71"/>
     </row>
@@ -15376,358 +15447,358 @@
       <c r="CD7" s="25"/>
     </row>
     <row r="8" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="404" t="s">
+      <c r="A8" s="451" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="407" t="s">
+      <c r="B8" s="454" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="410" t="s">
+      <c r="C8" s="402" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="413" t="s">
+      <c r="D8" s="457" t="s">
         <v>142</v>
       </c>
-      <c r="E8" s="413" t="s">
+      <c r="E8" s="457" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="492" t="s">
+      <c r="F8" s="474" t="s">
         <v>143</v>
       </c>
-      <c r="G8" s="467" t="s">
+      <c r="G8" s="465" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="495" t="s">
+      <c r="H8" s="477" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="495" t="s">
+      <c r="I8" s="477" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="467" t="s">
+      <c r="J8" s="465" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="498" t="s">
+      <c r="K8" s="480" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="499"/>
-      <c r="M8" s="499"/>
-      <c r="N8" s="499"/>
-      <c r="O8" s="499"/>
-      <c r="P8" s="499"/>
-      <c r="Q8" s="499"/>
-      <c r="R8" s="499"/>
-      <c r="S8" s="499"/>
-      <c r="T8" s="499"/>
-      <c r="U8" s="499"/>
-      <c r="V8" s="499"/>
-      <c r="W8" s="499"/>
-      <c r="X8" s="499"/>
-      <c r="Y8" s="500" t="s">
+      <c r="L8" s="481"/>
+      <c r="M8" s="481"/>
+      <c r="N8" s="481"/>
+      <c r="O8" s="481"/>
+      <c r="P8" s="481"/>
+      <c r="Q8" s="481"/>
+      <c r="R8" s="481"/>
+      <c r="S8" s="481"/>
+      <c r="T8" s="481"/>
+      <c r="U8" s="481"/>
+      <c r="V8" s="481"/>
+      <c r="W8" s="481"/>
+      <c r="X8" s="481"/>
+      <c r="Y8" s="482" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="501"/>
-      <c r="AA8" s="501"/>
-      <c r="AB8" s="501"/>
-      <c r="AC8" s="501"/>
-      <c r="AD8" s="501"/>
-      <c r="AE8" s="501"/>
-      <c r="AF8" s="501"/>
-      <c r="AG8" s="501"/>
-      <c r="AH8" s="501"/>
-      <c r="AI8" s="501"/>
-      <c r="AJ8" s="501"/>
-      <c r="AK8" s="501"/>
-      <c r="AL8" s="501"/>
-      <c r="AM8" s="501"/>
-      <c r="AN8" s="501"/>
-      <c r="AO8" s="502"/>
-      <c r="AP8" s="467" t="s">
+      <c r="Z8" s="483"/>
+      <c r="AA8" s="483"/>
+      <c r="AB8" s="483"/>
+      <c r="AC8" s="483"/>
+      <c r="AD8" s="483"/>
+      <c r="AE8" s="483"/>
+      <c r="AF8" s="483"/>
+      <c r="AG8" s="483"/>
+      <c r="AH8" s="483"/>
+      <c r="AI8" s="483"/>
+      <c r="AJ8" s="483"/>
+      <c r="AK8" s="483"/>
+      <c r="AL8" s="483"/>
+      <c r="AM8" s="483"/>
+      <c r="AN8" s="483"/>
+      <c r="AO8" s="484"/>
+      <c r="AP8" s="465" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="467" t="s">
+      <c r="AQ8" s="465" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="467" t="s">
+      <c r="AR8" s="465" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="467" t="s">
+      <c r="AS8" s="465" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="467" t="s">
+      <c r="AT8" s="465" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="467" t="s">
+      <c r="AU8" s="465" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="410" t="s">
+      <c r="AV8" s="402" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="410" t="s">
+      <c r="AW8" s="402" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="410" t="s">
+      <c r="AX8" s="402" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="431" t="s">
+      <c r="AY8" s="405" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="432"/>
-      <c r="BA8" s="432"/>
-      <c r="BB8" s="432"/>
-      <c r="BC8" s="432"/>
-      <c r="BD8" s="432"/>
-      <c r="BE8" s="432"/>
-      <c r="BF8" s="432"/>
-      <c r="BG8" s="432"/>
-      <c r="BH8" s="432"/>
-      <c r="BI8" s="432"/>
-      <c r="BJ8" s="432"/>
-      <c r="BK8" s="432"/>
-      <c r="BL8" s="432"/>
-      <c r="BM8" s="432"/>
-      <c r="BN8" s="432"/>
-      <c r="BO8" s="432"/>
-      <c r="BP8" s="433"/>
-      <c r="BQ8" s="434" t="s">
+      <c r="AZ8" s="406"/>
+      <c r="BA8" s="406"/>
+      <c r="BB8" s="406"/>
+      <c r="BC8" s="406"/>
+      <c r="BD8" s="406"/>
+      <c r="BE8" s="406"/>
+      <c r="BF8" s="406"/>
+      <c r="BG8" s="406"/>
+      <c r="BH8" s="406"/>
+      <c r="BI8" s="406"/>
+      <c r="BJ8" s="406"/>
+      <c r="BK8" s="406"/>
+      <c r="BL8" s="406"/>
+      <c r="BM8" s="406"/>
+      <c r="BN8" s="406"/>
+      <c r="BO8" s="406"/>
+      <c r="BP8" s="407"/>
+      <c r="BQ8" s="433" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="435"/>
-      <c r="BS8" s="436" t="s">
+      <c r="BR8" s="442"/>
+      <c r="BS8" s="410" t="s">
         <v>144</v>
       </c>
-      <c r="BT8" s="436" t="s">
+      <c r="BT8" s="410" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="434" t="s">
+      <c r="BU8" s="433" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="114"/>
-      <c r="BW8" s="457" t="s">
+      <c r="BW8" s="436" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="443" t="s">
+      <c r="BX8" s="421" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="444"/>
-      <c r="BZ8" s="444"/>
-      <c r="CA8" s="445"/>
-      <c r="CB8" s="452" t="s">
+      <c r="BY8" s="422"/>
+      <c r="BZ8" s="422"/>
+      <c r="CA8" s="423"/>
+      <c r="CB8" s="430" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="384" t="s">
+      <c r="CC8" s="326" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="384" t="s">
+      <c r="CD8" s="326" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="27"/>
       <c r="CI8" s="28"/>
     </row>
     <row r="9" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="405"/>
-      <c r="B9" s="408"/>
-      <c r="C9" s="411"/>
-      <c r="D9" s="414"/>
-      <c r="E9" s="414"/>
-      <c r="F9" s="493"/>
-      <c r="G9" s="468"/>
-      <c r="H9" s="496"/>
-      <c r="I9" s="496"/>
-      <c r="J9" s="468"/>
-      <c r="K9" s="476" t="s">
+      <c r="A9" s="452"/>
+      <c r="B9" s="455"/>
+      <c r="C9" s="403"/>
+      <c r="D9" s="458"/>
+      <c r="E9" s="458"/>
+      <c r="F9" s="475"/>
+      <c r="G9" s="466"/>
+      <c r="H9" s="478"/>
+      <c r="I9" s="478"/>
+      <c r="J9" s="466"/>
+      <c r="K9" s="468" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="476" t="s">
+      <c r="L9" s="468" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="476" t="s">
+      <c r="M9" s="468" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="476" t="s">
+      <c r="N9" s="468" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="476" t="s">
+      <c r="O9" s="468" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="476" t="s">
+      <c r="P9" s="468" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="476" t="s">
+      <c r="Q9" s="468" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="476" t="s">
+      <c r="R9" s="468" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="476" t="s">
+      <c r="S9" s="468" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="476" t="s">
+      <c r="T9" s="468" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="476" t="s">
+      <c r="U9" s="468" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="485" t="s">
+      <c r="V9" s="493" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="486"/>
-      <c r="X9" s="476" t="s">
+      <c r="W9" s="494"/>
+      <c r="X9" s="468" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="482" t="s">
+      <c r="Y9" s="490" t="s">
         <v>47</v>
       </c>
-      <c r="Z9" s="482" t="s">
+      <c r="Z9" s="490" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="482" t="s">
+      <c r="AA9" s="490" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="482" t="s">
+      <c r="AB9" s="490" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="479" t="s">
+      <c r="AC9" s="487" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="479" t="s">
+      <c r="AD9" s="487" t="s">
         <v>145</v>
       </c>
-      <c r="AE9" s="479" t="s">
+      <c r="AE9" s="487" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="479" t="s">
+      <c r="AF9" s="487" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="482" t="s">
+      <c r="AG9" s="490" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="479" t="s">
+      <c r="AH9" s="487" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="479" t="s">
+      <c r="AI9" s="487" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="482" t="s">
+      <c r="AJ9" s="490" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="460" t="s">
+      <c r="AK9" s="418" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="410" t="s">
+      <c r="AL9" s="402" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="482" t="s">
+      <c r="AM9" s="490" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="342" t="s">
+      <c r="AN9" s="329" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="410" t="s">
+      <c r="AO9" s="402" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="468"/>
-      <c r="AQ9" s="468"/>
-      <c r="AR9" s="468"/>
-      <c r="AS9" s="468"/>
-      <c r="AT9" s="468"/>
-      <c r="AU9" s="468"/>
-      <c r="AV9" s="411"/>
-      <c r="AW9" s="411"/>
-      <c r="AX9" s="411"/>
-      <c r="AY9" s="431" t="s">
+      <c r="AP9" s="466"/>
+      <c r="AQ9" s="466"/>
+      <c r="AR9" s="466"/>
+      <c r="AS9" s="466"/>
+      <c r="AT9" s="466"/>
+      <c r="AU9" s="466"/>
+      <c r="AV9" s="403"/>
+      <c r="AW9" s="403"/>
+      <c r="AX9" s="403"/>
+      <c r="AY9" s="405" t="s">
         <v>64</v>
       </c>
-      <c r="AZ9" s="432"/>
-      <c r="BA9" s="432"/>
-      <c r="BB9" s="432"/>
-      <c r="BC9" s="432"/>
-      <c r="BD9" s="432"/>
-      <c r="BE9" s="432"/>
-      <c r="BF9" s="432"/>
-      <c r="BG9" s="432"/>
-      <c r="BH9" s="432"/>
-      <c r="BI9" s="432"/>
-      <c r="BJ9" s="433"/>
-      <c r="BK9" s="431" t="s">
+      <c r="AZ9" s="406"/>
+      <c r="BA9" s="406"/>
+      <c r="BB9" s="406"/>
+      <c r="BC9" s="406"/>
+      <c r="BD9" s="406"/>
+      <c r="BE9" s="406"/>
+      <c r="BF9" s="406"/>
+      <c r="BG9" s="406"/>
+      <c r="BH9" s="406"/>
+      <c r="BI9" s="406"/>
+      <c r="BJ9" s="407"/>
+      <c r="BK9" s="405" t="s">
         <v>65</v>
       </c>
-      <c r="BL9" s="432"/>
-      <c r="BM9" s="432"/>
-      <c r="BN9" s="432"/>
-      <c r="BO9" s="432"/>
-      <c r="BP9" s="433"/>
-      <c r="BQ9" s="437" t="s">
+      <c r="BL9" s="406"/>
+      <c r="BM9" s="406"/>
+      <c r="BN9" s="406"/>
+      <c r="BO9" s="406"/>
+      <c r="BP9" s="407"/>
+      <c r="BQ9" s="408" t="s">
         <v>66</v>
       </c>
-      <c r="BR9" s="437" t="s">
+      <c r="BR9" s="408" t="s">
         <v>67</v>
       </c>
-      <c r="BS9" s="437"/>
-      <c r="BT9" s="437"/>
-      <c r="BU9" s="455"/>
+      <c r="BS9" s="408"/>
+      <c r="BT9" s="408"/>
+      <c r="BU9" s="434"/>
       <c r="BV9" s="114"/>
-      <c r="BW9" s="458"/>
-      <c r="BX9" s="446"/>
-      <c r="BY9" s="447"/>
-      <c r="BZ9" s="447"/>
-      <c r="CA9" s="448"/>
-      <c r="CB9" s="453"/>
-      <c r="CC9" s="385"/>
-      <c r="CD9" s="385"/>
+      <c r="BW9" s="437"/>
+      <c r="BX9" s="424"/>
+      <c r="BY9" s="425"/>
+      <c r="BZ9" s="425"/>
+      <c r="CA9" s="426"/>
+      <c r="CB9" s="431"/>
+      <c r="CC9" s="327"/>
+      <c r="CD9" s="327"/>
       <c r="CH9" s="27"/>
       <c r="CI9" s="28"/>
     </row>
     <row r="10" spans="1:87" s="29" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="405"/>
-      <c r="B10" s="408"/>
-      <c r="C10" s="411"/>
-      <c r="D10" s="414"/>
-      <c r="E10" s="414"/>
-      <c r="F10" s="493"/>
-      <c r="G10" s="468"/>
-      <c r="H10" s="496"/>
-      <c r="I10" s="496"/>
-      <c r="J10" s="468"/>
-      <c r="K10" s="477"/>
-      <c r="L10" s="477"/>
-      <c r="M10" s="477"/>
-      <c r="N10" s="477"/>
-      <c r="O10" s="477"/>
-      <c r="P10" s="477"/>
-      <c r="Q10" s="477"/>
-      <c r="R10" s="477"/>
-      <c r="S10" s="477"/>
-      <c r="T10" s="477"/>
-      <c r="U10" s="477"/>
-      <c r="V10" s="487"/>
-      <c r="W10" s="488"/>
-      <c r="X10" s="477"/>
-      <c r="Y10" s="483"/>
-      <c r="Z10" s="483"/>
-      <c r="AA10" s="483"/>
-      <c r="AB10" s="483"/>
-      <c r="AC10" s="480"/>
-      <c r="AD10" s="480"/>
-      <c r="AE10" s="480"/>
-      <c r="AF10" s="480"/>
-      <c r="AG10" s="483"/>
-      <c r="AH10" s="480"/>
-      <c r="AI10" s="480"/>
-      <c r="AJ10" s="483"/>
-      <c r="AK10" s="461"/>
-      <c r="AL10" s="411"/>
-      <c r="AM10" s="483"/>
-      <c r="AN10" s="343"/>
-      <c r="AO10" s="411"/>
-      <c r="AP10" s="468"/>
-      <c r="AQ10" s="468"/>
-      <c r="AR10" s="468"/>
-      <c r="AS10" s="468"/>
-      <c r="AT10" s="468"/>
-      <c r="AU10" s="468"/>
-      <c r="AV10" s="411"/>
-      <c r="AW10" s="411"/>
-      <c r="AX10" s="411"/>
+      <c r="A10" s="452"/>
+      <c r="B10" s="455"/>
+      <c r="C10" s="403"/>
+      <c r="D10" s="458"/>
+      <c r="E10" s="458"/>
+      <c r="F10" s="475"/>
+      <c r="G10" s="466"/>
+      <c r="H10" s="478"/>
+      <c r="I10" s="478"/>
+      <c r="J10" s="466"/>
+      <c r="K10" s="469"/>
+      <c r="L10" s="469"/>
+      <c r="M10" s="469"/>
+      <c r="N10" s="469"/>
+      <c r="O10" s="469"/>
+      <c r="P10" s="469"/>
+      <c r="Q10" s="469"/>
+      <c r="R10" s="469"/>
+      <c r="S10" s="469"/>
+      <c r="T10" s="469"/>
+      <c r="U10" s="469"/>
+      <c r="V10" s="495"/>
+      <c r="W10" s="496"/>
+      <c r="X10" s="469"/>
+      <c r="Y10" s="491"/>
+      <c r="Z10" s="491"/>
+      <c r="AA10" s="491"/>
+      <c r="AB10" s="491"/>
+      <c r="AC10" s="488"/>
+      <c r="AD10" s="488"/>
+      <c r="AE10" s="488"/>
+      <c r="AF10" s="488"/>
+      <c r="AG10" s="491"/>
+      <c r="AH10" s="488"/>
+      <c r="AI10" s="488"/>
+      <c r="AJ10" s="491"/>
+      <c r="AK10" s="419"/>
+      <c r="AL10" s="403"/>
+      <c r="AM10" s="491"/>
+      <c r="AN10" s="330"/>
+      <c r="AO10" s="403"/>
+      <c r="AP10" s="466"/>
+      <c r="AQ10" s="466"/>
+      <c r="AR10" s="466"/>
+      <c r="AS10" s="466"/>
+      <c r="AT10" s="466"/>
+      <c r="AU10" s="466"/>
+      <c r="AV10" s="403"/>
+      <c r="AW10" s="403"/>
+      <c r="AX10" s="403"/>
       <c r="AY10" s="101" t="s">
         <v>68</v>
       </c>
@@ -15737,123 +15808,123 @@
       <c r="BA10" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="BB10" s="474" t="s">
+      <c r="BB10" s="497" t="s">
         <v>71</v>
       </c>
-      <c r="BC10" s="465" t="s">
+      <c r="BC10" s="485" t="s">
         <v>72</v>
       </c>
-      <c r="BD10" s="465" t="s">
+      <c r="BD10" s="485" t="s">
         <v>73</v>
       </c>
-      <c r="BE10" s="465" t="s">
+      <c r="BE10" s="485" t="s">
         <v>146</v>
       </c>
-      <c r="BF10" s="465" t="s">
+      <c r="BF10" s="485" t="s">
         <v>75</v>
       </c>
-      <c r="BG10" s="465" t="s">
+      <c r="BG10" s="485" t="s">
         <v>76</v>
       </c>
-      <c r="BH10" s="465" t="s">
+      <c r="BH10" s="485" t="s">
         <v>77</v>
       </c>
-      <c r="BI10" s="465" t="s">
+      <c r="BI10" s="485" t="s">
         <v>80</v>
       </c>
-      <c r="BJ10" s="472" t="s">
+      <c r="BJ10" s="501" t="s">
         <v>81</v>
       </c>
-      <c r="BK10" s="465" t="s">
+      <c r="BK10" s="485" t="s">
         <v>82</v>
       </c>
-      <c r="BL10" s="470" t="s">
+      <c r="BL10" s="499" t="s">
         <v>83</v>
       </c>
-      <c r="BM10" s="465" t="s">
+      <c r="BM10" s="485" t="s">
         <v>84</v>
       </c>
-      <c r="BN10" s="470" t="s">
+      <c r="BN10" s="499" t="s">
         <v>85</v>
       </c>
-      <c r="BO10" s="470" t="s">
+      <c r="BO10" s="499" t="s">
         <v>147</v>
       </c>
-      <c r="BP10" s="436" t="s">
+      <c r="BP10" s="410" t="s">
         <v>86</v>
       </c>
-      <c r="BQ10" s="437"/>
-      <c r="BR10" s="437"/>
-      <c r="BS10" s="437"/>
-      <c r="BT10" s="437"/>
-      <c r="BU10" s="455"/>
+      <c r="BQ10" s="408"/>
+      <c r="BR10" s="408"/>
+      <c r="BS10" s="408"/>
+      <c r="BT10" s="408"/>
+      <c r="BU10" s="434"/>
       <c r="BV10" s="114"/>
-      <c r="BW10" s="459"/>
-      <c r="BX10" s="449"/>
-      <c r="BY10" s="450"/>
-      <c r="BZ10" s="450"/>
-      <c r="CA10" s="451"/>
-      <c r="CB10" s="454"/>
-      <c r="CC10" s="386"/>
-      <c r="CD10" s="386"/>
+      <c r="BW10" s="438"/>
+      <c r="BX10" s="427"/>
+      <c r="BY10" s="428"/>
+      <c r="BZ10" s="428"/>
+      <c r="CA10" s="429"/>
+      <c r="CB10" s="432"/>
+      <c r="CC10" s="328"/>
+      <c r="CD10" s="328"/>
       <c r="CH10" s="27"/>
       <c r="CI10" s="28"/>
     </row>
     <row r="11" spans="1:87" s="29" customFormat="1" ht="28">
-      <c r="A11" s="406"/>
-      <c r="B11" s="409"/>
-      <c r="C11" s="412"/>
-      <c r="D11" s="415"/>
-      <c r="E11" s="415"/>
-      <c r="F11" s="494"/>
-      <c r="G11" s="469"/>
-      <c r="H11" s="497"/>
-      <c r="I11" s="497"/>
-      <c r="J11" s="469"/>
-      <c r="K11" s="478"/>
-      <c r="L11" s="478"/>
-      <c r="M11" s="478"/>
-      <c r="N11" s="478"/>
-      <c r="O11" s="478"/>
-      <c r="P11" s="478"/>
-      <c r="Q11" s="478"/>
-      <c r="R11" s="478"/>
-      <c r="S11" s="478"/>
-      <c r="T11" s="478"/>
-      <c r="U11" s="478"/>
+      <c r="A11" s="453"/>
+      <c r="B11" s="456"/>
+      <c r="C11" s="404"/>
+      <c r="D11" s="459"/>
+      <c r="E11" s="459"/>
+      <c r="F11" s="476"/>
+      <c r="G11" s="467"/>
+      <c r="H11" s="479"/>
+      <c r="I11" s="479"/>
+      <c r="J11" s="467"/>
+      <c r="K11" s="470"/>
+      <c r="L11" s="470"/>
+      <c r="M11" s="470"/>
+      <c r="N11" s="470"/>
+      <c r="O11" s="470"/>
+      <c r="P11" s="470"/>
+      <c r="Q11" s="470"/>
+      <c r="R11" s="470"/>
+      <c r="S11" s="470"/>
+      <c r="T11" s="470"/>
+      <c r="U11" s="470"/>
       <c r="V11" s="30" t="s">
         <v>87</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="X11" s="478"/>
-      <c r="Y11" s="484"/>
-      <c r="Z11" s="484"/>
-      <c r="AA11" s="484"/>
-      <c r="AB11" s="484"/>
-      <c r="AC11" s="481"/>
-      <c r="AD11" s="481"/>
-      <c r="AE11" s="481"/>
-      <c r="AF11" s="481"/>
-      <c r="AG11" s="484"/>
-      <c r="AH11" s="481"/>
-      <c r="AI11" s="481"/>
-      <c r="AJ11" s="484"/>
-      <c r="AK11" s="462"/>
-      <c r="AL11" s="412"/>
-      <c r="AM11" s="484"/>
-      <c r="AN11" s="344"/>
-      <c r="AO11" s="412"/>
-      <c r="AP11" s="469"/>
-      <c r="AQ11" s="469"/>
-      <c r="AR11" s="469"/>
-      <c r="AS11" s="469"/>
-      <c r="AT11" s="469"/>
-      <c r="AU11" s="469"/>
-      <c r="AV11" s="412"/>
-      <c r="AW11" s="412"/>
-      <c r="AX11" s="412"/>
+      <c r="X11" s="470"/>
+      <c r="Y11" s="492"/>
+      <c r="Z11" s="492"/>
+      <c r="AA11" s="492"/>
+      <c r="AB11" s="492"/>
+      <c r="AC11" s="489"/>
+      <c r="AD11" s="489"/>
+      <c r="AE11" s="489"/>
+      <c r="AF11" s="489"/>
+      <c r="AG11" s="492"/>
+      <c r="AH11" s="489"/>
+      <c r="AI11" s="489"/>
+      <c r="AJ11" s="492"/>
+      <c r="AK11" s="420"/>
+      <c r="AL11" s="404"/>
+      <c r="AM11" s="492"/>
+      <c r="AN11" s="331"/>
+      <c r="AO11" s="404"/>
+      <c r="AP11" s="467"/>
+      <c r="AQ11" s="467"/>
+      <c r="AR11" s="467"/>
+      <c r="AS11" s="467"/>
+      <c r="AT11" s="467"/>
+      <c r="AU11" s="467"/>
+      <c r="AV11" s="404"/>
+      <c r="AW11" s="404"/>
+      <c r="AX11" s="404"/>
       <c r="AY11" s="102" t="s">
         <v>89</v>
       </c>
@@ -15863,28 +15934,28 @@
       <c r="BA11" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="BB11" s="475"/>
-      <c r="BC11" s="466"/>
-      <c r="BD11" s="466"/>
-      <c r="BE11" s="466"/>
-      <c r="BF11" s="466"/>
-      <c r="BG11" s="466"/>
-      <c r="BH11" s="466"/>
-      <c r="BI11" s="466"/>
-      <c r="BJ11" s="473"/>
-      <c r="BK11" s="466"/>
-      <c r="BL11" s="471"/>
-      <c r="BM11" s="466"/>
-      <c r="BN11" s="471"/>
-      <c r="BO11" s="471"/>
-      <c r="BP11" s="438"/>
-      <c r="BQ11" s="438"/>
-      <c r="BR11" s="438"/>
-      <c r="BS11" s="438"/>
-      <c r="BT11" s="438"/>
-      <c r="BU11" s="456"/>
+      <c r="BB11" s="498"/>
+      <c r="BC11" s="486"/>
+      <c r="BD11" s="486"/>
+      <c r="BE11" s="486"/>
+      <c r="BF11" s="486"/>
+      <c r="BG11" s="486"/>
+      <c r="BH11" s="486"/>
+      <c r="BI11" s="486"/>
+      <c r="BJ11" s="502"/>
+      <c r="BK11" s="486"/>
+      <c r="BL11" s="500"/>
+      <c r="BM11" s="486"/>
+      <c r="BN11" s="500"/>
+      <c r="BO11" s="500"/>
+      <c r="BP11" s="409"/>
+      <c r="BQ11" s="409"/>
+      <c r="BR11" s="409"/>
+      <c r="BS11" s="409"/>
+      <c r="BT11" s="409"/>
+      <c r="BU11" s="435"/>
       <c r="BV11" s="114"/>
-      <c r="BW11" s="459"/>
+      <c r="BW11" s="438"/>
       <c r="BX11" s="72" t="s">
         <v>92</v>
       </c>
@@ -15897,9 +15968,9 @@
       <c r="CA11" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="CB11" s="454"/>
-      <c r="CC11" s="386"/>
-      <c r="CD11" s="386"/>
+      <c r="CB11" s="432"/>
+      <c r="CC11" s="328"/>
+      <c r="CD11" s="328"/>
       <c r="CE11" s="11"/>
       <c r="CF11" s="31"/>
       <c r="CH11" s="27"/>
@@ -16459,7 +16530,7 @@
       <c r="BI14" s="81"/>
       <c r="BJ14" s="81">
         <f t="shared" si="4"/>
-        <v>4630005</v>
+        <v>2426916</v>
       </c>
       <c r="BK14" s="81">
         <f t="shared" si="4"/>
@@ -16517,8 +16588,8 @@
       <c r="D15" s="90" t="s">
         <v>99</v>
       </c>
-      <c r="E15" s="123" t="s">
-        <v>114</v>
+      <c r="E15" s="503" t="s">
+        <v>100</v>
       </c>
       <c r="F15" s="124" t="s">
         <v>101</v>
@@ -16666,23 +16737,23 @@
         <v>95200</v>
       </c>
       <c r="BF15" s="85">
-        <f>AM15+IF(AR15&gt;="730000",730000,AR15)+IF(((AV15-AM15-IF(AR15&gt;="730000",730000,AR15)-AS15)*15%-AS15)&gt;"0",((AV15-AM15-IF(AR15&gt;="730000",730000,AR15)-AS15)*15%-AS15),0)</f>
-        <v>0</v>
+        <f t="shared" ref="BF15:BF21" si="10">AM15+IF(AR15&gt;="730000",730000,AR15)+IF(((AV15-AM15-IF(AR15&gt;="730000",730000,AR15)-AS15)*15%-AS15)&gt;0,((AV15-AM15-IF(AR15&gt;="730000",730000,AR15)-AS15)*15%-AS15),0)</f>
+        <v>4846153.8461538469</v>
       </c>
       <c r="BG15" s="85">
         <f>AV15-BF15+AW15</f>
-        <v>32307692.307692312</v>
+        <v>27461538.461538464</v>
       </c>
       <c r="BH15" s="85">
         <v>3</v>
       </c>
       <c r="BI15" s="85">
         <f>BG15-BB15-BC15+BD15-BH15*4400000-IF(E15="CT",11000000,0)</f>
-        <v>18026192.307692312</v>
+        <v>2180038.4615384638</v>
       </c>
       <c r="BJ15" s="84">
         <f>IF(BI15&gt;0,ROUND(IF(BI15&gt;=80000000,BI15*35%-9850000,IF(BI15&gt;=52000000,BI15*30%-5850000,IF(BI15&gt;=32000000,BI15*25%-3250000,IF(BI15&gt;=18000000,BI15*20%-1650000,IF(BI15&gt;=10000000,BI15*15%-750000,IF(BI15&gt;5000000,BI15*10%-250000,BI15*5%)))))),0),0)</f>
-        <v>1955238</v>
+        <v>109002</v>
       </c>
       <c r="BK15" s="85"/>
       <c r="BL15" s="85"/>
@@ -16796,39 +16867,39 @@
         <v>0</v>
       </c>
       <c r="Y16" s="91">
-        <f t="shared" ref="Y16:Y17" si="10">G16*(K16+L16)/26</f>
+        <f t="shared" ref="Y16:Y17" si="11">G16*(K16+L16)/26</f>
         <v>3424615.3846153845</v>
       </c>
       <c r="Z16" s="91">
-        <f t="shared" ref="Z16:Z17" si="11">M16*G16/26</f>
+        <f t="shared" ref="Z16:Z17" si="12">M16*G16/26</f>
         <v>163076.92307692306</v>
       </c>
       <c r="AA16" s="91">
-        <f t="shared" ref="AA16:AA17" si="12">G16*N16/26</f>
+        <f t="shared" ref="AA16:AA17" si="13">G16*N16/26</f>
         <v>0</v>
       </c>
       <c r="AB16" s="91">
-        <f t="shared" ref="AB16:AB17" si="13">G16*O16/26</f>
+        <f t="shared" ref="AB16:AB17" si="14">G16*O16/26</f>
         <v>652307.69230769225</v>
       </c>
       <c r="AC16" s="91">
-        <f t="shared" ref="AC16:AC17" si="14">G16*P16*150%/26</f>
+        <f t="shared" ref="AC16:AC17" si="15">G16*P16*150%/26</f>
         <v>0</v>
       </c>
       <c r="AD16" s="91">
-        <f t="shared" ref="AD16:AD17" si="15">G16*Q16/26*200%</f>
+        <f t="shared" ref="AD16:AD17" si="16">G16*Q16/26*200%</f>
         <v>0</v>
       </c>
       <c r="AE16" s="91">
-        <f t="shared" ref="AE16:AE17" si="16">G16*R16/26*300%</f>
+        <f t="shared" ref="AE16:AE17" si="17">G16*R16/26*300%</f>
         <v>0</v>
       </c>
       <c r="AF16" s="91">
-        <f t="shared" ref="AF16:AF17" si="17">IF(F16="LT",0,(G16+H16)/26*S16*30%)</f>
+        <f t="shared" ref="AF16:AF17" si="18">IF(F16="LT",0,(G16+H16)/26*S16*30%)</f>
         <v>0</v>
       </c>
       <c r="AG16" s="91">
-        <f t="shared" ref="AG16:AG17" si="18">T16*G16/23/8</f>
+        <f t="shared" ref="AG16:AG17" si="19">T16*G16/23/8</f>
         <v>0</v>
       </c>
       <c r="AH16" s="91">
@@ -16836,7 +16907,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="91">
-        <f t="shared" ref="AI16:AI17" si="19">G16*V16/26</f>
+        <f t="shared" ref="AI16:AI17" si="20">G16*V16/26</f>
         <v>0</v>
       </c>
       <c r="AJ16" s="91"/>
@@ -16850,11 +16921,11 @@
         <v>0</v>
       </c>
       <c r="AN16" s="91">
-        <f t="shared" ref="AN16:AN17" si="20">H16/26*K16</f>
+        <f t="shared" ref="AN16:AN17" si="21">H16/26*K16</f>
         <v>315000</v>
       </c>
       <c r="AO16" s="91">
-        <f t="shared" ref="AO16:AO17" si="21">IF(F16="LN",I16*(K16+L16)/26+(H16+I16)*50%*M16/26+IF(F16="LT",BW16*O16/26-AB16,0)+MAX($G16*P16/26*150%,P16*$BW16/26)-AC16+MAX($G16*Q16/26*200%,Q16*$BW16/26)-AD16+MAX($G16*R16/26*300%,R16*$BW16/26)-AE16+BW16*S16/26-AF16+AH16-AG16,I16-I16*($CF$3-K16-L16)/26+(H16+I16)*50%*M16/26+IF(F16="LT",BW16*O16/26-AB16,0)+MAX($G16*P16/26*150%,P16*$BW16/26)-AC16+MAX($G16*Q16/26*200%,Q16*$BW16/26)-AD16+MAX($G16*R16/26*300%,R16*$BW16/26)-AE16+BW16*S16/26-AF16+AH16-AG16+(G16-G16*($CF$3-K16-L16)/26-Y16)+(H16-H16*($CF$3-K16-L16)/26-AN16))</f>
+        <f t="shared" ref="AO16:AO17" si="22">IF(F16="LN",I16*(K16+L16)/26+(H16+I16)*50%*M16/26+IF(F16="LT",BW16*O16/26-AB16,0)+MAX($G16*P16/26*150%,P16*$BW16/26)-AC16+MAX($G16*Q16/26*200%,Q16*$BW16/26)-AD16+MAX($G16*R16/26*300%,R16*$BW16/26)-AE16+BW16*S16/26-AF16+AH16-AG16,I16-I16*($CF$3-K16-L16)/26+(H16+I16)*50%*M16/26+IF(F16="LT",BW16*O16/26-AB16,0)+MAX($G16*P16/26*150%,P16*$BW16/26)-AC16+MAX($G16*Q16/26*200%,Q16*$BW16/26)-AD16+MAX($G16*R16/26*300%,R16*$BW16/26)-AE16+BW16*S16/26-AF16+AH16-AG16+(G16-G16*($CF$3-K16-L16)/26-Y16)+(H16-H16*($CF$3-K16-L16)/26-AN16))</f>
         <v>17584230.769230772</v>
       </c>
       <c r="AP16" s="91"/>
@@ -16864,7 +16935,7 @@
       <c r="AT16" s="91"/>
       <c r="AU16" s="91"/>
       <c r="AV16" s="94">
-        <f t="shared" ref="AV16:AV17" si="22">Y16+Z16+AA16+AB16+AC16+AD16+AE16+AF16+AG16+AI16+AJ16+AK16+AL16+AM16+AN16+AO16+AP16-AQ16+AR16+AS16+AT16+AU16</f>
+        <f t="shared" ref="AV16:AV17" si="23">Y16+Z16+AA16+AB16+AC16+AD16+AE16+AF16+AG16+AI16+AJ16+AK16+AL16+AM16+AN16+AO16+AP16-AQ16+AR16+AS16+AT16+AU16</f>
         <v>22139230.769230772</v>
       </c>
       <c r="AW16" s="94"/>
@@ -16872,15 +16943,15 @@
         <v>102</v>
       </c>
       <c r="AY16" s="85">
-        <f t="shared" ref="AY16:AY21" si="23">ROUND(IF($AX16="x",($G16+$H16)*AY$11,0),0)</f>
+        <f t="shared" ref="AY16:AY21" si="24">ROUND(IF($AX16="x",($G16+$H16)*AY$11,0),0)</f>
         <v>740800</v>
       </c>
       <c r="AZ16" s="85">
-        <f t="shared" ref="AZ16:BA21" si="24">ROUND(IF($AX16="x",($G16+$H16)*AZ$11,0),0)</f>
+        <f t="shared" ref="AZ16:BA21" si="25">ROUND(IF($AX16="x",($G16+$H16)*AZ$11,0),0)</f>
         <v>138900</v>
       </c>
       <c r="BA16" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>92600</v>
       </c>
       <c r="BB16" s="85">
@@ -16890,25 +16961,25 @@
       <c r="BC16" s="85"/>
       <c r="BD16" s="85"/>
       <c r="BE16" s="85">
-        <f t="shared" ref="BE16:BE17" si="25">IF(G16*1%&gt;=234000,234000,G16*1%)</f>
+        <f t="shared" ref="BE16:BE17" si="26">IF(G16*1%&gt;=234000,234000,G16*1%)</f>
         <v>84800</v>
       </c>
       <c r="BF16" s="85">
-        <f t="shared" ref="BF16:BF17" si="26">AM16+IF(AR16&gt;="730000",730000,AR16)+IF(((AV16-AM16-IF(AR16&gt;="730000",730000,AR16)-AS16)*15%-AS16)&gt;"0",((AV16-AM16-IF(AR16&gt;="730000",730000,AR16)-AS16)*15%-AS16),0)</f>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>3320884.6153846155</v>
       </c>
       <c r="BG16" s="85">
         <f t="shared" ref="BG16:BG17" si="27">AV16-BF16+AW16</f>
-        <v>22139230.769230772</v>
+        <v>18818346.153846156</v>
       </c>
       <c r="BH16" s="85"/>
       <c r="BI16" s="85">
         <f t="shared" ref="BI16:BI17" si="28">BG16-BB16-BC16+BD16-BH16*4400000-IF(E16="CT",11000000,0)</f>
-        <v>10166930.769230772</v>
+        <v>6846046.1538461559</v>
       </c>
       <c r="BJ16" s="84">
         <f t="shared" ref="BJ16:BJ17" si="29">IF(BI16&gt;0,ROUND(IF(BI16&gt;=80000000,BI16*35%-9850000,IF(BI16&gt;=52000000,BI16*30%-5850000,IF(BI16&gt;=32000000,BI16*25%-3250000,IF(BI16&gt;=18000000,BI16*20%-1650000,IF(BI16&gt;=10000000,BI16*15%-750000,IF(BI16&gt;5000000,BI16*10%-250000,BI16*5%)))))),0),0)</f>
-        <v>775040</v>
+        <v>434605</v>
       </c>
       <c r="BK16" s="85"/>
       <c r="BL16" s="85"/>
@@ -17023,39 +17094,39 @@
         <v>0</v>
       </c>
       <c r="Y17" s="91">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3308461.5384615385</v>
       </c>
       <c r="Z17" s="91">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AA17" s="91">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AB17" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>601538.4615384615</v>
       </c>
       <c r="AC17" s="91">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AD17" s="91">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE17" s="91">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>3609230.769230769</v>
       </c>
       <c r="AF17" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AG17" s="91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH17" s="91">
@@ -17063,7 +17134,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="91">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ17" s="91"/>
@@ -17077,11 +17148,11 @@
         <v>0</v>
       </c>
       <c r="AN17" s="91">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>126923.07692307694</v>
       </c>
       <c r="AO17" s="91">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>20969230.769230772</v>
       </c>
       <c r="AP17" s="91"/>
@@ -17091,7 +17162,7 @@
       <c r="AT17" s="91"/>
       <c r="AU17" s="91"/>
       <c r="AV17" s="94">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>28615384.615384616</v>
       </c>
       <c r="AW17" s="94"/>
@@ -17099,15 +17170,15 @@
         <v>102</v>
       </c>
       <c r="AY17" s="85">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>649600</v>
       </c>
       <c r="AZ17" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>121800</v>
       </c>
       <c r="BA17" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>81200</v>
       </c>
       <c r="BB17" s="85">
@@ -17117,25 +17188,25 @@
       <c r="BC17" s="85"/>
       <c r="BD17" s="85"/>
       <c r="BE17" s="85">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>78200</v>
       </c>
       <c r="BF17" s="85">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>4292307.692307692</v>
       </c>
       <c r="BG17" s="85">
         <f t="shared" si="27"/>
-        <v>28615384.615384616</v>
+        <v>24323076.923076924</v>
       </c>
       <c r="BH17" s="85"/>
       <c r="BI17" s="85">
         <f t="shared" si="28"/>
-        <v>16762784.615384616</v>
+        <v>12470476.923076924</v>
       </c>
       <c r="BJ17" s="84">
         <f t="shared" si="29"/>
-        <v>1764418</v>
+        <v>1120572</v>
       </c>
       <c r="BK17" s="85"/>
       <c r="BL17" s="85"/>
@@ -17328,15 +17399,15 @@
         <v>102</v>
       </c>
       <c r="AY18" s="85">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>621600</v>
       </c>
       <c r="AZ18" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>116550</v>
       </c>
       <c r="BA18" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>77700</v>
       </c>
       <c r="BB18" s="85">
@@ -17350,21 +17421,21 @@
         <v>69900</v>
       </c>
       <c r="BF18" s="85">
-        <f t="shared" ref="BF18:BF19" si="49">AM18+IF(AR18&gt;="730000",730000,AR18)+IF(((AV18-AM18-IF(AR18&gt;="730000",730000,AR18)-AS18)*15%-AS18)&gt;"0",((AV18-AM18-IF(AR18&gt;="730000",730000,AR18)-AS18)*15%-AS18),0)</f>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>1912557.6923076923</v>
       </c>
       <c r="BG18" s="85">
-        <f t="shared" ref="BG18:BG19" si="50">AV18-BF18+AW18</f>
-        <v>12750384.615384616</v>
+        <f t="shared" ref="BG18:BG19" si="49">AV18-BF18+AW18</f>
+        <v>10837826.923076924</v>
       </c>
       <c r="BH18" s="85"/>
       <c r="BI18" s="85">
-        <f t="shared" ref="BI18:BI19" si="51">BG18-BB18-BC18+BD18-BH18*4400000-IF(E18="CT",11000000,0)</f>
-        <v>934534.61538461596</v>
+        <f t="shared" ref="BI18:BI19" si="50">BG18-BB18-BC18+BD18-BH18*4400000-IF(E18="CT",11000000,0)</f>
+        <v>-978023.07692307606</v>
       </c>
       <c r="BJ18" s="84">
-        <f t="shared" ref="BJ18:BJ19" si="52">IF(BI18&gt;0,ROUND(IF(BI18&gt;=80000000,BI18*35%-9850000,IF(BI18&gt;=52000000,BI18*30%-5850000,IF(BI18&gt;=32000000,BI18*25%-3250000,IF(BI18&gt;=18000000,BI18*20%-1650000,IF(BI18&gt;=10000000,BI18*15%-750000,IF(BI18&gt;5000000,BI18*10%-250000,BI18*5%)))))),0),0)</f>
-        <v>46727</v>
+        <f t="shared" ref="BJ18:BJ19" si="51">IF(BI18&gt;0,ROUND(IF(BI18&gt;=80000000,BI18*35%-9850000,IF(BI18&gt;=52000000,BI18*30%-5850000,IF(BI18&gt;=32000000,BI18*25%-3250000,IF(BI18&gt;=18000000,BI18*20%-1650000,IF(BI18&gt;=10000000,BI18*15%-750000,IF(BI18&gt;5000000,BI18*10%-250000,BI18*5%)))))),0),0)</f>
+        <v>0</v>
       </c>
       <c r="BK18" s="85"/>
       <c r="BL18" s="85"/>
@@ -17377,11 +17448,11 @@
       <c r="BQ18" s="85"/>
       <c r="BR18" s="85"/>
       <c r="BS18" s="85" t="str">
-        <f t="shared" ref="BS18:BS19" si="53">IF(AV18&gt;=11000000,"80%","100%")</f>
+        <f t="shared" ref="BS18:BS19" si="52">IF(AV18&gt;=11000000,"80%","100%")</f>
         <v>80%</v>
       </c>
       <c r="BT18" s="85">
-        <f t="shared" ref="BT18:BT19" si="54">AV18*BS18-BN18-BK18-BP18-BO18</f>
+        <f t="shared" ref="BT18:BT19" si="53">AV18*BS18-BN18-BK18-BP18-BO18</f>
         <v>10200307.692307694</v>
       </c>
       <c r="BU18" s="105"/>
@@ -17401,7 +17472,7 @@
         <v>1150000</v>
       </c>
       <c r="CB18" s="84">
-        <f t="shared" ref="CB18:CB19" si="55">SUM(BW18:CA18)</f>
+        <f t="shared" ref="CB18:CB19" si="54">SUM(BW18:CA18)</f>
         <v>24150000</v>
       </c>
       <c r="CC18" s="84" t="s">
@@ -17555,19 +17626,19 @@
         <v>102</v>
       </c>
       <c r="AY19" s="85">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>412000</v>
       </c>
       <c r="AZ19" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>77250</v>
       </c>
       <c r="BA19" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>51500</v>
       </c>
       <c r="BB19" s="85">
-        <f t="shared" ref="BB19" si="56">SUM(AY19:BA19)</f>
+        <f t="shared" ref="BB19" si="55">SUM(AY19:BA19)</f>
         <v>540750</v>
       </c>
       <c r="BC19" s="85"/>
@@ -17577,20 +17648,20 @@
         <v>48500</v>
       </c>
       <c r="BF19" s="85">
+        <f t="shared" si="10"/>
+        <v>1124711.5384615383</v>
+      </c>
+      <c r="BG19" s="85">
         <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="BG19" s="85">
-        <f t="shared" si="50"/>
-        <v>7498076.9230769221</v>
+        <v>6373365.384615384</v>
       </c>
       <c r="BH19" s="85"/>
       <c r="BI19" s="85">
+        <f t="shared" si="50"/>
+        <v>-5167384.615384616</v>
+      </c>
+      <c r="BJ19" s="84">
         <f t="shared" si="51"/>
-        <v>-4042673.0769230779</v>
-      </c>
-      <c r="BJ19" s="84">
-        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="BK19" s="85"/>
@@ -17604,11 +17675,11 @@
       <c r="BQ19" s="85"/>
       <c r="BR19" s="85"/>
       <c r="BS19" s="85" t="str">
+        <f t="shared" si="52"/>
+        <v>100%</v>
+      </c>
+      <c r="BT19" s="85">
         <f t="shared" si="53"/>
-        <v>100%</v>
-      </c>
-      <c r="BT19" s="85">
-        <f t="shared" si="54"/>
         <v>7498076.9230769221</v>
       </c>
       <c r="BU19" s="105"/>
@@ -17628,7 +17699,7 @@
         <v>550000</v>
       </c>
       <c r="CB19" s="84">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>11550000</v>
       </c>
       <c r="CC19" s="84" t="s">
@@ -17656,7 +17727,7 @@
         <v>104</v>
       </c>
       <c r="E20" s="123" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="F20" s="124" t="s">
         <v>101</v>
@@ -17708,39 +17779,39 @@
         <v>0</v>
       </c>
       <c r="Y20" s="91">
-        <f t="shared" ref="Y20:Y21" si="57">G20*(K20+L20)/26</f>
+        <f t="shared" ref="Y20:Y21" si="56">G20*(K20+L20)/26</f>
         <v>2560384.6153846155</v>
       </c>
       <c r="Z20" s="91">
-        <f t="shared" ref="Z20:Z21" si="58">M20*G20/26</f>
+        <f t="shared" ref="Z20:Z21" si="57">M20*G20/26</f>
         <v>121923.07692307692</v>
       </c>
       <c r="AA20" s="91">
-        <f t="shared" ref="AA20:AA21" si="59">G20*N20/26</f>
+        <f t="shared" ref="AA20:AA21" si="58">G20*N20/26</f>
         <v>0</v>
       </c>
       <c r="AB20" s="91">
-        <f t="shared" ref="AB20:AB21" si="60">G20*O20/26</f>
+        <f t="shared" ref="AB20:AB21" si="59">G20*O20/26</f>
         <v>487692.30769230769</v>
       </c>
       <c r="AC20" s="91">
-        <f t="shared" ref="AC20:AC21" si="61">G20*P20*150%/26</f>
+        <f t="shared" ref="AC20:AC21" si="60">G20*P20*150%/26</f>
         <v>0</v>
       </c>
       <c r="AD20" s="91">
-        <f t="shared" ref="AD20:AD21" si="62">G20*Q20/26*200%</f>
+        <f t="shared" ref="AD20:AD21" si="61">G20*Q20/26*200%</f>
         <v>0</v>
       </c>
       <c r="AE20" s="91">
-        <f t="shared" ref="AE20:AE21" si="63">G20*R20/26*300%</f>
+        <f t="shared" ref="AE20:AE21" si="62">G20*R20/26*300%</f>
         <v>0</v>
       </c>
       <c r="AF20" s="91">
-        <f t="shared" ref="AF20:AF21" si="64">IF(F20="LT",0,(G20+H20)/26*S20*30%)</f>
+        <f t="shared" ref="AF20:AF21" si="63">IF(F20="LT",0,(G20+H20)/26*S20*30%)</f>
         <v>0</v>
       </c>
       <c r="AG20" s="91">
-        <f t="shared" ref="AG20:AG21" si="65">T20*G20/23/8</f>
+        <f t="shared" ref="AG20:AG21" si="64">T20*G20/23/8</f>
         <v>0</v>
       </c>
       <c r="AH20" s="91">
@@ -17748,7 +17819,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="91">
-        <f t="shared" ref="AI20:AI21" si="66">G20*V20/26</f>
+        <f t="shared" ref="AI20:AI21" si="65">G20*V20/26</f>
         <v>0</v>
       </c>
       <c r="AJ20" s="91"/>
@@ -17762,11 +17833,11 @@
         <v>0</v>
       </c>
       <c r="AN20" s="91">
-        <f t="shared" ref="AN20:AN21" si="67">H20/26*K20</f>
+        <f t="shared" ref="AN20:AN21" si="66">H20/26*K20</f>
         <v>315000</v>
       </c>
       <c r="AO20" s="91">
-        <f t="shared" ref="AO20:AO21" si="68">IF(F20="LN",I20*(K20+L20)/26+(H20+I20)*50%*M20/26+IF(F20="LT",BW20*O20/26-AB20,0)+MAX($G20*P20/26*150%,P20*$BW20/26)-AC20+MAX($G20*Q20/26*200%,Q20*$BW20/26)-AD20+MAX($G20*R20/26*300%,R20*$BW20/26)-AE20+BW20*S20/26-AF20+AH20-AG20,I20-I20*($CF$3-K20-L20)/26+(H20+I20)*50%*M20/26+IF(F20="LT",BW20*O20/26-AB20,0)+MAX($G20*P20/26*150%,P20*$BW20/26)-AC20+MAX($G20*Q20/26*200%,Q20*$BW20/26)-AD20+MAX($G20*R20/26*300%,R20*$BW20/26)-AE20+BW20*S20/26-AF20+AH20-AG20+(G20-G20*($CF$3-K20-L20)/26-Y20)+(H20-H20*($CF$3-K20-L20)/26-AN20))</f>
+        <f t="shared" ref="AO20:AO21" si="67">IF(F20="LN",I20*(K20+L20)/26+(H20+I20)*50%*M20/26+IF(F20="LT",BW20*O20/26-AB20,0)+MAX($G20*P20/26*150%,P20*$BW20/26)-AC20+MAX($G20*Q20/26*200%,Q20*$BW20/26)-AD20+MAX($G20*R20/26*300%,R20*$BW20/26)-AE20+BW20*S20/26-AF20+AH20-AG20,I20-I20*($CF$3-K20-L20)/26+(H20+I20)*50%*M20/26+IF(F20="LT",BW20*O20/26-AB20,0)+MAX($G20*P20/26*150%,P20*$BW20/26)-AC20+MAX($G20*Q20/26*200%,Q20*$BW20/26)-AD20+MAX($G20*R20/26*300%,R20*$BW20/26)-AE20+BW20*S20/26-AF20+AH20-AG20+(G20-G20*($CF$3-K20-L20)/26-Y20)+(H20-H20*($CF$3-K20-L20)/26-AN20))</f>
         <v>9259134.615384616</v>
       </c>
       <c r="AP20" s="91"/>
@@ -17776,7 +17847,7 @@
       <c r="AT20" s="91"/>
       <c r="AU20" s="91"/>
       <c r="AV20" s="94">
-        <f t="shared" ref="AV20:AV21" si="69">Y20+Z20+AA20+AB20+AC20+AD20+AE20+AF20+AG20+AI20+AJ20+AK20+AL20+AM20+AN20+AO20+AP20-AQ20+AR20+AS20+AT20+AU20</f>
+        <f t="shared" ref="AV20:AV21" si="68">Y20+Z20+AA20+AB20+AC20+AD20+AE20+AF20+AG20+AI20+AJ20+AK20+AL20+AM20+AN20+AO20+AP20-AQ20+AR20+AS20+AT20+AU20</f>
         <v>12744134.615384616</v>
       </c>
       <c r="AW20" s="94"/>
@@ -17784,15 +17855,15 @@
         <v>102</v>
       </c>
       <c r="AY20" s="85">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>569600</v>
       </c>
       <c r="AZ20" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>106800</v>
       </c>
       <c r="BA20" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>71200</v>
       </c>
       <c r="BB20" s="85">
@@ -17802,25 +17873,25 @@
       <c r="BC20" s="85"/>
       <c r="BD20" s="85"/>
       <c r="BE20" s="85">
-        <f t="shared" ref="BE20:BE21" si="70">IF(G20*1%&gt;=234000,234000,G20*1%)</f>
+        <f t="shared" ref="BE20:BE21" si="69">IF(G20*1%&gt;=234000,234000,G20*1%)</f>
         <v>63400</v>
       </c>
       <c r="BF20" s="85">
-        <f t="shared" ref="BF20:BF21" si="71">AM20+IF(AR20&gt;="730000",730000,AR20)+IF(((AV20-AM20-IF(AR20&gt;="730000",730000,AR20)-AS20)*15%-AS20)&gt;"0",((AV20-AM20-IF(AR20&gt;="730000",730000,AR20)-AS20)*15%-AS20),0)</f>
-        <v>0</v>
+        <f>AM20+IF(AR20&gt;="730000",730000,AR20)+IF(((AV20-AM20-IF(AR20&gt;="730000",730000,AR20)-AS20)*15%-AS20)&gt;0,((AV20-AM20-IF(AR20&gt;="730000",730000,AR20)-AS20)*15%-AS20),0)</f>
+        <v>1911620.1923076923</v>
       </c>
       <c r="BG20" s="85">
-        <f t="shared" ref="BG20:BG21" si="72">AV20-BF20+AW20</f>
-        <v>12744134.615384616</v>
+        <f t="shared" ref="BG20:BG21" si="70">AV20-BF20+AW20</f>
+        <v>10832514.423076924</v>
       </c>
       <c r="BH20" s="85"/>
       <c r="BI20" s="85">
-        <f t="shared" ref="BI20:BI21" si="73">BG20-BB20-BC20+BD20-BH20*4400000-IF(E20="CT",11000000,0)</f>
-        <v>996534.61538461596</v>
+        <f t="shared" ref="BI20:BI21" si="71">BG20-BB20-BC20+BD20-BH20*4400000-IF(E20="CT",11000000,0)</f>
+        <v>10084914.423076924</v>
       </c>
       <c r="BJ20" s="84">
-        <f t="shared" ref="BJ20:BJ21" si="74">IF(BI20&gt;0,ROUND(IF(BI20&gt;=80000000,BI20*35%-9850000,IF(BI20&gt;=52000000,BI20*30%-5850000,IF(BI20&gt;=32000000,BI20*25%-3250000,IF(BI20&gt;=18000000,BI20*20%-1650000,IF(BI20&gt;=10000000,BI20*15%-750000,IF(BI20&gt;5000000,BI20*10%-250000,BI20*5%)))))),0),0)</f>
-        <v>49827</v>
+        <f t="shared" ref="BJ20:BJ21" si="72">IF(BI20&gt;0,ROUND(IF(BI20&gt;=80000000,BI20*35%-9850000,IF(BI20&gt;=52000000,BI20*30%-5850000,IF(BI20&gt;=32000000,BI20*25%-3250000,IF(BI20&gt;=18000000,BI20*20%-1650000,IF(BI20&gt;=10000000,BI20*15%-750000,IF(BI20&gt;5000000,BI20*10%-250000,BI20*5%)))))),0),0)</f>
+        <v>762737</v>
       </c>
       <c r="BK20" s="85"/>
       <c r="BL20" s="85"/>
@@ -17833,11 +17904,11 @@
       <c r="BQ20" s="85"/>
       <c r="BR20" s="85"/>
       <c r="BS20" s="85" t="str">
-        <f t="shared" ref="BS20:BS21" si="75">IF(AV20&gt;=11000000,"80%","100%")</f>
+        <f t="shared" ref="BS20:BS21" si="73">IF(AV20&gt;=11000000,"80%","100%")</f>
         <v>80%</v>
       </c>
       <c r="BT20" s="85">
-        <f t="shared" ref="BT20:BT21" si="76">AV20*BS20-BN20-BK20-BP20-BO20</f>
+        <f t="shared" ref="BT20:BT21" si="74">AV20*BS20-BN20-BK20-BP20-BO20</f>
         <v>10195307.692307694</v>
       </c>
       <c r="BU20" s="105"/>
@@ -17857,7 +17928,7 @@
         <v>1150000</v>
       </c>
       <c r="CB20" s="84">
-        <f t="shared" ref="CB20:CB21" si="77">SUM(BW20:CA20)</f>
+        <f t="shared" ref="CB20:CB21" si="75">SUM(BW20:CA20)</f>
         <v>24150000</v>
       </c>
       <c r="CC20" s="84" t="s">
@@ -17935,39 +18006,39 @@
         <v>0</v>
       </c>
       <c r="Y21" s="91">
+        <f t="shared" si="56"/>
+        <v>2682307.6923076925</v>
+      </c>
+      <c r="Z21" s="91">
         <f t="shared" si="57"/>
-        <v>2682307.6923076925</v>
-      </c>
-      <c r="Z21" s="91">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="91">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="AA21" s="91">
+      <c r="AB21" s="91">
         <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="AB21" s="91">
+        <v>487692.30769230769</v>
+      </c>
+      <c r="AC21" s="91">
         <f t="shared" si="60"/>
-        <v>487692.30769230769</v>
-      </c>
-      <c r="AC21" s="91">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="91">
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="AD21" s="91">
+      <c r="AE21" s="91">
         <f t="shared" si="62"/>
-        <v>0</v>
-      </c>
-      <c r="AE21" s="91">
+        <v>2926153.846153846</v>
+      </c>
+      <c r="AF21" s="91">
         <f t="shared" si="63"/>
-        <v>2926153.846153846</v>
-      </c>
-      <c r="AF21" s="91">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="91">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="AG21" s="91">
-        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AH21" s="91">
@@ -17975,7 +18046,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="91">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AJ21" s="91"/>
@@ -17989,11 +18060,11 @@
         <v>0</v>
       </c>
       <c r="AN21" s="91">
+        <f t="shared" si="66"/>
+        <v>126923.07692307694</v>
+      </c>
+      <c r="AO21" s="91">
         <f t="shared" si="67"/>
-        <v>126923.07692307694</v>
-      </c>
-      <c r="AO21" s="91">
-        <f t="shared" si="68"/>
         <v>6249230.7692307699</v>
       </c>
       <c r="AP21" s="91"/>
@@ -18003,7 +18074,7 @@
       <c r="AT21" s="91"/>
       <c r="AU21" s="91"/>
       <c r="AV21" s="94">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>12472307.692307692</v>
       </c>
       <c r="AW21" s="94"/>
@@ -18011,43 +18082,43 @@
         <v>102</v>
       </c>
       <c r="AY21" s="85">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>531200</v>
       </c>
       <c r="AZ21" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>99600</v>
       </c>
       <c r="BA21" s="85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>66400</v>
       </c>
       <c r="BB21" s="85">
-        <f t="shared" ref="BB21" si="78">SUM(AY21:BA21)</f>
+        <f t="shared" ref="BB21" si="76">SUM(AY21:BA21)</f>
         <v>697200</v>
       </c>
       <c r="BC21" s="85"/>
       <c r="BD21" s="85"/>
       <c r="BE21" s="85">
+        <f t="shared" si="69"/>
+        <v>63400</v>
+      </c>
+      <c r="BF21" s="85">
+        <f t="shared" si="10"/>
+        <v>1870846.1538461538</v>
+      </c>
+      <c r="BG21" s="85">
         <f t="shared" si="70"/>
-        <v>63400</v>
-      </c>
-      <c r="BF21" s="85">
-        <f t="shared" si="71"/>
-        <v>0</v>
-      </c>
-      <c r="BG21" s="85">
-        <f t="shared" si="72"/>
-        <v>12472307.692307692</v>
+        <v>10601461.538461538</v>
       </c>
       <c r="BH21" s="85"/>
       <c r="BI21" s="85">
-        <f t="shared" si="73"/>
-        <v>775107.69230769202</v>
+        <f t="shared" si="71"/>
+        <v>-1095738.461538462</v>
       </c>
       <c r="BJ21" s="84">
-        <f t="shared" si="74"/>
-        <v>38755</v>
+        <f t="shared" si="72"/>
+        <v>0</v>
       </c>
       <c r="BK21" s="85"/>
       <c r="BL21" s="85"/>
@@ -18060,11 +18131,11 @@
       <c r="BQ21" s="85"/>
       <c r="BR21" s="85"/>
       <c r="BS21" s="85" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>80%</v>
       </c>
       <c r="BT21" s="85">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>9977846.153846154</v>
       </c>
       <c r="BU21" s="105"/>
@@ -18084,7 +18155,7 @@
         <v>850000</v>
       </c>
       <c r="CB21" s="84">
-        <f t="shared" si="77"/>
+        <f t="shared" si="75"/>
         <v>17850000</v>
       </c>
       <c r="CC21" s="84" t="s">
@@ -18298,11 +18369,56 @@
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <mergeCells count="82">
-    <mergeCell ref="AP8:AP11"/>
-    <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="BQ9:BQ11"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="AX8:AX11"/>
+    <mergeCell ref="AY8:BP8"/>
+    <mergeCell ref="BQ8:BR8"/>
+    <mergeCell ref="BT8:BT11"/>
+    <mergeCell ref="BU8:BU11"/>
+    <mergeCell ref="BW8:BW11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="AS8:AS11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="BS8:BS11"/>
+    <mergeCell ref="BO10:BO11"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BL10:BL11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="AY9:BJ9"/>
+    <mergeCell ref="BK9:BP9"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="AC9:AC11"/>
     <mergeCell ref="BW3:CB6"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="B8:B11"/>
@@ -18319,6 +18435,11 @@
     <mergeCell ref="BX8:CA10"/>
     <mergeCell ref="CB8:CB11"/>
     <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="AP8:AP11"/>
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="A3:BU3"/>
     <mergeCell ref="BE10:BE11"/>
     <mergeCell ref="AH9:AH11"/>
     <mergeCell ref="AI9:AI11"/>
@@ -18330,56 +18451,6 @@
     <mergeCell ref="AN9:AN11"/>
     <mergeCell ref="AO9:AO11"/>
     <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="AV8:AV11"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="AY8:BP8"/>
-    <mergeCell ref="BQ8:BR8"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="BU8:BU11"/>
-    <mergeCell ref="BW8:BW11"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="BF10:BF11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="BS8:BS11"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="BJ10:BJ11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="AY9:BJ9"/>
-    <mergeCell ref="BK9:BP9"/>
-    <mergeCell ref="BQ9:BQ11"/>
-    <mergeCell ref="BR9:BR11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B12 C12:BU12 B22:B1048576">
     <cfRule type="duplicateValues" dxfId="12" priority="6"/>
@@ -18613,91 +18684,91 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" outlineLevel="1">
-      <c r="A3" s="402" t="str">
+      <c r="A3" s="449" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
         <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
       </c>
-      <c r="B3" s="402"/>
-      <c r="C3" s="402"/>
-      <c r="D3" s="402"/>
-      <c r="E3" s="402"/>
-      <c r="F3" s="402"/>
-      <c r="G3" s="402"/>
-      <c r="H3" s="402"/>
-      <c r="I3" s="402"/>
-      <c r="J3" s="402"/>
-      <c r="K3" s="402"/>
-      <c r="L3" s="402"/>
-      <c r="M3" s="402"/>
-      <c r="N3" s="402"/>
-      <c r="O3" s="402"/>
-      <c r="P3" s="402"/>
-      <c r="Q3" s="402"/>
-      <c r="R3" s="402"/>
-      <c r="S3" s="402"/>
-      <c r="T3" s="402"/>
-      <c r="U3" s="402"/>
-      <c r="V3" s="402"/>
-      <c r="W3" s="402"/>
-      <c r="X3" s="402"/>
-      <c r="Y3" s="402"/>
-      <c r="Z3" s="402"/>
-      <c r="AA3" s="402"/>
-      <c r="AB3" s="402"/>
-      <c r="AC3" s="402"/>
-      <c r="AD3" s="402"/>
-      <c r="AE3" s="402"/>
-      <c r="AF3" s="402"/>
-      <c r="AG3" s="402"/>
-      <c r="AH3" s="402"/>
-      <c r="AI3" s="402"/>
-      <c r="AJ3" s="402"/>
-      <c r="AK3" s="402"/>
-      <c r="AL3" s="402"/>
-      <c r="AM3" s="402"/>
-      <c r="AN3" s="402"/>
-      <c r="AO3" s="402"/>
-      <c r="AP3" s="402"/>
-      <c r="AQ3" s="402"/>
-      <c r="AR3" s="402"/>
-      <c r="AS3" s="402"/>
-      <c r="AT3" s="402"/>
-      <c r="AU3" s="402"/>
-      <c r="AV3" s="402"/>
-      <c r="AW3" s="402"/>
-      <c r="AX3" s="402"/>
-      <c r="AY3" s="402"/>
-      <c r="AZ3" s="402"/>
-      <c r="BA3" s="402"/>
-      <c r="BB3" s="402"/>
-      <c r="BC3" s="402"/>
-      <c r="BD3" s="402"/>
-      <c r="BE3" s="402"/>
-      <c r="BF3" s="402"/>
-      <c r="BG3" s="402"/>
-      <c r="BH3" s="402"/>
-      <c r="BI3" s="402"/>
-      <c r="BJ3" s="402"/>
-      <c r="BK3" s="402"/>
-      <c r="BL3" s="402"/>
-      <c r="BM3" s="402"/>
-      <c r="BN3" s="402"/>
-      <c r="BO3" s="402"/>
-      <c r="BP3" s="402"/>
-      <c r="BQ3" s="402"/>
-      <c r="BR3" s="402"/>
-      <c r="BS3" s="402"/>
-      <c r="BT3" s="402"/>
-      <c r="BU3" s="402"/>
+      <c r="B3" s="449"/>
+      <c r="C3" s="449"/>
+      <c r="D3" s="449"/>
+      <c r="E3" s="449"/>
+      <c r="F3" s="449"/>
+      <c r="G3" s="449"/>
+      <c r="H3" s="449"/>
+      <c r="I3" s="449"/>
+      <c r="J3" s="449"/>
+      <c r="K3" s="449"/>
+      <c r="L3" s="449"/>
+      <c r="M3" s="449"/>
+      <c r="N3" s="449"/>
+      <c r="O3" s="449"/>
+      <c r="P3" s="449"/>
+      <c r="Q3" s="449"/>
+      <c r="R3" s="449"/>
+      <c r="S3" s="449"/>
+      <c r="T3" s="449"/>
+      <c r="U3" s="449"/>
+      <c r="V3" s="449"/>
+      <c r="W3" s="449"/>
+      <c r="X3" s="449"/>
+      <c r="Y3" s="449"/>
+      <c r="Z3" s="449"/>
+      <c r="AA3" s="449"/>
+      <c r="AB3" s="449"/>
+      <c r="AC3" s="449"/>
+      <c r="AD3" s="449"/>
+      <c r="AE3" s="449"/>
+      <c r="AF3" s="449"/>
+      <c r="AG3" s="449"/>
+      <c r="AH3" s="449"/>
+      <c r="AI3" s="449"/>
+      <c r="AJ3" s="449"/>
+      <c r="AK3" s="449"/>
+      <c r="AL3" s="449"/>
+      <c r="AM3" s="449"/>
+      <c r="AN3" s="449"/>
+      <c r="AO3" s="449"/>
+      <c r="AP3" s="449"/>
+      <c r="AQ3" s="449"/>
+      <c r="AR3" s="449"/>
+      <c r="AS3" s="449"/>
+      <c r="AT3" s="449"/>
+      <c r="AU3" s="449"/>
+      <c r="AV3" s="449"/>
+      <c r="AW3" s="449"/>
+      <c r="AX3" s="449"/>
+      <c r="AY3" s="449"/>
+      <c r="AZ3" s="449"/>
+      <c r="BA3" s="449"/>
+      <c r="BB3" s="449"/>
+      <c r="BC3" s="449"/>
+      <c r="BD3" s="449"/>
+      <c r="BE3" s="449"/>
+      <c r="BF3" s="449"/>
+      <c r="BG3" s="449"/>
+      <c r="BH3" s="449"/>
+      <c r="BI3" s="449"/>
+      <c r="BJ3" s="449"/>
+      <c r="BK3" s="449"/>
+      <c r="BL3" s="449"/>
+      <c r="BM3" s="449"/>
+      <c r="BN3" s="449"/>
+      <c r="BO3" s="449"/>
+      <c r="BP3" s="449"/>
+      <c r="BQ3" s="449"/>
+      <c r="BR3" s="449"/>
+      <c r="BS3" s="449"/>
+      <c r="BT3" s="449"/>
+      <c r="BU3" s="449"/>
       <c r="BV3"/>
-      <c r="BW3" s="403" t="s">
+      <c r="BW3" s="450" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="403"/>
-      <c r="BY3" s="403"/>
-      <c r="BZ3" s="403"/>
-      <c r="CA3" s="403"/>
-      <c r="CB3" s="402"/>
+      <c r="BX3" s="450"/>
+      <c r="BY3" s="450"/>
+      <c r="BZ3" s="450"/>
+      <c r="CA3" s="450"/>
+      <c r="CB3" s="449"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -18781,368 +18852,368 @@
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
       <c r="BV4"/>
-      <c r="BW4" s="402"/>
-      <c r="BX4" s="402"/>
-      <c r="BY4" s="402"/>
-      <c r="BZ4" s="402"/>
-      <c r="CA4" s="402"/>
-      <c r="CB4" s="402"/>
+      <c r="BW4" s="449"/>
+      <c r="BX4" s="449"/>
+      <c r="BY4" s="449"/>
+      <c r="BZ4" s="449"/>
+      <c r="CA4" s="449"/>
+      <c r="CB4" s="449"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="404" t="s">
+      <c r="A5" s="451" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="407" t="s">
+      <c r="B5" s="454" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="410" t="s">
+      <c r="C5" s="402" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="413" t="s">
+      <c r="D5" s="457" t="s">
         <v>142</v>
       </c>
-      <c r="E5" s="413" t="s">
+      <c r="E5" s="457" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="492" t="s">
+      <c r="F5" s="474" t="s">
         <v>143</v>
       </c>
-      <c r="G5" s="410" t="s">
+      <c r="G5" s="402" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="416" t="s">
+      <c r="H5" s="415" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="416" t="s">
+      <c r="I5" s="415" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="410" t="s">
+      <c r="J5" s="402" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="419" t="s">
+      <c r="K5" s="460" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="420"/>
-      <c r="M5" s="420"/>
-      <c r="N5" s="420"/>
-      <c r="O5" s="420"/>
-      <c r="P5" s="420"/>
-      <c r="Q5" s="420"/>
-      <c r="R5" s="420"/>
-      <c r="S5" s="420"/>
-      <c r="T5" s="420"/>
-      <c r="U5" s="420"/>
-      <c r="V5" s="420"/>
-      <c r="W5" s="420"/>
-      <c r="X5" s="420"/>
-      <c r="Y5" s="421" t="s">
+      <c r="L5" s="461"/>
+      <c r="M5" s="461"/>
+      <c r="N5" s="461"/>
+      <c r="O5" s="461"/>
+      <c r="P5" s="461"/>
+      <c r="Q5" s="461"/>
+      <c r="R5" s="461"/>
+      <c r="S5" s="461"/>
+      <c r="T5" s="461"/>
+      <c r="U5" s="461"/>
+      <c r="V5" s="461"/>
+      <c r="W5" s="461"/>
+      <c r="X5" s="461"/>
+      <c r="Y5" s="462" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="422"/>
-      <c r="AA5" s="422"/>
-      <c r="AB5" s="422"/>
-      <c r="AC5" s="422"/>
-      <c r="AD5" s="422"/>
-      <c r="AE5" s="422"/>
-      <c r="AF5" s="422"/>
-      <c r="AG5" s="422"/>
-      <c r="AH5" s="422"/>
-      <c r="AI5" s="422"/>
-      <c r="AJ5" s="422"/>
-      <c r="AK5" s="422"/>
-      <c r="AL5" s="422"/>
-      <c r="AM5" s="422"/>
-      <c r="AN5" s="422"/>
-      <c r="AO5" s="423"/>
-      <c r="AP5" s="410" t="s">
+      <c r="Z5" s="463"/>
+      <c r="AA5" s="463"/>
+      <c r="AB5" s="463"/>
+      <c r="AC5" s="463"/>
+      <c r="AD5" s="463"/>
+      <c r="AE5" s="463"/>
+      <c r="AF5" s="463"/>
+      <c r="AG5" s="463"/>
+      <c r="AH5" s="463"/>
+      <c r="AI5" s="463"/>
+      <c r="AJ5" s="463"/>
+      <c r="AK5" s="463"/>
+      <c r="AL5" s="463"/>
+      <c r="AM5" s="463"/>
+      <c r="AN5" s="463"/>
+      <c r="AO5" s="464"/>
+      <c r="AP5" s="402" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="410" t="s">
+      <c r="AQ5" s="402" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="410" t="s">
+      <c r="AR5" s="402" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="410" t="s">
+      <c r="AS5" s="402" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="410" t="s">
+      <c r="AT5" s="402" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="410" t="s">
+      <c r="AU5" s="402" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="410" t="s">
+      <c r="AV5" s="402" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="410" t="s">
+      <c r="AW5" s="402" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="410" t="s">
+      <c r="AX5" s="402" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="431" t="s">
+      <c r="AY5" s="405" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="432"/>
-      <c r="BA5" s="432"/>
-      <c r="BB5" s="432"/>
-      <c r="BC5" s="432"/>
-      <c r="BD5" s="432"/>
-      <c r="BE5" s="432"/>
-      <c r="BF5" s="432"/>
-      <c r="BG5" s="432"/>
-      <c r="BH5" s="432"/>
-      <c r="BI5" s="432"/>
-      <c r="BJ5" s="432"/>
-      <c r="BK5" s="432"/>
-      <c r="BL5" s="432"/>
-      <c r="BM5" s="432"/>
-      <c r="BN5" s="432"/>
-      <c r="BO5" s="432"/>
-      <c r="BP5" s="433"/>
-      <c r="BQ5" s="434" t="s">
+      <c r="AZ5" s="406"/>
+      <c r="BA5" s="406"/>
+      <c r="BB5" s="406"/>
+      <c r="BC5" s="406"/>
+      <c r="BD5" s="406"/>
+      <c r="BE5" s="406"/>
+      <c r="BF5" s="406"/>
+      <c r="BG5" s="406"/>
+      <c r="BH5" s="406"/>
+      <c r="BI5" s="406"/>
+      <c r="BJ5" s="406"/>
+      <c r="BK5" s="406"/>
+      <c r="BL5" s="406"/>
+      <c r="BM5" s="406"/>
+      <c r="BN5" s="406"/>
+      <c r="BO5" s="406"/>
+      <c r="BP5" s="407"/>
+      <c r="BQ5" s="433" t="s">
         <v>26</v>
       </c>
-      <c r="BR5" s="435"/>
-      <c r="BS5" s="436" t="s">
+      <c r="BR5" s="442"/>
+      <c r="BS5" s="410" t="s">
         <v>144</v>
       </c>
-      <c r="BT5" s="436" t="s">
+      <c r="BT5" s="410" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="434" t="s">
+      <c r="BU5" s="433" t="s">
         <v>28</v>
       </c>
       <c r="BV5"/>
-      <c r="BW5" s="457" t="s">
+      <c r="BW5" s="436" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="443" t="s">
+      <c r="BX5" s="421" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="444"/>
-      <c r="BZ5" s="444"/>
-      <c r="CA5" s="445"/>
-      <c r="CB5" s="452" t="s">
+      <c r="BY5" s="422"/>
+      <c r="BZ5" s="422"/>
+      <c r="CA5" s="423"/>
+      <c r="CB5" s="430" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="384" t="s">
+      <c r="CC5" s="326" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="384" t="s">
+      <c r="CD5" s="326" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
     <row r="6" spans="1:87" s="136" customFormat="1">
-      <c r="A6" s="405"/>
-      <c r="B6" s="408"/>
-      <c r="C6" s="411"/>
-      <c r="D6" s="414"/>
-      <c r="E6" s="414"/>
-      <c r="F6" s="493"/>
-      <c r="G6" s="411"/>
-      <c r="H6" s="417"/>
-      <c r="I6" s="417"/>
-      <c r="J6" s="411"/>
-      <c r="K6" s="424" t="s">
+      <c r="A6" s="452"/>
+      <c r="B6" s="455"/>
+      <c r="C6" s="403"/>
+      <c r="D6" s="458"/>
+      <c r="E6" s="458"/>
+      <c r="F6" s="475"/>
+      <c r="G6" s="403"/>
+      <c r="H6" s="416"/>
+      <c r="I6" s="416"/>
+      <c r="J6" s="403"/>
+      <c r="K6" s="439" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="424" t="s">
+      <c r="L6" s="439" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="424" t="s">
+      <c r="M6" s="439" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="424" t="s">
+      <c r="N6" s="439" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="424" t="s">
+      <c r="O6" s="439" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="424" t="s">
+      <c r="P6" s="439" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="424" t="s">
+      <c r="Q6" s="439" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="424" t="s">
+      <c r="R6" s="439" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="424" t="s">
+      <c r="S6" s="439" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="424" t="s">
+      <c r="T6" s="439" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="424" t="s">
+      <c r="U6" s="439" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="427" t="s">
+      <c r="V6" s="445" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="428"/>
-      <c r="X6" s="424" t="s">
+      <c r="W6" s="446"/>
+      <c r="X6" s="439" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="410" t="s">
+      <c r="Y6" s="402" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="410" t="s">
+      <c r="Z6" s="402" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="410" t="s">
+      <c r="AA6" s="402" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="410" t="s">
+      <c r="AB6" s="402" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="416" t="s">
+      <c r="AC6" s="415" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="416" t="s">
+      <c r="AD6" s="415" t="s">
         <v>145</v>
       </c>
-      <c r="AE6" s="416" t="s">
+      <c r="AE6" s="415" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="416" t="s">
+      <c r="AF6" s="415" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="410" t="s">
+      <c r="AG6" s="402" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="416" t="s">
+      <c r="AH6" s="415" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="416" t="s">
+      <c r="AI6" s="415" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="410" t="s">
+      <c r="AJ6" s="402" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="460" t="s">
+      <c r="AK6" s="418" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="410" t="s">
+      <c r="AL6" s="402" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="410" t="s">
+      <c r="AM6" s="402" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="342" t="s">
+      <c r="AN6" s="329" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="410" t="s">
+      <c r="AO6" s="402" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="411"/>
-      <c r="AQ6" s="411"/>
-      <c r="AR6" s="411"/>
-      <c r="AS6" s="411"/>
-      <c r="AT6" s="411"/>
-      <c r="AU6" s="411"/>
-      <c r="AV6" s="411"/>
-      <c r="AW6" s="411"/>
-      <c r="AX6" s="411"/>
-      <c r="AY6" s="431" t="s">
+      <c r="AP6" s="403"/>
+      <c r="AQ6" s="403"/>
+      <c r="AR6" s="403"/>
+      <c r="AS6" s="403"/>
+      <c r="AT6" s="403"/>
+      <c r="AU6" s="403"/>
+      <c r="AV6" s="403"/>
+      <c r="AW6" s="403"/>
+      <c r="AX6" s="403"/>
+      <c r="AY6" s="405" t="s">
         <v>64</v>
       </c>
-      <c r="AZ6" s="432"/>
-      <c r="BA6" s="432"/>
-      <c r="BB6" s="432"/>
-      <c r="BC6" s="432"/>
-      <c r="BD6" s="432"/>
-      <c r="BE6" s="432"/>
-      <c r="BF6" s="432"/>
-      <c r="BG6" s="432"/>
-      <c r="BH6" s="432"/>
-      <c r="BI6" s="432"/>
-      <c r="BJ6" s="433"/>
-      <c r="BK6" s="431" t="s">
+      <c r="AZ6" s="406"/>
+      <c r="BA6" s="406"/>
+      <c r="BB6" s="406"/>
+      <c r="BC6" s="406"/>
+      <c r="BD6" s="406"/>
+      <c r="BE6" s="406"/>
+      <c r="BF6" s="406"/>
+      <c r="BG6" s="406"/>
+      <c r="BH6" s="406"/>
+      <c r="BI6" s="406"/>
+      <c r="BJ6" s="407"/>
+      <c r="BK6" s="405" t="s">
         <v>65</v>
       </c>
-      <c r="BL6" s="432"/>
-      <c r="BM6" s="432"/>
-      <c r="BN6" s="432"/>
-      <c r="BO6" s="432"/>
-      <c r="BP6" s="433"/>
-      <c r="BQ6" s="437" t="s">
+      <c r="BL6" s="406"/>
+      <c r="BM6" s="406"/>
+      <c r="BN6" s="406"/>
+      <c r="BO6" s="406"/>
+      <c r="BP6" s="407"/>
+      <c r="BQ6" s="408" t="s">
         <v>66</v>
       </c>
-      <c r="BR6" s="437" t="s">
+      <c r="BR6" s="408" t="s">
         <v>67</v>
       </c>
-      <c r="BS6" s="437"/>
-      <c r="BT6" s="437"/>
-      <c r="BU6" s="455"/>
+      <c r="BS6" s="408"/>
+      <c r="BT6" s="408"/>
+      <c r="BU6" s="434"/>
       <c r="BV6"/>
-      <c r="BW6" s="458"/>
-      <c r="BX6" s="446"/>
-      <c r="BY6" s="447"/>
-      <c r="BZ6" s="447"/>
-      <c r="CA6" s="448"/>
-      <c r="CB6" s="453"/>
-      <c r="CC6" s="385"/>
-      <c r="CD6" s="385"/>
+      <c r="BW6" s="437"/>
+      <c r="BX6" s="424"/>
+      <c r="BY6" s="425"/>
+      <c r="BZ6" s="425"/>
+      <c r="CA6" s="426"/>
+      <c r="CB6" s="431"/>
+      <c r="CC6" s="327"/>
+      <c r="CD6" s="327"/>
       <c r="CH6" s="137"/>
       <c r="CI6" s="138"/>
     </row>
     <row r="7" spans="1:87" s="136" customFormat="1">
-      <c r="A7" s="405"/>
-      <c r="B7" s="408"/>
-      <c r="C7" s="411"/>
-      <c r="D7" s="414"/>
-      <c r="E7" s="414"/>
-      <c r="F7" s="493"/>
-      <c r="G7" s="411"/>
-      <c r="H7" s="417"/>
-      <c r="I7" s="417"/>
-      <c r="J7" s="411"/>
-      <c r="K7" s="425"/>
-      <c r="L7" s="425"/>
-      <c r="M7" s="425"/>
-      <c r="N7" s="425"/>
-      <c r="O7" s="425"/>
-      <c r="P7" s="425"/>
-      <c r="Q7" s="425"/>
-      <c r="R7" s="425"/>
-      <c r="S7" s="425"/>
-      <c r="T7" s="425"/>
-      <c r="U7" s="425"/>
-      <c r="V7" s="429"/>
-      <c r="W7" s="430"/>
-      <c r="X7" s="425"/>
-      <c r="Y7" s="411"/>
-      <c r="Z7" s="411"/>
-      <c r="AA7" s="411"/>
-      <c r="AB7" s="411"/>
-      <c r="AC7" s="417"/>
-      <c r="AD7" s="417"/>
-      <c r="AE7" s="417"/>
-      <c r="AF7" s="417"/>
-      <c r="AG7" s="411"/>
-      <c r="AH7" s="417"/>
-      <c r="AI7" s="417"/>
-      <c r="AJ7" s="411"/>
-      <c r="AK7" s="461"/>
-      <c r="AL7" s="411"/>
-      <c r="AM7" s="411"/>
-      <c r="AN7" s="343"/>
-      <c r="AO7" s="411"/>
-      <c r="AP7" s="411"/>
-      <c r="AQ7" s="411"/>
-      <c r="AR7" s="411"/>
-      <c r="AS7" s="411"/>
-      <c r="AT7" s="411"/>
-      <c r="AU7" s="411"/>
-      <c r="AV7" s="411"/>
-      <c r="AW7" s="411"/>
-      <c r="AX7" s="411"/>
+      <c r="A7" s="452"/>
+      <c r="B7" s="455"/>
+      <c r="C7" s="403"/>
+      <c r="D7" s="458"/>
+      <c r="E7" s="458"/>
+      <c r="F7" s="475"/>
+      <c r="G7" s="403"/>
+      <c r="H7" s="416"/>
+      <c r="I7" s="416"/>
+      <c r="J7" s="403"/>
+      <c r="K7" s="440"/>
+      <c r="L7" s="440"/>
+      <c r="M7" s="440"/>
+      <c r="N7" s="440"/>
+      <c r="O7" s="440"/>
+      <c r="P7" s="440"/>
+      <c r="Q7" s="440"/>
+      <c r="R7" s="440"/>
+      <c r="S7" s="440"/>
+      <c r="T7" s="440"/>
+      <c r="U7" s="440"/>
+      <c r="V7" s="447"/>
+      <c r="W7" s="448"/>
+      <c r="X7" s="440"/>
+      <c r="Y7" s="403"/>
+      <c r="Z7" s="403"/>
+      <c r="AA7" s="403"/>
+      <c r="AB7" s="403"/>
+      <c r="AC7" s="416"/>
+      <c r="AD7" s="416"/>
+      <c r="AE7" s="416"/>
+      <c r="AF7" s="416"/>
+      <c r="AG7" s="403"/>
+      <c r="AH7" s="416"/>
+      <c r="AI7" s="416"/>
+      <c r="AJ7" s="403"/>
+      <c r="AK7" s="419"/>
+      <c r="AL7" s="403"/>
+      <c r="AM7" s="403"/>
+      <c r="AN7" s="330"/>
+      <c r="AO7" s="403"/>
+      <c r="AP7" s="403"/>
+      <c r="AQ7" s="403"/>
+      <c r="AR7" s="403"/>
+      <c r="AS7" s="403"/>
+      <c r="AT7" s="403"/>
+      <c r="AU7" s="403"/>
+      <c r="AV7" s="403"/>
+      <c r="AW7" s="403"/>
+      <c r="AX7" s="403"/>
       <c r="AY7" s="101" t="s">
         <v>68</v>
       </c>
@@ -19152,123 +19223,123 @@
       <c r="BA7" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="BB7" s="436" t="s">
+      <c r="BB7" s="410" t="s">
         <v>71</v>
       </c>
-      <c r="BC7" s="439" t="s">
+      <c r="BC7" s="411" t="s">
         <v>72</v>
       </c>
-      <c r="BD7" s="439" t="s">
+      <c r="BD7" s="411" t="s">
         <v>73</v>
       </c>
-      <c r="BE7" s="439" t="s">
+      <c r="BE7" s="411" t="s">
         <v>146</v>
       </c>
-      <c r="BF7" s="439" t="s">
+      <c r="BF7" s="411" t="s">
         <v>75</v>
       </c>
-      <c r="BG7" s="439" t="s">
+      <c r="BG7" s="411" t="s">
         <v>76</v>
       </c>
-      <c r="BH7" s="439" t="s">
+      <c r="BH7" s="411" t="s">
         <v>77</v>
       </c>
-      <c r="BI7" s="439" t="s">
+      <c r="BI7" s="411" t="s">
         <v>80</v>
       </c>
-      <c r="BJ7" s="463" t="s">
+      <c r="BJ7" s="413" t="s">
         <v>81</v>
       </c>
-      <c r="BK7" s="439" t="s">
+      <c r="BK7" s="411" t="s">
         <v>82</v>
       </c>
-      <c r="BL7" s="436" t="s">
+      <c r="BL7" s="410" t="s">
         <v>83</v>
       </c>
-      <c r="BM7" s="439" t="s">
+      <c r="BM7" s="411" t="s">
         <v>84</v>
       </c>
-      <c r="BN7" s="436" t="s">
+      <c r="BN7" s="410" t="s">
         <v>85</v>
       </c>
-      <c r="BO7" s="436" t="s">
+      <c r="BO7" s="410" t="s">
         <v>147</v>
       </c>
-      <c r="BP7" s="436" t="s">
+      <c r="BP7" s="410" t="s">
         <v>86</v>
       </c>
-      <c r="BQ7" s="437"/>
-      <c r="BR7" s="437"/>
-      <c r="BS7" s="437"/>
-      <c r="BT7" s="437"/>
-      <c r="BU7" s="455"/>
+      <c r="BQ7" s="408"/>
+      <c r="BR7" s="408"/>
+      <c r="BS7" s="408"/>
+      <c r="BT7" s="408"/>
+      <c r="BU7" s="434"/>
       <c r="BV7"/>
-      <c r="BW7" s="459"/>
-      <c r="BX7" s="449"/>
-      <c r="BY7" s="450"/>
-      <c r="BZ7" s="450"/>
-      <c r="CA7" s="451"/>
-      <c r="CB7" s="454"/>
-      <c r="CC7" s="386"/>
-      <c r="CD7" s="386"/>
+      <c r="BW7" s="438"/>
+      <c r="BX7" s="427"/>
+      <c r="BY7" s="428"/>
+      <c r="BZ7" s="428"/>
+      <c r="CA7" s="429"/>
+      <c r="CB7" s="432"/>
+      <c r="CC7" s="328"/>
+      <c r="CD7" s="328"/>
       <c r="CH7" s="137"/>
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="136" customFormat="1" ht="24">
-      <c r="A8" s="406"/>
-      <c r="B8" s="409"/>
-      <c r="C8" s="412"/>
-      <c r="D8" s="415"/>
-      <c r="E8" s="415"/>
-      <c r="F8" s="494"/>
-      <c r="G8" s="412"/>
-      <c r="H8" s="418"/>
-      <c r="I8" s="418"/>
-      <c r="J8" s="412"/>
-      <c r="K8" s="426"/>
-      <c r="L8" s="426"/>
-      <c r="M8" s="426"/>
-      <c r="N8" s="426"/>
-      <c r="O8" s="426"/>
-      <c r="P8" s="426"/>
-      <c r="Q8" s="426"/>
-      <c r="R8" s="426"/>
-      <c r="S8" s="426"/>
-      <c r="T8" s="426"/>
-      <c r="U8" s="426"/>
+      <c r="A8" s="453"/>
+      <c r="B8" s="456"/>
+      <c r="C8" s="404"/>
+      <c r="D8" s="459"/>
+      <c r="E8" s="459"/>
+      <c r="F8" s="476"/>
+      <c r="G8" s="404"/>
+      <c r="H8" s="417"/>
+      <c r="I8" s="417"/>
+      <c r="J8" s="404"/>
+      <c r="K8" s="441"/>
+      <c r="L8" s="441"/>
+      <c r="M8" s="441"/>
+      <c r="N8" s="441"/>
+      <c r="O8" s="441"/>
+      <c r="P8" s="441"/>
+      <c r="Q8" s="441"/>
+      <c r="R8" s="441"/>
+      <c r="S8" s="441"/>
+      <c r="T8" s="441"/>
+      <c r="U8" s="441"/>
       <c r="V8" s="140" t="s">
         <v>87</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>88</v>
       </c>
-      <c r="X8" s="426"/>
-      <c r="Y8" s="412"/>
-      <c r="Z8" s="412"/>
-      <c r="AA8" s="412"/>
-      <c r="AB8" s="412"/>
-      <c r="AC8" s="418"/>
-      <c r="AD8" s="418"/>
-      <c r="AE8" s="418"/>
-      <c r="AF8" s="418"/>
-      <c r="AG8" s="412"/>
-      <c r="AH8" s="418"/>
-      <c r="AI8" s="418"/>
-      <c r="AJ8" s="412"/>
-      <c r="AK8" s="462"/>
-      <c r="AL8" s="412"/>
-      <c r="AM8" s="412"/>
-      <c r="AN8" s="344"/>
-      <c r="AO8" s="412"/>
-      <c r="AP8" s="412"/>
-      <c r="AQ8" s="412"/>
-      <c r="AR8" s="412"/>
-      <c r="AS8" s="412"/>
-      <c r="AT8" s="412"/>
-      <c r="AU8" s="412"/>
-      <c r="AV8" s="412"/>
-      <c r="AW8" s="412"/>
-      <c r="AX8" s="412"/>
+      <c r="X8" s="441"/>
+      <c r="Y8" s="404"/>
+      <c r="Z8" s="404"/>
+      <c r="AA8" s="404"/>
+      <c r="AB8" s="404"/>
+      <c r="AC8" s="417"/>
+      <c r="AD8" s="417"/>
+      <c r="AE8" s="417"/>
+      <c r="AF8" s="417"/>
+      <c r="AG8" s="404"/>
+      <c r="AH8" s="417"/>
+      <c r="AI8" s="417"/>
+      <c r="AJ8" s="404"/>
+      <c r="AK8" s="420"/>
+      <c r="AL8" s="404"/>
+      <c r="AM8" s="404"/>
+      <c r="AN8" s="331"/>
+      <c r="AO8" s="404"/>
+      <c r="AP8" s="404"/>
+      <c r="AQ8" s="404"/>
+      <c r="AR8" s="404"/>
+      <c r="AS8" s="404"/>
+      <c r="AT8" s="404"/>
+      <c r="AU8" s="404"/>
+      <c r="AV8" s="404"/>
+      <c r="AW8" s="404"/>
+      <c r="AX8" s="404"/>
       <c r="AY8" s="102" t="s">
         <v>89</v>
       </c>
@@ -19278,28 +19349,28 @@
       <c r="BA8" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="BB8" s="438"/>
-      <c r="BC8" s="440"/>
-      <c r="BD8" s="440"/>
-      <c r="BE8" s="440"/>
-      <c r="BF8" s="440"/>
-      <c r="BG8" s="440"/>
-      <c r="BH8" s="440"/>
-      <c r="BI8" s="440"/>
-      <c r="BJ8" s="464"/>
-      <c r="BK8" s="440"/>
-      <c r="BL8" s="438"/>
-      <c r="BM8" s="440"/>
-      <c r="BN8" s="438"/>
-      <c r="BO8" s="438"/>
-      <c r="BP8" s="438"/>
-      <c r="BQ8" s="438"/>
-      <c r="BR8" s="438"/>
-      <c r="BS8" s="438"/>
-      <c r="BT8" s="438"/>
-      <c r="BU8" s="456"/>
+      <c r="BB8" s="409"/>
+      <c r="BC8" s="412"/>
+      <c r="BD8" s="412"/>
+      <c r="BE8" s="412"/>
+      <c r="BF8" s="412"/>
+      <c r="BG8" s="412"/>
+      <c r="BH8" s="412"/>
+      <c r="BI8" s="412"/>
+      <c r="BJ8" s="414"/>
+      <c r="BK8" s="412"/>
+      <c r="BL8" s="409"/>
+      <c r="BM8" s="412"/>
+      <c r="BN8" s="409"/>
+      <c r="BO8" s="409"/>
+      <c r="BP8" s="409"/>
+      <c r="BQ8" s="409"/>
+      <c r="BR8" s="409"/>
+      <c r="BS8" s="409"/>
+      <c r="BT8" s="409"/>
+      <c r="BU8" s="435"/>
       <c r="BV8"/>
-      <c r="BW8" s="459"/>
+      <c r="BW8" s="438"/>
       <c r="BX8" s="72" t="s">
         <v>92</v>
       </c>
@@ -19312,9 +19383,9 @@
       <c r="CA8" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="CB8" s="454"/>
-      <c r="CC8" s="386"/>
-      <c r="CD8" s="386"/>
+      <c r="CB8" s="432"/>
+      <c r="CC8" s="328"/>
+      <c r="CD8" s="328"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
       <c r="CI8" s="138"/>
@@ -21491,6 +21562,72 @@
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <mergeCells count="82">
+    <mergeCell ref="BK6:BP6"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="BJ7:BJ8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="AY6:BJ6"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="CB5:CB8"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AT5:AT8"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AW5:AW8"/>
+    <mergeCell ref="BK7:BK8"/>
+    <mergeCell ref="BL7:BL8"/>
+    <mergeCell ref="BM7:BM8"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="BH7:BH8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="BQ6:BQ8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="AY5:BP5"/>
+    <mergeCell ref="BQ5:BR5"/>
+    <mergeCell ref="BS5:BS8"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BR6:BR8"/>
     <mergeCell ref="A3:BU3"/>
     <mergeCell ref="BW3:CB4"/>
     <mergeCell ref="A5:A8"/>
@@ -21507,72 +21644,6 @@
     <mergeCell ref="Y5:AO5"/>
     <mergeCell ref="AP5:AP8"/>
     <mergeCell ref="P6:P8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="AY5:BP5"/>
-    <mergeCell ref="BQ5:BR5"/>
-    <mergeCell ref="BS5:BS8"/>
-    <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="BQ6:BQ8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="CB5:CB8"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AT5:AT8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AW5:AW8"/>
-    <mergeCell ref="BK7:BK8"/>
-    <mergeCell ref="BL7:BL8"/>
-    <mergeCell ref="BM7:BM8"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="AY6:BJ6"/>
-    <mergeCell ref="BK6:BP6"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="BJ7:BJ8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 C9:BU9 B20:B1048576">
     <cfRule type="duplicateValues" dxfId="6" priority="63"/>

--- a/thaco/API/1 - VPTQ THACO-11FEBv2.xlsx
+++ b/thaco/API/1 - VPTQ THACO-11FEBv2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/API/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F3329C-22EE-8142-9521-EF5CA36403B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A647EC9A-AD52-B442-9490-D413A7D93B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38400" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="761" xr2:uid="{D2D6ECD8-DC99-4D28-8DAC-0623419D46D2}"/>
   </bookViews>
